--- a/research/traditional_assets/database/data/finland/finland_power.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_power.xlsx
@@ -650,10 +650,10 @@
         <v>0.1534915466639813</v>
       </c>
       <c r="X2">
-        <v>0.07593523652692906</v>
+        <v>0.0759195897827952</v>
       </c>
       <c r="Y2">
-        <v>0.07755631013705223</v>
+        <v>0.07757195688118609</v>
       </c>
       <c r="Z2">
         <v>0.6532177612136955</v>
@@ -662,10 +662,10 @@
         <v>0.1106147202491732</v>
       </c>
       <c r="AB2">
-        <v>0.06687216140403508</v>
+        <v>0.06686164350388715</v>
       </c>
       <c r="AC2">
-        <v>0.04374255884513811</v>
+        <v>0.04375307674528604</v>
       </c>
       <c r="AD2">
         <v>6122</v>
@@ -787,10 +787,10 @@
         <v>0.1534915466639813</v>
       </c>
       <c r="X3">
-        <v>0.07593523652692906</v>
+        <v>0.0759195897827952</v>
       </c>
       <c r="Y3">
-        <v>0.07755631013705223</v>
+        <v>0.07757195688118609</v>
       </c>
       <c r="Z3">
         <v>0.6532177612136955</v>
@@ -799,10 +799,10 @@
         <v>0.1106147202491732</v>
       </c>
       <c r="AB3">
-        <v>0.06687216140403508</v>
+        <v>0.06686164350388715</v>
       </c>
       <c r="AC3">
-        <v>0.04374255884513811</v>
+        <v>0.04375307674528604</v>
       </c>
       <c r="AD3">
         <v>6122</v>
@@ -1139,49 +1139,49 @@
         <v>5.66719555731852</v>
       </c>
       <c r="F2">
-        <v>7.09356410817006</v>
+        <v>3.0021311098624</v>
       </c>
       <c r="G2">
         <v>3.30062540435627</v>
       </c>
       <c r="H2">
-        <v>1.91317338796636</v>
+        <v>4.32981345697649</v>
       </c>
       <c r="I2">
         <v>0.327789854684472</v>
       </c>
       <c r="J2">
-        <v>0.19</v>
+        <v>0.43</v>
       </c>
       <c r="K2">
         <v>12554.6</v>
       </c>
       <c r="L2">
-        <v>15183.7911625794</v>
+        <v>10754.2214794009</v>
       </c>
       <c r="M2">
         <v>13964.4</v>
       </c>
       <c r="N2">
-        <v>14020.1451625794</v>
+        <v>14072.9594794009</v>
       </c>
       <c r="O2">
         <v>6122</v>
       </c>
       <c r="P2">
-        <v>3548.554</v>
+        <v>8030.938</v>
       </c>
       <c r="Q2">
-        <v>0.0668721614040351</v>
+        <v>0.06686164350388719</v>
       </c>
       <c r="R2">
-        <v>0.0665798017045888</v>
+        <v>0.0662944374417184</v>
       </c>
       <c r="S2">
         <v>0.0482861955533515</v>
       </c>
       <c r="T2">
-        <v>0.0454061955533515</v>
+        <v>0.0474061955533515</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.0759352365269291</v>
+        <v>0.0759195897827952</v>
       </c>
       <c r="X2">
-        <v>0.0715464500610519</v>
+        <v>0.08054346202417061</v>
       </c>
       <c r="Y2">
         <v>0.6192904673517921</v>
       </c>
       <c r="Z2">
-        <v>0.529099251526041</v>
+        <v>0.714362147344329</v>
       </c>
       <c r="AA2">
         <v>6122</v>
@@ -1236,7 +1236,7 @@
         <v>12554.6</v>
       </c>
       <c r="AK2">
-        <v>0.0486609081127847</v>
+        <v>0.04863564251455779</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06747840389755926</v>
+        <v>0.06746714808947185</v>
       </c>
       <c r="C2">
-        <v>18562.40691517397</v>
+        <v>18562.54365853564</v>
       </c>
       <c r="D2">
-        <v>13850.20691517397</v>
+        <v>13850.34365853564</v>
       </c>
       <c r="E2">
         <v>-6122</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06747840389755926</v>
+        <v>0.06746714808947185</v>
       </c>
       <c r="T2">
         <v>0.4454993697880389</v>
       </c>
       <c r="U2">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06742230904529765</v>
+        <v>0.06739987574882643</v>
       </c>
       <c r="C3">
-        <v>18386.12858854977</v>
+        <v>18388.35738163073</v>
       </c>
       <c r="D3">
-        <v>13860.69458854977</v>
+        <v>13862.92338163073</v>
       </c>
       <c r="E3">
         <v>-5935.234</v>
@@ -1539,37 +1539,37 @@
         <v>1428.7</v>
       </c>
       <c r="M3">
-        <v>10.39497429839656</v>
+        <v>10.13350189839656</v>
       </c>
       <c r="N3">
-        <v>1418.305025701603</v>
+        <v>1418.566498101603</v>
       </c>
       <c r="O3">
-        <v>283.6610051403206</v>
+        <v>283.7132996203206</v>
       </c>
       <c r="P3">
-        <v>1134.644020561283</v>
+        <v>1134.853198481283</v>
       </c>
       <c r="Q3">
-        <v>1560.744020561282</v>
+        <v>1560.953198481282</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06765358291895368</v>
+        <v>0.06764223615484133</v>
       </c>
       <c r="T3">
         <v>0.4490993646954171</v>
       </c>
       <c r="U3">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>137.4414172645313</v>
+        <v>140.9877862879825</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06736621419303605</v>
+        <v>0.06733260340818099</v>
       </c>
       <c r="C4">
-        <v>18209.86615694351</v>
+        <v>18214.19397683635</v>
       </c>
       <c r="D4">
-        <v>13871.19815694351</v>
+        <v>13875.52597683635</v>
       </c>
       <c r="E4">
         <v>-5748.468</v>
@@ -1621,37 +1621,37 @@
         <v>1428.7</v>
       </c>
       <c r="M4">
-        <v>20.78994859679312</v>
+        <v>20.26700379679313</v>
       </c>
       <c r="N4">
-        <v>1407.910051403207</v>
+        <v>1408.432996203207</v>
       </c>
       <c r="O4">
-        <v>281.5820102806413</v>
+        <v>281.6865992406413</v>
       </c>
       <c r="P4">
-        <v>1126.328041122565</v>
+        <v>1126.746396962565</v>
       </c>
       <c r="Q4">
-        <v>1552.428041122565</v>
+        <v>1552.846396962565</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06783233702241737</v>
+        <v>0.06782089744603466</v>
       </c>
       <c r="T4">
         <v>0.4527728288866192</v>
       </c>
       <c r="U4">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>68.72070863226561</v>
+        <v>70.49389314399126</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06731011934077445</v>
+        <v>0.06726533106753557</v>
       </c>
       <c r="C5">
-        <v>18033.61965651811</v>
+        <v>18040.05350658744</v>
       </c>
       <c r="D5">
-        <v>13881.7176565181</v>
+        <v>13888.15150658744</v>
       </c>
       <c r="E5">
         <v>-5561.702</v>
@@ -1703,37 +1703,37 @@
         <v>1428.7</v>
       </c>
       <c r="M5">
-        <v>31.18492289518968</v>
+        <v>30.40050569518968</v>
       </c>
       <c r="N5">
-        <v>1397.51507710481</v>
+        <v>1398.29949430481</v>
       </c>
       <c r="O5">
-        <v>279.5030154209621</v>
+        <v>279.6598988609621</v>
       </c>
       <c r="P5">
-        <v>1118.012061683848</v>
+        <v>1118.639595443848</v>
       </c>
       <c r="Q5">
-        <v>1544.112061683848</v>
+        <v>1544.739595443848</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06801477677749887</v>
+        <v>0.06800324247519074</v>
       </c>
       <c r="T5">
         <v>0.4565220346075368</v>
       </c>
       <c r="U5">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.81380575484376</v>
+        <v>46.99592876266085</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06725402448851284</v>
+        <v>0.06719805872689015</v>
       </c>
       <c r="C6">
-        <v>17857.38912354625</v>
+        <v>17865.93603354638</v>
       </c>
       <c r="D6">
-        <v>13892.25312354625</v>
+        <v>13900.80003354638</v>
       </c>
       <c r="E6">
         <v>-5374.936</v>
@@ -1785,37 +1785,37 @@
         <v>1428.7</v>
       </c>
       <c r="M6">
-        <v>41.57989719358625</v>
+        <v>40.53400759358625</v>
       </c>
       <c r="N6">
-        <v>1387.120102806414</v>
+        <v>1388.165992406414</v>
       </c>
       <c r="O6">
-        <v>277.4240205612827</v>
+        <v>277.6331984812827</v>
       </c>
       <c r="P6">
-        <v>1109.696082245131</v>
+        <v>1110.532793925131</v>
       </c>
       <c r="Q6">
-        <v>1535.796082245131</v>
+        <v>1536.632793925131</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06820101736081123</v>
+        <v>0.06818938635912092</v>
       </c>
       <c r="T6">
         <v>0.4603493487809736</v>
       </c>
       <c r="U6">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.36035431613281</v>
+        <v>35.24694657199563</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06719792963625124</v>
+        <v>0.0671307863862447</v>
       </c>
       <c r="C7">
-        <v>17681.17459441083</v>
+        <v>17691.84162060404</v>
       </c>
       <c r="D7">
-        <v>13902.80459441083</v>
+        <v>13913.47162060404</v>
       </c>
       <c r="E7">
         <v>-5188.17</v>
@@ -1867,37 +1867,37 @@
         <v>1428.7</v>
       </c>
       <c r="M7">
-        <v>51.97487149198281</v>
+        <v>50.66750949198281</v>
       </c>
       <c r="N7">
-        <v>1376.725128508017</v>
+        <v>1378.032490508017</v>
       </c>
       <c r="O7">
-        <v>275.3450257016034</v>
+        <v>275.6064981016034</v>
       </c>
       <c r="P7">
-        <v>1101.380102806414</v>
+        <v>1102.425992406414</v>
       </c>
       <c r="Q7">
-        <v>1527.480102806413</v>
+        <v>1528.525992406413</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06839117879850912</v>
+        <v>0.06837944906166013</v>
       </c>
       <c r="T7">
         <v>0.4642572379896405</v>
       </c>
       <c r="U7">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.48828345290625</v>
+        <v>28.1975572575965</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06714183478398963</v>
+        <v>0.06706351404559928</v>
       </c>
       <c r="C8">
-        <v>17504.97610560536</v>
+        <v>17517.77033088081</v>
       </c>
       <c r="D8">
-        <v>13913.37210560537</v>
+        <v>13926.16633088081</v>
       </c>
       <c r="E8">
         <v>-5001.404</v>
@@ -1949,37 +1949,37 @@
         <v>1428.7</v>
       </c>
       <c r="M8">
-        <v>62.36984579037937</v>
+        <v>60.80101139037937</v>
       </c>
       <c r="N8">
-        <v>1366.330154209621</v>
+        <v>1367.89898860962</v>
       </c>
       <c r="O8">
-        <v>273.2660308419241</v>
+        <v>273.5797977219241</v>
       </c>
       <c r="P8">
-        <v>1093.064123367697</v>
+        <v>1094.319190887696</v>
       </c>
       <c r="Q8">
-        <v>1519.164123367696</v>
+        <v>1520.419190887696</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.06858538622424314</v>
+        <v>0.06857355565148744</v>
       </c>
       <c r="T8">
         <v>0.4682482737772155</v>
       </c>
       <c r="U8">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.90690287742188</v>
+        <v>23.49796438133042</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06708573993172803</v>
+        <v>0.06699624170495386</v>
       </c>
       <c r="C9">
-        <v>17328.7936937344</v>
+        <v>17343.72222772766</v>
       </c>
       <c r="D9">
-        <v>13923.9556937344</v>
+        <v>13938.88422772767</v>
       </c>
       <c r="E9">
         <v>-4814.638</v>
@@ -2031,37 +2031,37 @@
         <v>1428.7</v>
       </c>
       <c r="M9">
-        <v>72.76482008877595</v>
+        <v>70.93451328877595</v>
       </c>
       <c r="N9">
-        <v>1355.935179911224</v>
+        <v>1357.765486711224</v>
       </c>
       <c r="O9">
-        <v>271.1870359822448</v>
+        <v>271.5530973422448</v>
       </c>
       <c r="P9">
-        <v>1084.748143928979</v>
+        <v>1086.212389368979</v>
       </c>
       <c r="Q9">
-        <v>1510.848143928979</v>
+        <v>1512.312389368979</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.06878377015375638</v>
+        <v>0.06877183657657984</v>
       </c>
       <c r="T9">
         <v>0.4723251382914048</v>
       </c>
       <c r="U9">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.63448818064732</v>
+        <v>20.14111232685465</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06702964507946645</v>
+        <v>0.06692896936430842</v>
       </c>
       <c r="C10">
-        <v>17152.62739551395</v>
+        <v>17169.6973747272</v>
       </c>
       <c r="D10">
-        <v>13934.55539551396</v>
+        <v>13951.6253747272</v>
       </c>
       <c r="E10">
         <v>-4627.872</v>
@@ -2113,37 +2113,37 @@
         <v>1428.7</v>
       </c>
       <c r="M10">
-        <v>83.1597943871725</v>
+        <v>81.06801518717251</v>
       </c>
       <c r="N10">
-        <v>1345.540205612827</v>
+        <v>1347.631984812827</v>
       </c>
       <c r="O10">
-        <v>269.1080411225655</v>
+        <v>269.5263969625655</v>
       </c>
       <c r="P10">
-        <v>1076.432164490262</v>
+        <v>1078.105587850262</v>
       </c>
       <c r="Q10">
-        <v>1502.532164490262</v>
+        <v>1504.205587850262</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.06898646677738947</v>
+        <v>0.06897442795656554</v>
       </c>
       <c r="T10">
         <v>0.476490630295033</v>
       </c>
       <c r="U10">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.18017715806641</v>
+        <v>17.62347328599781</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06697355022720483</v>
+        <v>0.06686169702366299</v>
       </c>
       <c r="C11">
-        <v>16976.47724777193</v>
+        <v>16995.6958356947</v>
       </c>
       <c r="D11">
-        <v>13945.17124777193</v>
+        <v>13964.3898356947</v>
       </c>
       <c r="E11">
         <v>-4441.106</v>
@@ -2195,37 +2195,37 @@
         <v>1428.7</v>
       </c>
       <c r="M11">
-        <v>93.55476868556906</v>
+        <v>91.20151708556905</v>
       </c>
       <c r="N11">
-        <v>1335.145231314431</v>
+        <v>1337.498482914431</v>
       </c>
       <c r="O11">
-        <v>267.0290462628861</v>
+        <v>267.4996965828861</v>
       </c>
       <c r="P11">
-        <v>1068.116185051545</v>
+        <v>1069.998786331545</v>
       </c>
       <c r="Q11">
-        <v>1494.216185051544</v>
+        <v>1496.098786331544</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.06919361827187163</v>
+        <v>0.06918147189435314</v>
       </c>
       <c r="T11">
         <v>0.4807476715734662</v>
       </c>
       <c r="U11">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.27126858494792</v>
+        <v>15.66530958755362</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06691745537494322</v>
+        <v>0.06679442468301758</v>
       </c>
       <c r="C12">
-        <v>16800.34328744853</v>
+        <v>16821.71767467922</v>
       </c>
       <c r="D12">
-        <v>13955.80328744853</v>
+        <v>13977.17767467922</v>
       </c>
       <c r="E12">
         <v>-4254.34</v>
@@ -2277,37 +2277,37 @@
         <v>1428.7</v>
       </c>
       <c r="M12">
-        <v>103.9497429839656</v>
+        <v>101.3350189839656</v>
       </c>
       <c r="N12">
-        <v>1324.750257016034</v>
+        <v>1327.364981016034</v>
       </c>
       <c r="O12">
-        <v>264.9500514032068</v>
+        <v>265.4729962032068</v>
       </c>
       <c r="P12">
-        <v>1059.800205612827</v>
+        <v>1061.891984812827</v>
       </c>
       <c r="Q12">
-        <v>1485.900205612827</v>
+        <v>1487.991984812827</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.06940537313289785</v>
+        <v>0.06939311680853602</v>
       </c>
       <c r="T12">
         <v>0.485099313769198</v>
       </c>
       <c r="U12">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.74414172645312</v>
+        <v>14.09877862879825</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06686136052268161</v>
+        <v>0.06672715234237214</v>
       </c>
       <c r="C13">
-        <v>16624.22555159671</v>
+        <v>16647.76295596462</v>
       </c>
       <c r="D13">
-        <v>13966.45155159671</v>
+        <v>13989.98895596462</v>
       </c>
       <c r="E13">
         <v>-4067.574</v>
@@ -2359,37 +2359,37 @@
         <v>1428.7</v>
       </c>
       <c r="M13">
-        <v>114.3447172823622</v>
+        <v>111.4685208823622</v>
       </c>
       <c r="N13">
-        <v>1314.355282717638</v>
+        <v>1317.231479117638</v>
       </c>
       <c r="O13">
-        <v>262.8710565435276</v>
+        <v>263.4462958235276</v>
       </c>
       <c r="P13">
-        <v>1051.48422617411</v>
+        <v>1053.78518329411</v>
       </c>
       <c r="Q13">
-        <v>1477.58422617411</v>
+        <v>1479.88518329411</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.06962188653012691</v>
+        <v>0.06960951778820615</v>
       </c>
       <c r="T13">
         <v>0.4895487456771933</v>
       </c>
       <c r="U13">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.49467429677557</v>
+        <v>12.81707148072569</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06680526567042003</v>
+        <v>0.06665988000172671</v>
       </c>
       <c r="C14">
-        <v>16448.12407738259</v>
+        <v>16473.83174407067</v>
       </c>
       <c r="D14">
-        <v>13977.11607738259</v>
+        <v>14002.82374407067</v>
       </c>
       <c r="E14">
         <v>-3880.808</v>
@@ -2441,37 +2441,37 @@
         <v>1428.7</v>
       </c>
       <c r="M14">
-        <v>124.7396915807587</v>
+        <v>121.6020227807587</v>
       </c>
       <c r="N14">
-        <v>1303.960308419241</v>
+        <v>1307.097977219241</v>
       </c>
       <c r="O14">
-        <v>260.7920616838482</v>
+        <v>261.4195954438482</v>
       </c>
       <c r="P14">
-        <v>1043.168246735393</v>
+        <v>1045.678381775393</v>
       </c>
       <c r="Q14">
-        <v>1469.268246735393</v>
+        <v>1471.778381775393</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.06984332068638391</v>
+        <v>0.06983083697195969</v>
       </c>
       <c r="T14">
         <v>0.4940993010376432</v>
       </c>
       <c r="U14">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.45345143871094</v>
+        <v>11.74898219066521</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06674917081815841</v>
+        <v>0.06659260766108129</v>
       </c>
       <c r="C15">
-        <v>16272.03890208591</v>
+        <v>16299.92410375413</v>
       </c>
       <c r="D15">
-        <v>13987.79690208591</v>
+        <v>14015.68210375413</v>
       </c>
       <c r="E15">
         <v>-3694.042</v>
@@ -2523,37 +2523,37 @@
         <v>1428.7</v>
       </c>
       <c r="M15">
-        <v>135.1346658791553</v>
+        <v>131.7355246791553</v>
       </c>
       <c r="N15">
-        <v>1293.565334120844</v>
+        <v>1296.964475320844</v>
       </c>
       <c r="O15">
-        <v>258.7130668241689</v>
+        <v>259.3928950641689</v>
       </c>
       <c r="P15">
-        <v>1034.852267296676</v>
+        <v>1037.571580256676</v>
       </c>
       <c r="Q15">
-        <v>1460.952267296675</v>
+        <v>1463.671580256675</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07006984528301462</v>
+        <v>0.0700572439530409</v>
       </c>
       <c r="T15">
         <v>0.4987544668661493</v>
       </c>
       <c r="U15">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.57241671265625</v>
+        <v>10.84521432984481</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06669307596589681</v>
+        <v>0.06652533532043585</v>
       </c>
       <c r="C16">
-        <v>16095.97006310043</v>
+        <v>16126.04010000984</v>
       </c>
       <c r="D16">
-        <v>13998.49406310043</v>
+        <v>14028.56410000984</v>
       </c>
       <c r="E16">
         <v>-3507.276</v>
@@ -2605,37 +2605,37 @@
         <v>1428.7</v>
       </c>
       <c r="M16">
-        <v>145.5296401775519</v>
+        <v>141.8690265775519</v>
       </c>
       <c r="N16">
-        <v>1283.170359822448</v>
+        <v>1286.830973422448</v>
       </c>
       <c r="O16">
-        <v>256.6340719644896</v>
+        <v>257.3661946844896</v>
       </c>
       <c r="P16">
-        <v>1026.536287857958</v>
+        <v>1029.464778737958</v>
       </c>
       <c r="Q16">
-        <v>1452.636287857958</v>
+        <v>1455.564778737958</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07030163789352047</v>
+        <v>0.07028891621275191</v>
       </c>
       <c r="T16">
         <v>0.5035178923650859</v>
       </c>
       <c r="U16">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.817244090323658</v>
+        <v>10.07055616342732</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0666369811136352</v>
+        <v>0.06645806297979043</v>
       </c>
       <c r="C17">
-        <v>15919.9175979344</v>
+        <v>15952.17979807179</v>
       </c>
       <c r="D17">
-        <v>14009.2075979344</v>
+        <v>14041.46979807179</v>
       </c>
       <c r="E17">
         <v>-3320.51</v>
@@ -2687,37 +2687,37 @@
         <v>1428.7</v>
       </c>
       <c r="M17">
-        <v>155.9246144759484</v>
+        <v>152.0025284759484</v>
       </c>
       <c r="N17">
-        <v>1272.775385524051</v>
+        <v>1276.697471524051</v>
       </c>
       <c r="O17">
-        <v>254.5550771048103</v>
+        <v>255.3394943048103</v>
       </c>
       <c r="P17">
-        <v>1018.220308419241</v>
+        <v>1021.357977219241</v>
       </c>
       <c r="Q17">
-        <v>1444.320308419241</v>
+        <v>1447.457977219241</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07053888444780292</v>
+        <v>0.07052603958445611</v>
       </c>
       <c r="T17">
         <v>0.5083933984639973</v>
       </c>
       <c r="U17">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.16276115096875</v>
+        <v>9.399185752532171</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06672168626137361</v>
+        <v>0.06639079063914499</v>
       </c>
       <c r="C18">
-        <v>15716.98010114493</v>
+        <v>15778.34326341427</v>
       </c>
       <c r="D18">
-        <v>13993.03610114492</v>
+        <v>14054.39926341427</v>
       </c>
       <c r="E18">
         <v>-3133.744</v>
@@ -2769,45 +2769,45 @@
         <v>1428.7</v>
       </c>
       <c r="M18">
-        <v>169.606670374345</v>
+        <v>162.136030374345</v>
       </c>
       <c r="N18">
-        <v>1259.093329625655</v>
+        <v>1266.563969625655</v>
       </c>
       <c r="O18">
-        <v>251.818665925131</v>
+        <v>253.312793925131</v>
       </c>
       <c r="P18">
-        <v>1007.274663700524</v>
+        <v>1013.251175700524</v>
       </c>
       <c r="Q18">
-        <v>1433.374663700524</v>
+        <v>1439.351175700524</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07078177972956828</v>
+        <v>0.07076880875072471</v>
       </c>
       <c r="T18">
         <v>0.5133849880414544</v>
       </c>
       <c r="U18">
-        <v>0.0567577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04540619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.423607378451948</v>
+        <v>8.811736642998909</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06667439140911199</v>
+        <v>0.06652751829849957</v>
       </c>
       <c r="C19">
-        <v>15539.23879910657</v>
+        <v>15565.32370930132</v>
       </c>
       <c r="D19">
-        <v>14002.06079910658</v>
+        <v>14028.14570930132</v>
       </c>
       <c r="E19">
         <v>-2946.978</v>
@@ -2851,37 +2851,37 @@
         <v>1428.7</v>
       </c>
       <c r="M19">
-        <v>180.2070872727415</v>
+        <v>177.0320652727416</v>
       </c>
       <c r="N19">
-        <v>1248.492912727258</v>
+        <v>1251.667934727258</v>
       </c>
       <c r="O19">
-        <v>249.6985825454517</v>
+        <v>250.3335869454517</v>
       </c>
       <c r="P19">
-        <v>998.7943301818066</v>
+        <v>1001.334347781807</v>
       </c>
       <c r="Q19">
-        <v>1424.894330181807</v>
+        <v>1427.434347781807</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07103052790968944</v>
+        <v>0.07101742777642145</v>
       </c>
       <c r="T19">
         <v>0.5184968568858381</v>
       </c>
       <c r="U19">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.928101062072422</v>
+        <v>8.070289400956241</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.0666270965568504</v>
+        <v>0.06647224595785413</v>
       </c>
       <c r="C20">
-        <v>15361.50914539586</v>
+        <v>15389.15892424694</v>
       </c>
       <c r="D20">
-        <v>14011.09714539586</v>
+        <v>14038.74692424694</v>
       </c>
       <c r="E20">
         <v>-2760.212</v>
@@ -2933,37 +2933,37 @@
         <v>1428.7</v>
       </c>
       <c r="M20">
-        <v>190.8075041711381</v>
+        <v>187.4457161711381</v>
       </c>
       <c r="N20">
-        <v>1237.892495828862</v>
+        <v>1241.254283828862</v>
       </c>
       <c r="O20">
-        <v>247.5784991657723</v>
+        <v>248.2508567657724</v>
       </c>
       <c r="P20">
-        <v>990.3139966630894</v>
+        <v>993.0034270630895</v>
       </c>
       <c r="Q20">
-        <v>1416.413996663089</v>
+        <v>1419.103427063089</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07128534311859405</v>
+        <v>0.07127211068079373</v>
       </c>
       <c r="T20">
         <v>0.5237334054581335</v>
       </c>
       <c r="U20">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.487651003068398</v>
+        <v>7.621939989792009</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06657980170458881</v>
+        <v>0.06641697361720872</v>
       </c>
       <c r="C21">
-        <v>15183.79116257939</v>
+        <v>15213.01017420616</v>
       </c>
       <c r="D21">
-        <v>14020.14516257939</v>
+        <v>14049.36417420616</v>
       </c>
       <c r="E21">
         <v>-2573.446</v>
@@ -3015,37 +3015,37 @@
         <v>1428.7</v>
       </c>
       <c r="M21">
-        <v>201.4079210695347</v>
+        <v>197.8593670695347</v>
       </c>
       <c r="N21">
-        <v>1227.292078930465</v>
+        <v>1230.840632930465</v>
       </c>
       <c r="O21">
-        <v>245.458415786093</v>
+        <v>246.168126586093</v>
       </c>
       <c r="P21">
-        <v>981.8336631443721</v>
+        <v>984.6725063443721</v>
       </c>
       <c r="Q21">
-        <v>1407.933663144372</v>
+        <v>1410.772506344372</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07154645006105187</v>
+        <v>0.07153308205194064</v>
       </c>
       <c r="T21">
         <v>0.5290992515260414</v>
       </c>
       <c r="U21">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.093564108170061</v>
+        <v>7.220785253487164</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06688450685232719</v>
+        <v>0.0663617012765633</v>
       </c>
       <c r="C22">
-        <v>14938.93580678956</v>
+        <v>15036.87749558748</v>
       </c>
       <c r="D22">
-        <v>13962.05580678956</v>
+        <v>14059.99749558748</v>
       </c>
       <c r="E22">
         <v>-2386.68</v>
@@ -3097,45 +3097,45 @@
         <v>1428.7</v>
       </c>
       <c r="M22">
-        <v>220.2260419679312</v>
+        <v>208.2730179679312</v>
       </c>
       <c r="N22">
-        <v>1208.473958032069</v>
+        <v>1220.426982032069</v>
       </c>
       <c r="O22">
-        <v>241.6947916064137</v>
+        <v>244.0853964064137</v>
       </c>
       <c r="P22">
-        <v>966.7791664256549</v>
+        <v>976.3415856256548</v>
       </c>
       <c r="Q22">
-        <v>1392.879166425655</v>
+        <v>1402.441585625655</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07181408467707111</v>
+        <v>0.07180057770736623</v>
       </c>
       <c r="T22">
         <v>0.5345992437456467</v>
       </c>
       <c r="U22">
-        <v>0.0589577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04716619555335153</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.487425316430305</v>
+        <v>6.859745990812806</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06685481200006559</v>
+        <v>0.06659202893591787</v>
       </c>
       <c r="C23">
-        <v>14757.8096910564</v>
+        <v>14805.90682308299</v>
       </c>
       <c r="D23">
-        <v>13967.6956910564</v>
+        <v>14015.79282308299</v>
       </c>
       <c r="E23">
         <v>-2199.914000000001</v>
@@ -3179,37 +3179,37 @@
         <v>1428.7</v>
       </c>
       <c r="M23">
-        <v>231.2373440663278</v>
+        <v>225.3542150663278</v>
       </c>
       <c r="N23">
-        <v>1197.462655933672</v>
+        <v>1203.345784933672</v>
       </c>
       <c r="O23">
-        <v>239.4925311867344</v>
+        <v>240.6691569867344</v>
       </c>
       <c r="P23">
-        <v>957.9701247469377</v>
+        <v>962.6766279469377</v>
       </c>
       <c r="Q23">
-        <v>1384.070124746938</v>
+        <v>1388.776627946938</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07208849485298958</v>
+        <v>0.07207484540470131</v>
       </c>
       <c r="T23">
         <v>0.5402384762746093</v>
       </c>
       <c r="U23">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.178500301362195</v>
+        <v>6.339797103770592</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06682511714780398</v>
+        <v>0.06655035659527243</v>
       </c>
       <c r="C24">
-        <v>14576.68813355578</v>
+        <v>14627.11800534611</v>
       </c>
       <c r="D24">
-        <v>13973.34013355578</v>
+        <v>14023.77000534611</v>
       </c>
       <c r="E24">
         <v>-2013.148</v>
@@ -3261,37 +3261,37 @@
         <v>1428.7</v>
       </c>
       <c r="M24">
-        <v>242.2486461647244</v>
+        <v>236.0853681647244</v>
       </c>
       <c r="N24">
-        <v>1186.451353835276</v>
+        <v>1192.614631835276</v>
       </c>
       <c r="O24">
-        <v>237.2902707670551</v>
+        <v>238.5229263670551</v>
       </c>
       <c r="P24">
-        <v>949.1610830682205</v>
+        <v>954.0917054682204</v>
       </c>
       <c r="Q24">
-        <v>1375.261083068221</v>
+        <v>1380.19170546822</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07236994118726493</v>
+        <v>0.07235614560709627</v>
       </c>
       <c r="T24">
         <v>0.5460223045094427</v>
       </c>
       <c r="U24">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.897659378573004</v>
+        <v>6.051624508144655</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06679542229554239</v>
+        <v>0.066508684254627</v>
       </c>
       <c r="C25">
-        <v>14395.57113981596</v>
+        <v>14448.33827331373</v>
       </c>
       <c r="D25">
-        <v>13978.98913981596</v>
+        <v>14031.75627331373</v>
       </c>
       <c r="E25">
         <v>-1826.382000000001</v>
@@ -3343,37 +3343,37 @@
         <v>1428.7</v>
       </c>
       <c r="M25">
-        <v>253.2599482631209</v>
+        <v>246.8165212631209</v>
       </c>
       <c r="N25">
-        <v>1175.440051736879</v>
+        <v>1181.883478736879</v>
       </c>
       <c r="O25">
-        <v>235.0880103473758</v>
+        <v>236.3766957473758</v>
       </c>
       <c r="P25">
-        <v>940.3520413895033</v>
+        <v>945.5067829895031</v>
       </c>
       <c r="Q25">
-        <v>1366.452041389503</v>
+        <v>1371.606782989503</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07265869781593705</v>
+        <v>0.07264475230825473</v>
       </c>
       <c r="T25">
         <v>0.5519563620490768</v>
       </c>
       <c r="U25">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.64123940559157</v>
+        <v>5.788510399094887</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06705372744328078</v>
+        <v>0.06662061191398157</v>
       </c>
       <c r="C26">
-        <v>14159.81880779595</v>
+        <v>14240.1425342802</v>
       </c>
       <c r="D26">
-        <v>13930.00280779594</v>
+        <v>14010.3265342802</v>
       </c>
       <c r="E26">
         <v>-1639.616000000001</v>
@@ -3425,37 +3425,37 @@
         <v>1428.7</v>
       </c>
       <c r="M26">
-        <v>270.9948263615174</v>
+        <v>261.1335815615175</v>
       </c>
       <c r="N26">
-        <v>1157.705173638482</v>
+        <v>1167.566418438482</v>
       </c>
       <c r="O26">
-        <v>231.5410347276965</v>
+        <v>233.5132836876965</v>
       </c>
       <c r="P26">
-        <v>926.1641389107859</v>
+        <v>934.0531347507858</v>
       </c>
       <c r="Q26">
-        <v>1352.264138910786</v>
+        <v>1360.153134750786</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07295505330325844</v>
+        <v>0.07294095392260158</v>
       </c>
       <c r="T26">
         <v>0.5580465789976488</v>
       </c>
       <c r="U26">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.272056367947259</v>
+        <v>5.47114619060754</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06703603259101917</v>
+        <v>0.06658533957333615</v>
       </c>
       <c r="C27">
-        <v>13976.39759509579</v>
+        <v>14060.12273152385</v>
       </c>
       <c r="D27">
-        <v>13933.34759509579</v>
+        <v>14017.07273152385</v>
       </c>
       <c r="E27">
         <v>-1452.85</v>
@@ -3507,37 +3507,37 @@
         <v>1428.7</v>
       </c>
       <c r="M27">
-        <v>282.2862774599141</v>
+        <v>272.0141474599141</v>
       </c>
       <c r="N27">
-        <v>1146.413722540086</v>
+        <v>1156.685852540086</v>
       </c>
       <c r="O27">
-        <v>229.2827445080171</v>
+        <v>231.3371705080172</v>
       </c>
       <c r="P27">
-        <v>917.1309780320686</v>
+        <v>925.3486820320686</v>
       </c>
       <c r="Q27">
-        <v>1343.230978032069</v>
+        <v>1351.448682032069</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07325931160357506</v>
+        <v>0.07324505424666435</v>
       </c>
       <c r="T27">
         <v>0.5642992017315159</v>
       </c>
       <c r="U27">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.061174113229367</v>
+        <v>5.252300342983238</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06701833773875757</v>
+        <v>0.0665500672326907</v>
       </c>
       <c r="C28">
-        <v>13792.97798904126</v>
+        <v>13880.10942870198</v>
       </c>
       <c r="D28">
-        <v>13936.69398904126</v>
+        <v>14023.82542870198</v>
       </c>
       <c r="E28">
         <v>-1266.084</v>
@@ -3589,37 +3589,37 @@
         <v>1428.7</v>
       </c>
       <c r="M28">
-        <v>293.5777285583106</v>
+        <v>282.8947133583106</v>
       </c>
       <c r="N28">
-        <v>1135.122271441689</v>
+        <v>1145.805286641689</v>
       </c>
       <c r="O28">
-        <v>227.0244542883379</v>
+        <v>229.1610573283378</v>
       </c>
       <c r="P28">
-        <v>908.0978171533513</v>
+        <v>916.6442293133514</v>
       </c>
       <c r="Q28">
-        <v>1334.197817153351</v>
+        <v>1342.744229313351</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07357179310119753</v>
+        <v>0.07355737349840448</v>
       </c>
       <c r="T28">
         <v>0.5707208142690012</v>
       </c>
       <c r="U28">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.866513570412854</v>
+        <v>5.050288791330037</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06700064288649597</v>
+        <v>0.06651479489204529</v>
       </c>
       <c r="C29">
-        <v>13609.55999079024</v>
+        <v>13700.10263521309</v>
       </c>
       <c r="D29">
-        <v>13940.04199079024</v>
+        <v>14030.58463521309</v>
       </c>
       <c r="E29">
         <v>-1079.318</v>
@@ -3671,37 +3671,37 @@
         <v>1428.7</v>
       </c>
       <c r="M29">
-        <v>304.8691796567072</v>
+        <v>293.7752792567072</v>
       </c>
       <c r="N29">
-        <v>1123.830820343293</v>
+        <v>1134.924720743293</v>
       </c>
       <c r="O29">
-        <v>224.7661640686585</v>
+        <v>226.9849441486585</v>
       </c>
       <c r="P29">
-        <v>899.064656274634</v>
+        <v>907.9397765946342</v>
       </c>
       <c r="Q29">
-        <v>1325.164656274634</v>
+        <v>1334.039776594634</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07389283573574118</v>
+        <v>0.07387824944197312</v>
       </c>
       <c r="T29">
         <v>0.5773183613965547</v>
       </c>
       <c r="U29">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.686272327064229</v>
+        <v>4.863241058317814</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06698294803423437</v>
+        <v>0.06647952255139986</v>
       </c>
       <c r="C30">
-        <v>13426.14360150175</v>
+        <v>13520.10236047384</v>
       </c>
       <c r="D30">
-        <v>13943.39160150175</v>
+        <v>14037.35036047384</v>
       </c>
       <c r="E30">
         <v>-892.5519999999997</v>
@@ -3753,37 +3753,37 @@
         <v>1428.7</v>
       </c>
       <c r="M30">
-        <v>316.1606307551038</v>
+        <v>304.6558451551037</v>
       </c>
       <c r="N30">
-        <v>1112.539369244896</v>
+        <v>1124.044154844896</v>
       </c>
       <c r="O30">
-        <v>222.5078738489792</v>
+        <v>224.8088309689792</v>
       </c>
       <c r="P30">
-        <v>890.0314953959169</v>
+        <v>899.2353238759169</v>
       </c>
       <c r="Q30">
-        <v>1316.131495395917</v>
+        <v>1325.335323875917</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07422279622124436</v>
+        <v>0.07420803860619643</v>
       </c>
       <c r="T30">
         <v>0.5840991737220955</v>
       </c>
       <c r="U30">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.518905458240507</v>
+        <v>4.689553877663606</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06696525318197276</v>
+        <v>0.06644425021075442</v>
       </c>
       <c r="C31">
-        <v>13242.72882233588</v>
+        <v>13340.10861391904</v>
       </c>
       <c r="D31">
-        <v>13946.74282233588</v>
+        <v>14044.12261391904</v>
       </c>
       <c r="E31">
         <v>-705.786000000001</v>
@@ -3835,37 +3835,37 @@
         <v>1428.7</v>
       </c>
       <c r="M31">
-        <v>327.4520818535003</v>
+        <v>315.5364110535003</v>
       </c>
       <c r="N31">
-        <v>1101.2479181465</v>
+        <v>1113.1635889465</v>
       </c>
       <c r="O31">
-        <v>220.2495836292999</v>
+        <v>222.6327177892999</v>
       </c>
       <c r="P31">
-        <v>880.9983345171997</v>
+        <v>890.5308711571997</v>
       </c>
       <c r="Q31">
-        <v>1307.0983345172</v>
+        <v>1316.6308711572</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07456205136831101</v>
+        <v>0.07454711760603167</v>
       </c>
       <c r="T31">
         <v>0.591070994845539</v>
       </c>
       <c r="U31">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.363081132094283</v>
+        <v>4.527845123261413</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06728355832971117</v>
+        <v>0.06640897787010899</v>
       </c>
       <c r="C32">
-        <v>12995.92422610823</v>
+        <v>13160.12140500173</v>
       </c>
       <c r="D32">
-        <v>13886.70422610823</v>
+        <v>14050.90140500173</v>
       </c>
       <c r="E32">
         <v>-519.0200000000004</v>
@@ -3917,45 +3917,45 @@
         <v>1428.7</v>
       </c>
       <c r="M32">
-        <v>346.5877049518969</v>
+        <v>326.4169769518969</v>
       </c>
       <c r="N32">
-        <v>1082.112295048103</v>
+        <v>1102.283023048103</v>
       </c>
       <c r="O32">
-        <v>216.4224590096206</v>
+        <v>220.4566046096206</v>
       </c>
       <c r="P32">
-        <v>865.6898360384824</v>
+        <v>881.8264184384823</v>
       </c>
       <c r="Q32">
-        <v>1291.789836038482</v>
+        <v>1307.926418438482</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07491099951957958</v>
+        <v>0.07489588457729077</v>
       </c>
       <c r="T32">
         <v>0.5982420108582238</v>
       </c>
       <c r="U32">
-        <v>0.0618577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04948619555335152</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.122188928191466</v>
+        <v>4.376916952486033</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06727706347744955</v>
+        <v>0.06662170552946356</v>
       </c>
       <c r="C33">
-        <v>12810.37811614983</v>
+        <v>12932.57147288012</v>
       </c>
       <c r="D33">
-        <v>13887.92411614983</v>
+        <v>14010.11747288012</v>
       </c>
       <c r="E33">
         <v>-332.2540000000008</v>
@@ -3999,37 +3999,37 @@
         <v>1428.7</v>
       </c>
       <c r="M33">
-        <v>358.1406284502934</v>
+        <v>343.0872888502934</v>
       </c>
       <c r="N33">
-        <v>1070.559371549706</v>
+        <v>1085.612711149706</v>
       </c>
       <c r="O33">
-        <v>214.1118743099413</v>
+        <v>217.1225422299413</v>
       </c>
       <c r="P33">
-        <v>856.4474972397651</v>
+        <v>868.4901689197652</v>
       </c>
       <c r="Q33">
-        <v>1282.547497239765</v>
+        <v>1294.590168919765</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07527006211001533</v>
+        <v>0.0752547607361226</v>
       </c>
       <c r="T33">
         <v>0.605620882407508</v>
       </c>
       <c r="U33">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.989215091798193</v>
+        <v>4.164246378196236</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06727056862518795</v>
+        <v>0.06659443318881814</v>
       </c>
       <c r="C34">
-        <v>12624.83222053494</v>
+        <v>12751.02086272307</v>
       </c>
       <c r="D34">
-        <v>13889.14422053494</v>
+        <v>14015.33286272307</v>
       </c>
       <c r="E34">
         <v>-145.4880000000003</v>
@@ -4081,37 +4081,37 @@
         <v>1428.7</v>
       </c>
       <c r="M34">
-        <v>369.69355194869</v>
+        <v>354.15462074869</v>
       </c>
       <c r="N34">
-        <v>1059.00644805131</v>
+        <v>1074.54537925131</v>
       </c>
       <c r="O34">
-        <v>211.801289610262</v>
+        <v>214.909075850262</v>
       </c>
       <c r="P34">
-        <v>847.205158441048</v>
+        <v>859.6363034010479</v>
       </c>
       <c r="Q34">
-        <v>1273.305158441048</v>
+        <v>1285.736303401048</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07563968536487568</v>
+        <v>0.07562419207609655</v>
       </c>
       <c r="T34">
         <v>0.6132167795905947</v>
       </c>
       <c r="U34">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.8645521201795</v>
+        <v>4.034113678877603</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06726407377292634</v>
+        <v>0.06656716084817271</v>
       </c>
       <c r="C35">
-        <v>12439.28653932006</v>
+        <v>12569.4741369618</v>
       </c>
       <c r="D35">
-        <v>13890.36453932006</v>
+        <v>14020.5521369618</v>
       </c>
       <c r="E35">
         <v>41.27800000000025</v>
@@ -4163,37 +4163,37 @@
         <v>1428.7</v>
       </c>
       <c r="M35">
-        <v>381.2464754470866</v>
+        <v>365.2219526470866</v>
       </c>
       <c r="N35">
-        <v>1047.453524552913</v>
+        <v>1063.478047352913</v>
       </c>
       <c r="O35">
-        <v>209.4907049105827</v>
+        <v>212.6956094705826</v>
       </c>
       <c r="P35">
-        <v>837.9628196423306</v>
+        <v>850.7824378823304</v>
       </c>
       <c r="Q35">
-        <v>1264.062819642331</v>
+        <v>1276.882437882331</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07602034214973186</v>
+        <v>0.07600465121726374</v>
       </c>
       <c r="T35">
         <v>0.6210394199731767</v>
       </c>
       <c r="U35">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.74744448017406</v>
+        <v>3.911867809820705</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06725757892066475</v>
+        <v>0.06653988850752728</v>
       </c>
       <c r="C36">
-        <v>12253.7410725617</v>
+        <v>12387.93129993754</v>
       </c>
       <c r="D36">
-        <v>13891.5850725617</v>
+        <v>14025.77529993754</v>
       </c>
       <c r="E36">
         <v>228.0439999999999</v>
@@ -4245,37 +4245,37 @@
         <v>1428.7</v>
       </c>
       <c r="M36">
-        <v>392.7993989454831</v>
+        <v>376.2892845454831</v>
       </c>
       <c r="N36">
-        <v>1035.900601054517</v>
+        <v>1052.410715454517</v>
       </c>
       <c r="O36">
-        <v>207.1801202109034</v>
+        <v>210.4821430909034</v>
       </c>
       <c r="P36">
-        <v>828.7204808436134</v>
+        <v>841.9285723636134</v>
       </c>
       <c r="Q36">
-        <v>1254.820480843613</v>
+        <v>1268.028572363613</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07641253398867459</v>
+        <v>0.07639663942331479</v>
       </c>
       <c r="T36">
         <v>0.6290991100643216</v>
       </c>
       <c r="U36">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.637225524874823</v>
+        <v>3.796812874237744</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06725108406840313</v>
+        <v>0.06651261616688185</v>
       </c>
       <c r="C37">
-        <v>12068.1958203164</v>
+        <v>12206.39235599798</v>
       </c>
       <c r="D37">
-        <v>13892.8058203164</v>
+        <v>14031.00235599799</v>
       </c>
       <c r="E37">
         <v>414.8100000000004</v>
@@ -4327,37 +4327,37 @@
         <v>1428.7</v>
       </c>
       <c r="M37">
-        <v>404.3523224438797</v>
+        <v>387.3566164438797</v>
       </c>
       <c r="N37">
-        <v>1024.34767755612</v>
+        <v>1041.34338355612</v>
       </c>
       <c r="O37">
-        <v>204.869535511224</v>
+        <v>208.268676711224</v>
       </c>
       <c r="P37">
-        <v>819.478142044896</v>
+        <v>833.074706844896</v>
       </c>
       <c r="Q37">
-        <v>1245.578142044896</v>
+        <v>1259.174706844896</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07681679326881555</v>
+        <v>0.07680068880493665</v>
       </c>
       <c r="T37">
         <v>0.6374067906198095</v>
       </c>
       <c r="U37">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.533304795592685</v>
+        <v>3.688332506402379</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06724458921614154</v>
+        <v>0.06648534382623643</v>
       </c>
       <c r="C38">
-        <v>11882.65078264072</v>
+        <v>12024.85730949733</v>
       </c>
       <c r="D38">
-        <v>13894.02678264071</v>
+        <v>14036.23330949733</v>
       </c>
       <c r="E38">
         <v>601.5759999999991</v>
@@ -4409,37 +4409,37 @@
         <v>1428.7</v>
       </c>
       <c r="M38">
-        <v>415.9052459422762</v>
+        <v>398.4239483422762</v>
       </c>
       <c r="N38">
-        <v>1012.794754057724</v>
+        <v>1030.276051657724</v>
       </c>
       <c r="O38">
-        <v>202.5589508115447</v>
+        <v>206.0552103315447</v>
       </c>
       <c r="P38">
-        <v>810.2358032461789</v>
+        <v>824.220841326179</v>
       </c>
       <c r="Q38">
-        <v>1236.335803246179</v>
+        <v>1250.320841326179</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.07723368565146092</v>
+        <v>0.07721736472973419</v>
       </c>
       <c r="T38">
         <v>0.6459740861926565</v>
       </c>
       <c r="U38">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.435157440159556</v>
+        <v>3.58587882566898</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.06723809436387994</v>
+        <v>0.06645807148559099</v>
       </c>
       <c r="C39">
-        <v>11697.10595959123</v>
+        <v>11843.32616479626</v>
       </c>
       <c r="D39">
-        <v>13895.24795959123</v>
+        <v>14041.46816479626</v>
       </c>
       <c r="E39">
         <v>788.3419999999996</v>
@@ -4491,37 +4491,37 @@
         <v>1428.7</v>
       </c>
       <c r="M39">
-        <v>427.4581694406728</v>
+        <v>409.4912802406728</v>
       </c>
       <c r="N39">
-        <v>1001.241830559327</v>
+        <v>1019.208719759327</v>
       </c>
       <c r="O39">
-        <v>200.2483661118654</v>
+        <v>203.8417439518654</v>
       </c>
       <c r="P39">
-        <v>800.9934644474616</v>
+        <v>815.3669758074617</v>
       </c>
       <c r="Q39">
-        <v>1227.093464447462</v>
+        <v>1241.466975807462</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.07766381271292043</v>
+        <v>0.07764726846166815</v>
       </c>
       <c r="T39">
         <v>0.6548133594027367</v>
       </c>
       <c r="U39">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.34231534718227</v>
+        <v>3.488963181731981</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06723159951161833</v>
+        <v>0.06643079914494557</v>
       </c>
       <c r="C40">
-        <v>11511.56135122453</v>
+        <v>11661.79892626197</v>
       </c>
       <c r="D40">
-        <v>13896.46935122453</v>
+        <v>14046.70692626197</v>
       </c>
       <c r="E40">
         <v>975.1079999999993</v>
@@ -4573,37 +4573,37 @@
         <v>1428.7</v>
       </c>
       <c r="M40">
-        <v>439.0110929390693</v>
+        <v>420.5586121390693</v>
       </c>
       <c r="N40">
-        <v>989.6889070609304</v>
+        <v>1008.141387860931</v>
       </c>
       <c r="O40">
-        <v>197.9377814121861</v>
+        <v>201.6282775721861</v>
       </c>
       <c r="P40">
-        <v>791.7511256487444</v>
+        <v>806.5131102887444</v>
       </c>
       <c r="Q40">
-        <v>1217.851125648745</v>
+        <v>1232.613110288744</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.07810781484087863</v>
+        <v>0.07809104005592256</v>
       </c>
       <c r="T40">
         <v>0.6639377704583032</v>
       </c>
       <c r="U40">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.254359680151158</v>
+        <v>3.397148361160086</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06722510465935673</v>
+        <v>0.06640352680430014</v>
       </c>
       <c r="C41">
-        <v>11326.01695759724</v>
+        <v>11480.27559826816</v>
       </c>
       <c r="D41">
-        <v>13897.69095759724</v>
+        <v>14051.94959826816</v>
       </c>
       <c r="E41">
         <v>1161.874</v>
@@ -4655,37 +4655,37 @@
         <v>1428.7</v>
       </c>
       <c r="M41">
-        <v>450.5640164374659</v>
+        <v>431.625944037466</v>
       </c>
       <c r="N41">
-        <v>978.135983562534</v>
+        <v>997.0740559625339</v>
       </c>
       <c r="O41">
-        <v>195.6271967125068</v>
+        <v>199.4148111925068</v>
       </c>
       <c r="P41">
-        <v>782.5087868500271</v>
+        <v>797.659244770027</v>
       </c>
       <c r="Q41">
-        <v>1208.608786850027</v>
+        <v>1223.759244770027</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.07856637441565514</v>
+        <v>0.07854936153851319</v>
       </c>
       <c r="T41">
         <v>0.6733613425320851</v>
       </c>
       <c r="U41">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.170914560147282</v>
+        <v>3.310041992925212</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06721860980709513</v>
+        <v>0.06637625446365472</v>
       </c>
       <c r="C42">
-        <v>11140.472778766</v>
+        <v>11298.75618519508</v>
       </c>
       <c r="D42">
-        <v>13898.912778766</v>
+        <v>14057.19618519508</v>
       </c>
       <c r="E42">
         <v>1348.639999999999</v>
@@ -4737,37 +4737,37 @@
         <v>1428.7</v>
       </c>
       <c r="M42">
-        <v>462.1169399358624</v>
+        <v>442.6932759358625</v>
       </c>
       <c r="N42">
-        <v>966.5830600641374</v>
+        <v>986.0067240641374</v>
       </c>
       <c r="O42">
-        <v>193.3166120128275</v>
+        <v>197.2013448128275</v>
       </c>
       <c r="P42">
-        <v>773.2664480513099</v>
+        <v>788.8053792513099</v>
       </c>
       <c r="Q42">
-        <v>1199.36644805131</v>
+        <v>1214.90537925131</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.07904021930959086</v>
+        <v>0.07902296040385684</v>
       </c>
       <c r="T42">
         <v>0.6830990336749931</v>
       </c>
       <c r="U42">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.0916416961436</v>
+        <v>3.227290943102082</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06721211495483352</v>
+        <v>0.06634898212300928</v>
       </c>
       <c r="C43">
-        <v>10954.92881478746</v>
+        <v>11117.24069142954</v>
       </c>
       <c r="D43">
-        <v>13900.13481478746</v>
+        <v>14062.44669142954</v>
       </c>
       <c r="E43">
         <v>1535.406</v>
@@ -4819,37 +4819,37 @@
         <v>1428.7</v>
       </c>
       <c r="M43">
-        <v>473.6698634342591</v>
+        <v>453.7606078342591</v>
       </c>
       <c r="N43">
-        <v>955.0301365657408</v>
+        <v>974.9393921657407</v>
       </c>
       <c r="O43">
-        <v>191.0060273131482</v>
+        <v>194.9878784331482</v>
       </c>
       <c r="P43">
-        <v>764.0241092525927</v>
+        <v>779.9515137325926</v>
       </c>
       <c r="Q43">
-        <v>1190.124109252593</v>
+        <v>1206.051513732593</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.07953012674230406</v>
+        <v>0.0795126134680257</v>
       </c>
       <c r="T43">
         <v>0.6931668160430844</v>
       </c>
       <c r="U43">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.016235801115707</v>
+        <v>3.148576529855689</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06807922010257192</v>
+        <v>0.06632170978236385</v>
       </c>
       <c r="C44">
-        <v>10606.89173929622</v>
+        <v>10935.72912136485</v>
       </c>
       <c r="D44">
-        <v>13738.86373929622</v>
+        <v>14067.70112136485</v>
       </c>
       <c r="E44">
         <v>1722.171999999999</v>
@@ -4901,45 +4901,45 @@
         <v>1428.7</v>
       </c>
       <c r="M44">
-        <v>505.6176341326554</v>
+        <v>464.8279397326556</v>
       </c>
       <c r="N44">
-        <v>923.0823658673444</v>
+        <v>963.8720602673443</v>
       </c>
       <c r="O44">
-        <v>184.6164731734689</v>
+        <v>192.7744120534689</v>
       </c>
       <c r="P44">
-        <v>738.4658926938755</v>
+        <v>771.0976482138755</v>
       </c>
       <c r="Q44">
-        <v>1164.565892693875</v>
+        <v>1197.197648213875</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08003692753476599</v>
+        <v>0.08001915112061415</v>
       </c>
       <c r="T44">
         <v>0.70358176332042</v>
       </c>
       <c r="U44">
-        <v>0.06445774444168939</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05156619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.825653030181225</v>
+        <v>3.073610422001983</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06809352525031032</v>
+        <v>0.06629443744171842</v>
       </c>
       <c r="C45">
-        <v>10417.49652642401</v>
+        <v>10754.22147940095</v>
       </c>
       <c r="D45">
-        <v>13736.23452642401</v>
+        <v>14072.95947940095</v>
       </c>
       <c r="E45">
         <v>1908.937999999999</v>
@@ -4983,45 +4983,45 @@
         <v>1428.7</v>
       </c>
       <c r="M45">
-        <v>517.656149231052</v>
+        <v>475.8952716310521</v>
       </c>
       <c r="N45">
-        <v>911.0438507689478</v>
+        <v>952.8047283689477</v>
       </c>
       <c r="O45">
-        <v>182.2087701537896</v>
+        <v>190.5609456737895</v>
       </c>
       <c r="P45">
-        <v>728.8350806151582</v>
+        <v>762.2437826951582</v>
       </c>
       <c r="Q45">
-        <v>1154.935080615158</v>
+        <v>1188.343782695158</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08056151081117396</v>
+        <v>0.08054346202417065</v>
       </c>
       <c r="T45">
         <v>0.7143621473443291</v>
       </c>
       <c r="U45">
-        <v>0.06445774444168939</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05156619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.75994016901422</v>
+        <v>3.002131109862402</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06810783039804871</v>
+        <v>0.06714716510107301</v>
       </c>
       <c r="C46">
-        <v>10228.10231966669</v>
+        <v>10404.88035759959</v>
       </c>
       <c r="D46">
-        <v>13733.60631966669</v>
+        <v>13910.38435759959</v>
       </c>
       <c r="E46">
         <v>2095.704</v>
@@ -5065,37 +5065,37 @@
         <v>1428.7</v>
       </c>
       <c r="M46">
-        <v>529.6946643294486</v>
+        <v>507.5068635294487</v>
       </c>
       <c r="N46">
-        <v>899.0053356705512</v>
+        <v>921.1931364705511</v>
       </c>
       <c r="O46">
-        <v>179.8010671341102</v>
+        <v>184.2386272941102</v>
       </c>
       <c r="P46">
-        <v>719.204268536441</v>
+        <v>736.9545091764409</v>
       </c>
       <c r="Q46">
-        <v>1145.304268536441</v>
+        <v>1163.054509176441</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.0811048292045965</v>
+        <v>0.08108649831713988</v>
       </c>
       <c r="T46">
         <v>0.7255275450833777</v>
       </c>
       <c r="U46">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.697214256082078</v>
+        <v>2.815134341364622</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06812213554578711</v>
+        <v>0.06713989276042757</v>
       </c>
       <c r="C47">
-        <v>10038.70911844686</v>
+        <v>10219.48496929729</v>
       </c>
       <c r="D47">
-        <v>13730.97911844686</v>
+        <v>13911.75496929729</v>
       </c>
       <c r="E47">
         <v>2282.469999999999</v>
@@ -5147,37 +5147,37 @@
         <v>1428.7</v>
       </c>
       <c r="M47">
-        <v>541.7331794278452</v>
+        <v>519.0411104278453</v>
       </c>
       <c r="N47">
-        <v>886.9668205721546</v>
+        <v>909.6588895721545</v>
       </c>
       <c r="O47">
-        <v>177.3933641144309</v>
+        <v>181.9317779144309</v>
       </c>
       <c r="P47">
-        <v>709.5734564577236</v>
+        <v>727.7271116577236</v>
       </c>
       <c r="Q47">
-        <v>1135.673456457724</v>
+        <v>1153.827111657724</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08166790463050713</v>
+        <v>0.08164928138439888</v>
       </c>
       <c r="T47">
         <v>0.7370989572856644</v>
       </c>
       <c r="U47">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.637276161502476</v>
+        <v>2.752575800445408</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06813644069352551</v>
+        <v>0.06713262041978214</v>
       </c>
       <c r="C48">
-        <v>9849.316922187552</v>
+        <v>10034.08985111859</v>
       </c>
       <c r="D48">
-        <v>13728.35292218755</v>
+        <v>13913.12585111859</v>
       </c>
       <c r="E48">
         <v>2469.235999999999</v>
@@ -5229,37 +5229,37 @@
         <v>1428.7</v>
       </c>
       <c r="M48">
-        <v>553.7716945262417</v>
+        <v>530.5753573262418</v>
       </c>
       <c r="N48">
-        <v>874.9283054737581</v>
+        <v>898.124642673758</v>
       </c>
       <c r="O48">
-        <v>174.9856610947516</v>
+        <v>179.6249285347516</v>
       </c>
       <c r="P48">
-        <v>699.9426443790064</v>
+        <v>718.4997141390064</v>
       </c>
       <c r="Q48">
-        <v>1126.042644379007</v>
+        <v>1144.599714139006</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08225183470182186</v>
+        <v>0.08223290826896379</v>
       </c>
       <c r="T48">
         <v>0.7490989403102581</v>
       </c>
       <c r="U48">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.579944071035031</v>
+        <v>2.6927371960879</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0681507458412639</v>
+        <v>0.06712534807913671</v>
       </c>
       <c r="C49">
-        <v>9659.925730312258</v>
+        <v>9848.695003143344</v>
       </c>
       <c r="D49">
-        <v>13725.72773031226</v>
+        <v>13914.49700314335</v>
       </c>
       <c r="E49">
         <v>2656.002</v>
@@ -5311,37 +5311,37 @@
         <v>1428.7</v>
       </c>
       <c r="M49">
-        <v>565.8102096246383</v>
+        <v>542.1096042246385</v>
       </c>
       <c r="N49">
-        <v>862.8897903753615</v>
+        <v>886.5903957753613</v>
       </c>
       <c r="O49">
-        <v>172.5779580750723</v>
+        <v>177.3180791550723</v>
       </c>
       <c r="P49">
-        <v>690.3118323002892</v>
+        <v>709.2723166202891</v>
       </c>
       <c r="Q49">
-        <v>1116.411832300289</v>
+        <v>1135.372316620289</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08285779987016734</v>
+        <v>0.08283855880954999</v>
       </c>
       <c r="T49">
         <v>0.7615517528829496</v>
       </c>
       <c r="U49">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.525051643991732</v>
+        <v>2.635444915320071</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06920185098900229</v>
+        <v>0.06711807573849128</v>
       </c>
       <c r="C50">
-        <v>9282.976524572501</v>
+        <v>9663.300425451465</v>
       </c>
       <c r="D50">
-        <v>13535.5445245725</v>
+        <v>13915.86842545146</v>
       </c>
       <c r="E50">
         <v>2842.767999999998</v>
@@ -5393,45 +5393,45 @@
         <v>1428.7</v>
       </c>
       <c r="M50">
-        <v>602.0535983230349</v>
+        <v>553.6438511230349</v>
       </c>
       <c r="N50">
-        <v>826.646401676965</v>
+        <v>875.0561488769649</v>
       </c>
       <c r="O50">
-        <v>165.329280335393</v>
+        <v>175.011229775393</v>
       </c>
       <c r="P50">
-        <v>661.3171213415719</v>
+        <v>700.044919101572</v>
       </c>
       <c r="Q50">
-        <v>1087.417121341572</v>
+        <v>1126.144919101572</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08348707139114148</v>
+        <v>0.08346750360169722</v>
       </c>
       <c r="T50">
         <v>0.77448351978536</v>
       </c>
       <c r="U50">
-        <v>0.0671577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.05372619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.373044532877991</v>
+        <v>2.580539812917571</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06923775613674069</v>
+        <v>0.06711080339784585</v>
       </c>
       <c r="C51">
-        <v>9089.807022379719</v>
+        <v>9477.906118122861</v>
       </c>
       <c r="D51">
-        <v>13529.14102237972</v>
+        <v>13917.24011812286</v>
       </c>
       <c r="E51">
         <v>3029.534</v>
@@ -5475,45 +5475,45 @@
         <v>1428.7</v>
       </c>
       <c r="M51">
-        <v>614.5963816214315</v>
+        <v>565.1780980214315</v>
       </c>
       <c r="N51">
-        <v>814.1036183785683</v>
+        <v>863.5219019785683</v>
       </c>
       <c r="O51">
-        <v>162.8207236757137</v>
+        <v>172.7043803957137</v>
       </c>
       <c r="P51">
-        <v>651.2828947028546</v>
+        <v>690.8175215828546</v>
       </c>
       <c r="Q51">
-        <v>1077.382894702855</v>
+        <v>1116.917521582855</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08414102022666362</v>
+        <v>0.08412111289549727</v>
       </c>
       <c r="T51">
         <v>0.7879224148015904</v>
       </c>
       <c r="U51">
-        <v>0.0671577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.05372619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.324615052615174</v>
+        <v>2.527875735102926</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06927366128447909</v>
+        <v>0.06850353105720043</v>
       </c>
       <c r="C52">
-        <v>8896.643576160604</v>
+        <v>9033.288565340754</v>
       </c>
       <c r="D52">
-        <v>13522.7435761606</v>
+        <v>13659.38856534075</v>
       </c>
       <c r="E52">
         <v>3216.299999999999</v>
@@ -5557,37 +5557,37 @@
         <v>1428.7</v>
       </c>
       <c r="M52">
-        <v>627.1391649198281</v>
+        <v>609.396394919828</v>
       </c>
       <c r="N52">
-        <v>801.5608350801717</v>
+        <v>819.3036050801718</v>
       </c>
       <c r="O52">
-        <v>160.3121670160344</v>
+        <v>163.8607210160344</v>
       </c>
       <c r="P52">
-        <v>641.2486680641374</v>
+        <v>655.4428840641374</v>
       </c>
       <c r="Q52">
-        <v>1067.348668064137</v>
+        <v>1081.542884064138</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.08482112701560666</v>
+        <v>0.08480086656104933</v>
       </c>
       <c r="T52">
         <v>0.8018988656184701</v>
       </c>
       <c r="U52">
-        <v>0.0671577444416894</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05372619555335152</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.278122751562871</v>
+        <v>2.344451020567588</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07122716643221749</v>
+        <v>0.06852425871655499</v>
       </c>
       <c r="C53">
-        <v>8370.699979239304</v>
+        <v>8842.757155822204</v>
       </c>
       <c r="D53">
-        <v>13183.5659792393</v>
+        <v>13655.6231558222</v>
       </c>
       <c r="E53">
         <v>3403.065999999999</v>
@@ -5639,45 +5639,45 @@
         <v>1428.7</v>
       </c>
       <c r="M53">
-        <v>684.4497584182246</v>
+        <v>621.5843228182246</v>
       </c>
       <c r="N53">
-        <v>744.2502415817752</v>
+        <v>807.1156771817753</v>
       </c>
       <c r="O53">
-        <v>148.850048316355</v>
+        <v>161.4231354363551</v>
       </c>
       <c r="P53">
-        <v>595.4001932654202</v>
+        <v>645.6925417454202</v>
       </c>
       <c r="Q53">
-        <v>1021.50019326542</v>
+        <v>1071.79254174542</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.08552899326532289</v>
+        <v>0.08550836527417494</v>
       </c>
       <c r="T53">
         <v>0.8164457838156306</v>
       </c>
       <c r="U53">
-        <v>0.07185774444168941</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.05748619555335153</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.087370157455751</v>
+        <v>2.298481392713322</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07130067157995588</v>
+        <v>0.06854498637590957</v>
       </c>
       <c r="C54">
-        <v>8171.503474666368</v>
+        <v>8652.227821711547</v>
       </c>
       <c r="D54">
-        <v>13171.13547466637</v>
+        <v>13651.85982171155</v>
       </c>
       <c r="E54">
         <v>3589.832</v>
@@ -5721,45 +5721,45 @@
         <v>1428.7</v>
       </c>
       <c r="M54">
-        <v>697.8703419166213</v>
+        <v>633.7722507166212</v>
       </c>
       <c r="N54">
-        <v>730.8296580833785</v>
+        <v>794.9277492833786</v>
       </c>
       <c r="O54">
-        <v>146.1659316166757</v>
+        <v>158.9855498566757</v>
       </c>
       <c r="P54">
-        <v>584.6637264667028</v>
+        <v>635.9421994267029</v>
       </c>
       <c r="Q54">
-        <v>1010.763726466703</v>
+        <v>1062.042199426703</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.0862663539421106</v>
+        <v>0.08624534310034745</v>
       </c>
       <c r="T54">
         <v>0.8315988236043393</v>
       </c>
       <c r="U54">
-        <v>0.07185774444168941</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.05748619555335153</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.047228423658524</v>
+        <v>2.254279827468834</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07137417672769429</v>
+        <v>0.06975291403526414</v>
       </c>
       <c r="C55">
-        <v>7972.330388930217</v>
+        <v>8249.675316329131</v>
       </c>
       <c r="D55">
-        <v>13158.72838893022</v>
+        <v>13436.07331632913</v>
       </c>
       <c r="E55">
         <v>3776.598</v>
@@ -5803,37 +5803,37 @@
         <v>1428.7</v>
       </c>
       <c r="M55">
-        <v>711.2909254150179</v>
+        <v>673.6762530150178</v>
       </c>
       <c r="N55">
-        <v>717.4090745849819</v>
+        <v>755.023746984982</v>
       </c>
       <c r="O55">
-        <v>143.4818149169964</v>
+        <v>151.0047493969964</v>
       </c>
       <c r="P55">
-        <v>573.9272596679855</v>
+        <v>604.0189975879856</v>
       </c>
       <c r="Q55">
-        <v>1000.027259667986</v>
+        <v>1030.118997587986</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.08703509166897441</v>
+        <v>0.0870136816850805</v>
       </c>
       <c r="T55">
         <v>0.8473966735968231</v>
       </c>
       <c r="U55">
-        <v>0.07185774444168941</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.05748619555335153</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.00860147226874</v>
+        <v>2.120751612671363</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07749568187543268</v>
+        <v>0.06979604169461871</v>
       </c>
       <c r="C56">
-        <v>6828.367300153934</v>
+        <v>8055.330964482671</v>
       </c>
       <c r="D56">
-        <v>12201.53130015393</v>
+        <v>13428.49496448267</v>
       </c>
       <c r="E56">
         <v>3963.364</v>
@@ -5885,45 +5885,45 @@
         <v>1428.7</v>
       </c>
       <c r="M56">
-        <v>865.9066049134143</v>
+        <v>686.3871257134143</v>
       </c>
       <c r="N56">
-        <v>562.7933950865855</v>
+        <v>742.3128742865855</v>
       </c>
       <c r="O56">
-        <v>112.5586790173171</v>
+        <v>148.4625748573171</v>
       </c>
       <c r="P56">
-        <v>450.2347160692684</v>
+        <v>593.8502994292684</v>
       </c>
       <c r="Q56">
-        <v>876.3347160692684</v>
+        <v>1019.950299429268</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.08783725277526708</v>
+        <v>0.08781542629523673</v>
       </c>
       <c r="T56">
         <v>0.8638813866324582</v>
       </c>
       <c r="U56">
-        <v>0.08585774444168939</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.06868619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.649946994159794</v>
+        <v>2.08147843465893</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07768118702317109</v>
+        <v>0.06983916935397329</v>
       </c>
       <c r="C57">
-        <v>6614.763727215117</v>
+        <v>7860.99515665656</v>
       </c>
       <c r="D57">
-        <v>12174.69372721512</v>
+        <v>13420.92515665656</v>
       </c>
       <c r="E57">
         <v>4150.129999999999</v>
@@ -5967,45 +5967,45 @@
         <v>1428.7</v>
       </c>
       <c r="M57">
-        <v>881.9419124118108</v>
+        <v>699.0979984118109</v>
       </c>
       <c r="N57">
-        <v>546.758087588189</v>
+        <v>729.602001588189</v>
       </c>
       <c r="O57">
-        <v>109.3516175176378</v>
+        <v>145.9204003176378</v>
       </c>
       <c r="P57">
-        <v>437.4064700705512</v>
+        <v>583.6816012705511</v>
       </c>
       <c r="Q57">
-        <v>863.5064700705512</v>
+        <v>1009.781601270551</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.08867506548628387</v>
+        <v>0.08865280399917766</v>
       </c>
       <c r="T57">
         <v>0.8810987535807883</v>
       </c>
       <c r="U57">
-        <v>0.08585774444168939</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.06868619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.619947957902343</v>
+        <v>2.043633372210586</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07786669217090947</v>
+        <v>0.06988229701332786</v>
       </c>
       <c r="C58">
-        <v>6401.277954995065</v>
+        <v>7666.667878409826</v>
       </c>
       <c r="D58">
-        <v>12147.97395499506</v>
+        <v>13413.36387840983</v>
       </c>
       <c r="E58">
         <v>4336.896000000001</v>
@@ -6049,45 +6049,45 @@
         <v>1428.7</v>
       </c>
       <c r="M58">
-        <v>897.9772199102075</v>
+        <v>711.8088711102075</v>
       </c>
       <c r="N58">
-        <v>530.7227800897923</v>
+        <v>716.8911288897923</v>
       </c>
       <c r="O58">
-        <v>106.1445560179585</v>
+        <v>143.3782257779585</v>
       </c>
       <c r="P58">
-        <v>424.5782240718339</v>
+        <v>573.5129031118338</v>
       </c>
       <c r="Q58">
-        <v>850.6782240718339</v>
+        <v>999.6129031118338</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.08955096059325596</v>
+        <v>0.08952824432602502</v>
       </c>
       <c r="T58">
         <v>0.8990987281176788</v>
       </c>
       <c r="U58">
-        <v>0.08585774444168939</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.06868619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.591020315796944</v>
+        <v>2.007139919135397</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07805219731864788</v>
+        <v>0.07348222467268242</v>
       </c>
       <c r="C59">
-        <v>6187.909209581372</v>
+        <v>6877.438955949576</v>
       </c>
       <c r="D59">
-        <v>12121.37120958137</v>
+        <v>12810.90095594958</v>
       </c>
       <c r="E59">
         <v>4523.662</v>
@@ -6131,45 +6131,45 @@
         <v>1428.7</v>
       </c>
       <c r="M59">
-        <v>914.012527408604</v>
+        <v>807.5559074086041</v>
       </c>
       <c r="N59">
-        <v>514.6874725913958</v>
+        <v>621.1440925913957</v>
       </c>
       <c r="O59">
-        <v>102.9374945182792</v>
+        <v>124.2288185182792</v>
       </c>
       <c r="P59">
-        <v>411.7499780731167</v>
+        <v>496.9152740731166</v>
       </c>
       <c r="Q59">
-        <v>837.8499780731167</v>
+        <v>923.0152740731166</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09046759500752907</v>
+        <v>0.09044440280760944</v>
       </c>
       <c r="T59">
         <v>0.9179359107725641</v>
       </c>
       <c r="U59">
-        <v>0.08585774444168939</v>
+        <v>0.0758577444416894</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335152</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.563107678677699</v>
+        <v>1.769165437207447</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07823770246638626</v>
+        <v>0.07539735233203701</v>
       </c>
       <c r="C60">
-        <v>5974.656723825983</v>
+        <v>6391.707460221251</v>
       </c>
       <c r="D60">
-        <v>12094.88472382598</v>
+        <v>12511.93546022125</v>
       </c>
       <c r="E60">
         <v>4710.427999999998</v>
@@ -6213,37 +6213,37 @@
         <v>1428.7</v>
       </c>
       <c r="M60">
-        <v>930.0478349070004</v>
+        <v>863.9700241070004</v>
       </c>
       <c r="N60">
-        <v>498.6521650929994</v>
+        <v>564.7299758929994</v>
       </c>
       <c r="O60">
-        <v>99.7304330185999</v>
+        <v>112.9459951785999</v>
       </c>
       <c r="P60">
-        <v>398.9217320743995</v>
+        <v>451.7839807143995</v>
       </c>
       <c r="Q60">
-        <v>825.0217320743996</v>
+        <v>877.8839807143995</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09142787867962471</v>
+        <v>0.09140418788355503</v>
       </c>
       <c r="T60">
         <v>0.9376701021253009</v>
       </c>
       <c r="U60">
-        <v>0.08585774444168939</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.536157546286705</v>
+        <v>1.653645335064378</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07842320761412466</v>
+        <v>0.07553407999139157</v>
       </c>
       <c r="C61">
-        <v>5761.519737271394</v>
+        <v>6184.13004728225</v>
       </c>
       <c r="D61">
-        <v>12068.51373727139</v>
+        <v>12491.12404728225</v>
       </c>
       <c r="E61">
         <v>4897.193999999998</v>
@@ -6295,37 +6295,37 @@
         <v>1428.7</v>
       </c>
       <c r="M61">
-        <v>946.0831424053969</v>
+        <v>878.866059005397</v>
       </c>
       <c r="N61">
-        <v>482.6168575946029</v>
+        <v>549.8339409946028</v>
       </c>
       <c r="O61">
-        <v>96.5233715189206</v>
+        <v>109.9667881989206</v>
       </c>
       <c r="P61">
-        <v>386.0934860756823</v>
+        <v>439.8671527956823</v>
       </c>
       <c r="Q61">
-        <v>812.1934860756824</v>
+        <v>865.9671527956823</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.09243500545767626</v>
+        <v>0.0924107917436931</v>
       </c>
       <c r="T61">
         <v>0.9583669369586595</v>
       </c>
       <c r="U61">
-        <v>0.08585774444168939</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.510120977705574</v>
+        <v>1.625617448029389</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1031543176824281</v>
+        <v>0.07567080765074614</v>
       </c>
       <c r="C62">
-        <v>2856.761938473384</v>
+        <v>5976.621751658528</v>
       </c>
       <c r="D62">
-        <v>9350.521938473385</v>
+        <v>12470.38175165853</v>
       </c>
       <c r="E62">
         <v>5083.959999999999</v>
@@ -6377,45 +6377,45 @@
         <v>1428.7</v>
       </c>
       <c r="M62">
-        <v>1511.210489903794</v>
+        <v>893.7620939037937</v>
       </c>
       <c r="N62">
-        <v>-82.510489903794</v>
+        <v>534.9379060962061</v>
       </c>
       <c r="O62">
-        <v>-16.5020979807588</v>
+        <v>106.9875812192412</v>
       </c>
       <c r="P62">
-        <v>-66.00839192303519</v>
+        <v>427.9503248769649</v>
       </c>
       <c r="Q62">
-        <v>360.0916080769648</v>
+        <v>854.0503248769649</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09384757393260065</v>
+        <v>0.09346772579683807</v>
       </c>
       <c r="T62">
-        <v>0.9873957514569504</v>
+        <v>0.9800986135336858</v>
       </c>
       <c r="U62">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V62">
-        <v>0.1890802121272932</v>
+        <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.1093588135156465</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9454010606364658</v>
+        <v>1.598523823895566</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1040448951268451</v>
+        <v>0.0758075353101007</v>
       </c>
       <c r="C63">
-        <v>2594.772990013</v>
+        <v>5769.182229599992</v>
       </c>
       <c r="D63">
-        <v>9275.298990013</v>
+        <v>12449.70822959999</v>
       </c>
       <c r="E63">
         <v>5270.725999999999</v>
@@ -6459,45 +6459,45 @@
         <v>1428.7</v>
       </c>
       <c r="M63">
-        <v>1536.39733140219</v>
+        <v>908.6581288021902</v>
       </c>
       <c r="N63">
-        <v>-107.6973314021905</v>
+        <v>520.0418711978097</v>
       </c>
       <c r="O63">
-        <v>-21.53946628043809</v>
+        <v>104.0083742395619</v>
       </c>
       <c r="P63">
-        <v>-86.15786512175237</v>
+        <v>416.0334969582477</v>
       </c>
       <c r="Q63">
-        <v>339.9421348782477</v>
+        <v>842.1334969582477</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.09507956300779558</v>
+        <v>0.09457886159629816</v>
       </c>
       <c r="T63">
-        <v>1.012713591237898</v>
+        <v>1.002944735061277</v>
       </c>
       <c r="U63">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V63">
-        <v>0.185980536518649</v>
+        <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.1097768287767291</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.9299026825932452</v>
+        <v>1.572318515307114</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1049354725712619</v>
+        <v>0.07594426296945528</v>
       </c>
       <c r="C64">
-        <v>2333.98468766451</v>
+        <v>5561.811139632253</v>
       </c>
       <c r="D64">
-        <v>9201.276687664507</v>
+        <v>12429.10313963225</v>
       </c>
       <c r="E64">
         <v>5457.491999999998</v>
@@ -6541,45 +6541,45 @@
         <v>1428.7</v>
       </c>
       <c r="M64">
-        <v>1561.584172900587</v>
+        <v>923.5541637005867</v>
       </c>
       <c r="N64">
-        <v>-132.8841729005869</v>
+        <v>505.1458362994131</v>
       </c>
       <c r="O64">
-        <v>-26.57683458011739</v>
+        <v>101.0291672598826</v>
       </c>
       <c r="P64">
-        <v>-106.3073383204695</v>
+        <v>404.1166690395304</v>
       </c>
       <c r="Q64">
-        <v>319.7926616795305</v>
+        <v>830.2166690395304</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.09637639361326386</v>
+        <v>0.09574847822730879</v>
       </c>
       <c r="T64">
-        <v>1.039363948902053</v>
+        <v>1.02699328403769</v>
       </c>
       <c r="U64">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V64">
-        <v>0.1829808504457676</v>
+        <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.1101813596745511</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.914904252228838</v>
+        <v>1.546958539253773</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1058260500156788</v>
+        <v>0.07608099062880985</v>
       </c>
       <c r="C65">
-        <v>2074.368513446736</v>
+        <v>5354.508142537832</v>
       </c>
       <c r="D65">
-        <v>9128.426513446737</v>
+        <v>12408.56614253783</v>
       </c>
       <c r="E65">
         <v>5644.258</v>
@@ -6623,45 +6623,45 @@
         <v>1428.7</v>
       </c>
       <c r="M65">
-        <v>1586.771014398983</v>
+        <v>938.4501985989834</v>
       </c>
       <c r="N65">
-        <v>-158.0710143989836</v>
+        <v>490.2498014010164</v>
       </c>
       <c r="O65">
-        <v>-31.61420287979672</v>
+        <v>98.04996028020328</v>
       </c>
       <c r="P65">
-        <v>-126.4568115191869</v>
+        <v>392.1998411208131</v>
       </c>
       <c r="Q65">
-        <v>299.6431884808131</v>
+        <v>818.2998411208132</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.09774332317037909</v>
+        <v>0.09698131737891459</v>
       </c>
       <c r="T65">
-        <v>1.067454866439946</v>
+        <v>1.052341754580395</v>
       </c>
       <c r="U65">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V65">
-        <v>0.180076392502184</v>
+        <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.1105730483216485</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.9003819625109198</v>
+        <v>1.5224036418053</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1067166274600957</v>
+        <v>0.08348811828816444</v>
       </c>
       <c r="C66">
-        <v>1815.896845436955</v>
+        <v>4148.260488372418</v>
       </c>
       <c r="D66">
-        <v>9056.720845436954</v>
+        <v>11389.08448837242</v>
       </c>
       <c r="E66">
         <v>5831.023999999999</v>
@@ -6705,45 +6705,45 @@
         <v>1428.7</v>
       </c>
       <c r="M66">
-        <v>1611.95785589738</v>
+        <v>1123.07917429738</v>
       </c>
       <c r="N66">
-        <v>-183.2578558973803</v>
+        <v>305.6208257026199</v>
       </c>
       <c r="O66">
-        <v>-36.65157117947606</v>
+        <v>61.12416514052398</v>
       </c>
       <c r="P66">
-        <v>-146.6062847179042</v>
+        <v>244.4966605620959</v>
       </c>
       <c r="Q66">
-        <v>279.4937152820958</v>
+        <v>670.5966605620958</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.09918619325844519</v>
+        <v>0.09828264759449849</v>
       </c>
       <c r="T66">
-        <v>1.097106390507723</v>
+        <v>1.079098473486583</v>
       </c>
       <c r="U66">
-        <v>0.1348577444416894</v>
+        <v>0.0939577444416894</v>
       </c>
       <c r="V66">
-        <v>0.1772626988693373</v>
+        <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.1109524966985242</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8863134943466867</v>
+        <v>1.272127586992094</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1076072049045126</v>
+        <v>0.083738445947519</v>
       </c>
       <c r="C67">
-        <v>1558.542922851548</v>
+        <v>3929.95886371959</v>
       </c>
       <c r="D67">
-        <v>8986.132922851546</v>
+        <v>11357.54886371959</v>
       </c>
       <c r="E67">
         <v>6017.789999999999</v>
@@ -6787,45 +6787,45 @@
         <v>1428.7</v>
       </c>
       <c r="M67">
-        <v>1637.144697395777</v>
+        <v>1140.627286395777</v>
       </c>
       <c r="N67">
-        <v>-208.4446973957768</v>
+        <v>288.0727136042233</v>
       </c>
       <c r="O67">
-        <v>-41.68893947915535</v>
+        <v>57.61454272084466</v>
       </c>
       <c r="P67">
-        <v>-166.7557579166214</v>
+        <v>230.4581708833786</v>
       </c>
       <c r="Q67">
-        <v>259.3442420833786</v>
+        <v>656.5581708833786</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1007115130658293</v>
+        <v>0.09965833953668718</v>
       </c>
       <c r="T67">
-        <v>1.128452287379372</v>
+        <v>1.10738414775884</v>
       </c>
       <c r="U67">
-        <v>0.1348577444416894</v>
+        <v>0.0939577444416894</v>
       </c>
       <c r="V67">
-        <v>0.1745355804251937</v>
+        <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.1113202697407267</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8726779021259685</v>
+        <v>1.252556393346062</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1084977823489295</v>
+        <v>0.1001231067374275</v>
       </c>
       <c r="C68">
-        <v>1302.280812747027</v>
+        <v>2000.625105220297</v>
       </c>
       <c r="D68">
-        <v>8916.636812747029</v>
+        <v>9614.981105220299</v>
       </c>
       <c r="E68">
         <v>6204.556</v>
@@ -6869,37 +6869,37 @@
         <v>1428.7</v>
       </c>
       <c r="M68">
-        <v>1662.331538894173</v>
+        <v>1510.714900094173</v>
       </c>
       <c r="N68">
-        <v>-233.6315388941734</v>
+        <v>-82.0149000941733</v>
       </c>
       <c r="O68">
-        <v>-46.72630777883469</v>
+        <v>-16.40298001883466</v>
       </c>
       <c r="P68">
-        <v>-186.9052311153388</v>
+        <v>-65.61192007533865</v>
       </c>
       <c r="Q68">
-        <v>239.1947688846613</v>
+        <v>360.4880799246614</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1023265575677655</v>
+        <v>0.1015716292986418</v>
       </c>
       <c r="T68">
-        <v>1.161642060537589</v>
+        <v>1.146723399036994</v>
       </c>
       <c r="U68">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V68">
-        <v>0.1718911019339029</v>
+        <v>0.1891422398641781</v>
       </c>
       <c r="W68">
-        <v>0.1116768981452868</v>
+        <v>0.09937689814528675</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8594555096695143</v>
+        <v>0.9457111993208905</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1093883597933464</v>
+        <v>0.1008906841818444</v>
       </c>
       <c r="C69">
-        <v>1047.085378254349</v>
+        <v>1745.242720407234</v>
       </c>
       <c r="D69">
-        <v>8848.207378254348</v>
+        <v>9546.364720407235</v>
       </c>
       <c r="E69">
         <v>6391.322</v>
@@ -6951,37 +6951,37 @@
         <v>1428.7</v>
       </c>
       <c r="M69">
-        <v>1687.51838039257</v>
+        <v>1533.60451979257</v>
       </c>
       <c r="N69">
-        <v>-258.8183803925699</v>
+        <v>-104.90451979257</v>
       </c>
       <c r="O69">
-        <v>-51.76367607851398</v>
+        <v>-20.980903958514</v>
       </c>
       <c r="P69">
-        <v>-207.0547043140559</v>
+        <v>-83.92361583405599</v>
       </c>
       <c r="Q69">
-        <v>219.0452956859441</v>
+        <v>342.176384165944</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1040394835546675</v>
+        <v>0.103261678671328</v>
       </c>
       <c r="T69">
-        <v>1.196843335099334</v>
+        <v>1.181472592947206</v>
       </c>
       <c r="U69">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V69">
-        <v>0.1693255630990685</v>
+        <v>0.1863192213587426</v>
       </c>
       <c r="W69">
-        <v>0.1120228809258301</v>
+        <v>0.09972288092583008</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8466278154953426</v>
+        <v>0.931596106793713</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1102789372377633</v>
+        <v>0.1016582616262613</v>
       </c>
       <c r="C70">
-        <v>792.9322482647513</v>
+        <v>1490.832744509284</v>
       </c>
       <c r="D70">
-        <v>8780.820248264752</v>
+        <v>9478.720744509283</v>
       </c>
       <c r="E70">
         <v>6578.088</v>
@@ -7033,37 +7033,37 @@
         <v>1428.7</v>
       </c>
       <c r="M70">
-        <v>1712.705221890966</v>
+        <v>1556.494139490966</v>
       </c>
       <c r="N70">
-        <v>-284.0052218909666</v>
+        <v>-127.7941394909665</v>
       </c>
       <c r="O70">
-        <v>-56.80104437819332</v>
+        <v>-25.5588278981933</v>
       </c>
       <c r="P70">
-        <v>-227.2041775127733</v>
+        <v>-102.2353115927732</v>
       </c>
       <c r="Q70">
-        <v>198.8958224872268</v>
+        <v>323.8646884072268</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1058594674157508</v>
+        <v>0.105057356129807</v>
       </c>
       <c r="T70">
-        <v>1.234244689321188</v>
+        <v>1.218393611476806</v>
       </c>
       <c r="U70">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V70">
-        <v>0.1668354812887881</v>
+        <v>0.1835792328093493</v>
       </c>
       <c r="W70">
-        <v>0.1123586877422398</v>
+        <v>0.1000586877422398</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8341774064439405</v>
+        <v>0.9178961640467467</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1111695146821802</v>
+        <v>0.1024258390706781</v>
       </c>
       <c r="C71">
-        <v>539.7977884903667</v>
+        <v>1237.374651976497</v>
       </c>
       <c r="D71">
-        <v>8714.451788490367</v>
+        <v>9412.028651976496</v>
       </c>
       <c r="E71">
         <v>6764.853999999999</v>
@@ -7115,37 +7115,37 @@
         <v>1428.7</v>
       </c>
       <c r="M71">
-        <v>1737.892063389363</v>
+        <v>1579.383759189363</v>
       </c>
       <c r="N71">
-        <v>-309.1920633893631</v>
+        <v>-150.6837591893629</v>
       </c>
       <c r="O71">
-        <v>-61.83841267787261</v>
+        <v>-30.13675183787259</v>
       </c>
       <c r="P71">
-        <v>-247.3536507114904</v>
+        <v>-120.5470073514904</v>
       </c>
       <c r="Q71">
-        <v>178.7463492885096</v>
+        <v>305.5529926485096</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1077968695904525</v>
+        <v>0.1069688837468975</v>
       </c>
       <c r="T71">
-        <v>1.274059034138001</v>
+        <v>1.257696631201864</v>
       </c>
       <c r="U71">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V71">
-        <v>0.1644175757628636</v>
+        <v>0.1809186642179095</v>
       </c>
       <c r="W71">
-        <v>0.112684761027739</v>
+        <v>0.100384761027739</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8220878788143181</v>
+        <v>0.9045933210895475</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1120600921265971</v>
+        <v>0.1031934165150951</v>
       </c>
       <c r="C72">
-        <v>287.659073827379</v>
+        <v>984.8484908923147</v>
       </c>
       <c r="D72">
-        <v>8649.079073827379</v>
+        <v>9346.268490892315</v>
       </c>
       <c r="E72">
         <v>6951.620000000001</v>
@@ -7197,37 +7197,37 @@
         <v>1428.7</v>
       </c>
       <c r="M72">
-        <v>1763.07890488776</v>
+        <v>1602.273378887759</v>
       </c>
       <c r="N72">
-        <v>-334.3789048877597</v>
+        <v>-173.5733788877596</v>
       </c>
       <c r="O72">
-        <v>-66.87578097755195</v>
+        <v>-34.71467577755193</v>
       </c>
       <c r="P72">
-        <v>-267.5031239102078</v>
+        <v>-138.8587031102077</v>
       </c>
       <c r="Q72">
-        <v>158.5968760897922</v>
+        <v>287.2412968897923</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1098634319101343</v>
+        <v>0.1090078465384608</v>
       </c>
       <c r="T72">
-        <v>1.316527668609268</v>
+        <v>1.299619852241927</v>
       </c>
       <c r="U72">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V72">
-        <v>0.1620687532519656</v>
+        <v>0.1783341118719394</v>
       </c>
       <c r="W72">
-        <v>0.1130015179336526</v>
+        <v>0.1007015179336526</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8103437662598278</v>
+        <v>0.8916705593596967</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1741798107397912</v>
+        <v>0.1039609939595119</v>
       </c>
       <c r="C73">
-        <v>-2870.165404494986</v>
+        <v>733.2348630732522</v>
       </c>
       <c r="D73">
-        <v>5678.020595505011</v>
+        <v>9281.42086307325</v>
       </c>
       <c r="E73">
         <v>7138.385999999999</v>
@@ -7279,45 +7279,45 @@
         <v>1428.7</v>
       </c>
       <c r="M73">
-        <v>2914.072517786156</v>
+        <v>1625.162998586156</v>
       </c>
       <c r="N73">
-        <v>-1485.372517786156</v>
+        <v>-196.4629985861559</v>
       </c>
       <c r="O73">
-        <v>-297.0745035572313</v>
+        <v>-39.29259971723118</v>
       </c>
       <c r="P73">
-        <v>-1188.298014228925</v>
+        <v>-157.1703988689247</v>
       </c>
       <c r="Q73">
-        <v>-762.1980142289248</v>
+        <v>268.9296011310753</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1153488646269567</v>
+        <v>0.1111874274535801</v>
       </c>
       <c r="T73">
-        <v>1.429255378172527</v>
+        <v>1.344434329905441</v>
       </c>
       <c r="U73">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V73">
-        <v>0.09805521250963203</v>
+        <v>0.175822363817405</v>
       </c>
       <c r="W73">
-        <v>0.1982093521098222</v>
+        <v>0.1010093521098221</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4902760625481601</v>
+        <v>0.8791118190870252</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.175919388184208</v>
+        <v>0.1047285714039288</v>
       </c>
       <c r="C74">
-        <v>-3111.03110042174</v>
+        <v>482.5149049912761</v>
       </c>
       <c r="D74">
-        <v>5623.920899578259</v>
+        <v>9217.466904991274</v>
       </c>
       <c r="E74">
         <v>7325.151999999998</v>
@@ -7361,45 +7361,45 @@
         <v>1428.7</v>
       </c>
       <c r="M74">
-        <v>2955.115792684552</v>
+        <v>1648.052618284552</v>
       </c>
       <c r="N74">
-        <v>-1526.415792684552</v>
+        <v>-219.3526182845526</v>
       </c>
       <c r="O74">
-        <v>-305.2831585369105</v>
+        <v>-43.87052365691052</v>
       </c>
       <c r="P74">
-        <v>-1221.132634147642</v>
+        <v>-175.4820946276421</v>
       </c>
       <c r="Q74">
-        <v>-795.0326341476419</v>
+        <v>250.6179053723579</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.117832752649348</v>
+        <v>0.1135226927197794</v>
       </c>
       <c r="T74">
-        <v>1.48030021310726</v>
+        <v>1.392449841687778</v>
       </c>
       <c r="U74">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V74">
-        <v>0.09669333455810937</v>
+        <v>0.1733803865421633</v>
       </c>
       <c r="W74">
-        <v>0.1985086353366536</v>
+        <v>0.1013086353366536</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4834666727905468</v>
+        <v>0.8669019327108164</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.177658965628625</v>
+        <v>0.1054961488483457</v>
       </c>
       <c r="C75">
-        <v>-3350.875611533604</v>
+        <v>232.6702694795822</v>
       </c>
       <c r="D75">
-        <v>5570.842388466394</v>
+        <v>9154.388269479581</v>
       </c>
       <c r="E75">
         <v>7511.917999999998</v>
@@ -7443,45 +7443,45 @@
         <v>1428.7</v>
       </c>
       <c r="M75">
-        <v>2996.159067582949</v>
+        <v>1670.942237982949</v>
       </c>
       <c r="N75">
-        <v>-1567.459067582949</v>
+        <v>-242.2422379829491</v>
       </c>
       <c r="O75">
-        <v>-313.4918135165898</v>
+        <v>-48.44844759658982</v>
       </c>
       <c r="P75">
-        <v>-1253.967254066359</v>
+        <v>-193.7937903863593</v>
       </c>
       <c r="Q75">
-        <v>-827.8672540663591</v>
+        <v>232.3062096136408</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1205006323771016</v>
+        <v>0.1160309405982897</v>
       </c>
       <c r="T75">
-        <v>1.535126146926048</v>
+        <v>1.444022058046585</v>
       </c>
       <c r="U75">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V75">
-        <v>0.09536876833128595</v>
+        <v>0.1710053127539145</v>
       </c>
       <c r="W75">
-        <v>0.198799719023024</v>
+        <v>0.101599719023024</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4768438416564297</v>
+        <v>0.8550265637695724</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1793985430730419</v>
+        <v>0.1062637262927626</v>
       </c>
       <c r="C76">
-        <v>-3589.727581291123</v>
+        <v>-16.31689181561342</v>
       </c>
       <c r="D76">
-        <v>5518.756418708877</v>
+        <v>9092.167108184385</v>
       </c>
       <c r="E76">
         <v>7698.683999999999</v>
@@ -7525,45 +7525,45 @@
         <v>1428.7</v>
       </c>
       <c r="M76">
-        <v>3037.202342481346</v>
+        <v>1693.831857681346</v>
       </c>
       <c r="N76">
-        <v>-1608.502342481346</v>
+        <v>-265.1318576813458</v>
       </c>
       <c r="O76">
-        <v>-321.7004684962692</v>
+        <v>-53.02637153626915</v>
       </c>
       <c r="P76">
-        <v>-1286.801873985077</v>
+        <v>-212.1054861450766</v>
       </c>
       <c r="Q76">
-        <v>-860.7018739850765</v>
+        <v>213.9945138549234</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1233737336223748</v>
+        <v>0.1187321306213009</v>
       </c>
       <c r="T76">
-        <v>1.594169460269357</v>
+        <v>1.499561367971453</v>
       </c>
       <c r="U76">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V76">
-        <v>0.09408000119167398</v>
+        <v>0.1686944301491319</v>
       </c>
       <c r="W76">
-        <v>0.1990829355827357</v>
+        <v>0.1018829355827357</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4704000059583698</v>
+        <v>0.8434721507456592</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1811381205174587</v>
+        <v>0.1070313037371795</v>
       </c>
       <c r="C77">
-        <v>-3827.614591841355</v>
+        <v>-264.4639452724532</v>
       </c>
       <c r="D77">
-        <v>5467.635408158644</v>
+        <v>9030.786054727545</v>
       </c>
       <c r="E77">
         <v>7885.449999999999</v>
@@ -7607,45 +7607,45 @@
         <v>1428.7</v>
       </c>
       <c r="M77">
-        <v>3078.245617379742</v>
+        <v>1716.721477379742</v>
       </c>
       <c r="N77">
-        <v>-1649.545617379742</v>
+        <v>-288.0214773797422</v>
       </c>
       <c r="O77">
-        <v>-329.9091234759485</v>
+        <v>-57.60429547594845</v>
       </c>
       <c r="P77">
-        <v>-1319.636493903794</v>
+        <v>-230.4171819037938</v>
       </c>
       <c r="Q77">
-        <v>-893.5364939037939</v>
+        <v>195.6828180962062</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1264766829672698</v>
+        <v>0.1216494158461529</v>
       </c>
       <c r="T77">
-        <v>1.657936238680132</v>
+        <v>1.559543822690312</v>
       </c>
       <c r="U77">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V77">
-        <v>0.09282560117578498</v>
+        <v>0.1664451710804767</v>
       </c>
       <c r="W77">
-        <v>0.1993585997008551</v>
+        <v>0.1021585997008551</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4641280058789249</v>
+        <v>0.8322258554023838</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1828776979618756</v>
+        <v>0.1077988811815964</v>
       </c>
       <c r="C78">
-        <v>-4064.563212722207</v>
+        <v>-511.7877914533983</v>
       </c>
       <c r="D78">
-        <v>5417.452787277793</v>
+        <v>8970.228208546601</v>
       </c>
       <c r="E78">
         <v>8072.215999999999</v>
@@ -7689,45 +7689,45 @@
         <v>1428.7</v>
       </c>
       <c r="M78">
-        <v>3119.288892278139</v>
+        <v>1739.611097078139</v>
       </c>
       <c r="N78">
-        <v>-1690.588892278139</v>
+        <v>-310.9110970781387</v>
       </c>
       <c r="O78">
-        <v>-338.1177784556278</v>
+        <v>-62.18221941562774</v>
       </c>
       <c r="P78">
-        <v>-1352.471113822511</v>
+        <v>-248.728877662511</v>
       </c>
       <c r="Q78">
-        <v>-926.3711138225109</v>
+        <v>177.3711223374891</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1298382114242393</v>
+        <v>0.1248098081730759</v>
       </c>
       <c r="T78">
-        <v>1.727016915291804</v>
+        <v>1.624524815302408</v>
       </c>
       <c r="U78">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V78">
-        <v>0.09160421168662992</v>
+        <v>0.1642551030399442</v>
       </c>
       <c r="W78">
-        <v>0.1996270095000766</v>
+        <v>0.1024270095000766</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4580210584331497</v>
+        <v>0.8212755151997209</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1846172754062926</v>
+        <v>0.1085664586260133</v>
       </c>
       <c r="C79">
-        <v>-4300.599046909036</v>
+        <v>-758.3048806193074</v>
       </c>
       <c r="D79">
-        <v>5368.182953090964</v>
+        <v>8910.477119380694</v>
       </c>
       <c r="E79">
         <v>8258.982</v>
@@ -7771,45 +7771,45 @@
         <v>1428.7</v>
       </c>
       <c r="M79">
-        <v>3160.332167176536</v>
+        <v>1762.500716776535</v>
       </c>
       <c r="N79">
-        <v>-1731.632167176536</v>
+        <v>-333.8007167765356</v>
       </c>
       <c r="O79">
-        <v>-346.3264334353072</v>
+        <v>-66.76014335530714</v>
       </c>
       <c r="P79">
-        <v>-1385.305733741229</v>
+        <v>-267.0405734212285</v>
       </c>
       <c r="Q79">
-        <v>-959.2057337412288</v>
+        <v>159.0594265787715</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1334920467035541</v>
+        <v>0.1282450172240792</v>
       </c>
       <c r="T79">
-        <v>1.802104607261013</v>
+        <v>1.695156329011208</v>
       </c>
       <c r="U79">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V79">
-        <v>0.09041454659979056</v>
+        <v>0.1621219198835812</v>
       </c>
       <c r="W79">
-        <v>0.1998884476162014</v>
+        <v>0.1026884476162014</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4520727329989528</v>
+        <v>0.8106095994179061</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1863568528507095</v>
+        <v>0.1093340360704302</v>
       </c>
       <c r="C80">
-        <v>-4535.746774371273</v>
+        <v>-1004.031227627609</v>
       </c>
       <c r="D80">
-        <v>5319.801225628727</v>
+        <v>8851.516772372392</v>
       </c>
       <c r="E80">
         <v>8445.748</v>
@@ -7853,45 +7853,45 @@
         <v>1428.7</v>
       </c>
       <c r="M80">
-        <v>3201.375442074932</v>
+        <v>1785.390336474932</v>
       </c>
       <c r="N80">
-        <v>-1772.675442074932</v>
+        <v>-356.6903364749321</v>
       </c>
       <c r="O80">
-        <v>-354.5350884149864</v>
+        <v>-71.33806729498643</v>
       </c>
       <c r="P80">
-        <v>-1418.140353659946</v>
+        <v>-285.3522691799457</v>
       </c>
       <c r="Q80">
-        <v>-992.0403536599457</v>
+        <v>140.7477308200544</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1374780488264429</v>
+        <v>0.1319925180069919</v>
       </c>
       <c r="T80">
-        <v>1.884018453045604</v>
+        <v>1.772208889420809</v>
       </c>
       <c r="U80">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V80">
-        <v>0.0892553857459471</v>
+        <v>0.1600434337312276</v>
       </c>
       <c r="W80">
-        <v>0.2001431821908872</v>
+        <v>0.1029431821908871</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4462769287297355</v>
+        <v>0.8002171686561381</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1880964302951263</v>
+        <v>0.1761254531636593</v>
       </c>
       <c r="C81">
-        <v>-4770.03019329469</v>
+        <v>-4425.089704863309</v>
       </c>
       <c r="D81">
-        <v>5272.283806705309</v>
+        <v>5617.22429513669</v>
       </c>
       <c r="E81">
         <v>8632.513999999999</v>
@@ -7935,37 +7935,37 @@
         <v>1428.7</v>
       </c>
       <c r="M81">
-        <v>3242.418716973329</v>
+        <v>3021.101006973328</v>
       </c>
       <c r="N81">
-        <v>-1813.718716973329</v>
+        <v>-1592.401006973329</v>
       </c>
       <c r="O81">
-        <v>-362.7437433946658</v>
+        <v>-318.4802013946658</v>
       </c>
       <c r="P81">
-        <v>-1450.974973578663</v>
+        <v>-1273.920805578663</v>
       </c>
       <c r="Q81">
-        <v>-1024.874973578663</v>
+        <v>-847.8208055786628</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1418436701991307</v>
+        <v>0.1412675886207164</v>
       </c>
       <c r="T81">
-        <v>1.973733617476347</v>
+        <v>1.962914103419949</v>
       </c>
       <c r="U81">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V81">
-        <v>0.08812557073650473</v>
+        <v>0.09458141231969826</v>
       </c>
       <c r="W81">
-        <v>0.2003914677889986</v>
+        <v>0.1853914677889986</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4406278536825237</v>
+        <v>0.4729070615984913</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1898360077395432</v>
+        <v>0.1777150306080762</v>
       </c>
       <c r="C82">
-        <v>-5003.472259114009</v>
+        <v>-4660.282314835302</v>
       </c>
       <c r="D82">
-        <v>5225.60774088599</v>
+        <v>5568.797685164697</v>
       </c>
       <c r="E82">
         <v>8819.279999999999</v>
@@ -8017,37 +8017,37 @@
         <v>1428.7</v>
       </c>
       <c r="M82">
-        <v>3283.461991871725</v>
+        <v>3059.342791871725</v>
       </c>
       <c r="N82">
-        <v>-1854.761991871725</v>
+        <v>-1630.642791871725</v>
       </c>
       <c r="O82">
-        <v>-370.952398374345</v>
+        <v>-326.128558374345</v>
       </c>
       <c r="P82">
-        <v>-1483.80959349738</v>
+        <v>-1304.51423349738</v>
       </c>
       <c r="Q82">
-        <v>-1057.70959349738</v>
+        <v>-878.41423349738</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1466458537090872</v>
+        <v>0.1460409680517522</v>
       </c>
       <c r="T82">
-        <v>2.072420298350165</v>
+        <v>2.061059808590946</v>
       </c>
       <c r="U82">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V82">
-        <v>0.08702400110229842</v>
+        <v>0.09339914466570204</v>
       </c>
       <c r="W82">
-        <v>0.2006335462471572</v>
+        <v>0.1856335462471572</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4351200055114921</v>
+        <v>0.4669957233285101</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1915755851839601</v>
+        <v>0.1793046080524931</v>
       </c>
       <c r="C83">
-        <v>-5236.095121490334</v>
+        <v>-4894.647081160498</v>
       </c>
       <c r="D83">
-        <v>5179.750878509666</v>
+        <v>5521.198918839502</v>
       </c>
       <c r="E83">
         <v>9006.046</v>
@@ -8099,37 +8099,37 @@
         <v>1428.7</v>
       </c>
       <c r="M83">
-        <v>3324.505266770122</v>
+        <v>3097.584576770122</v>
       </c>
       <c r="N83">
-        <v>-1895.805266770122</v>
+        <v>-1668.884576770122</v>
       </c>
       <c r="O83">
-        <v>-379.1610533540244</v>
+        <v>-333.7769153540244</v>
       </c>
       <c r="P83">
-        <v>-1516.644213416098</v>
+        <v>-1335.107661416097</v>
       </c>
       <c r="Q83">
-        <v>-1090.544213416098</v>
+        <v>-909.0076614160974</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1519535302200918</v>
+        <v>0.1513168084755286</v>
       </c>
       <c r="T83">
-        <v>2.18149505089491</v>
+        <v>2.169536640622049</v>
       </c>
       <c r="U83">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V83">
-        <v>0.08594963071831943</v>
+        <v>0.09224606880563163</v>
       </c>
       <c r="W83">
-        <v>0.2008696474594354</v>
+        <v>0.1858696474594354</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4297481535915971</v>
+        <v>0.4612303440281581</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.193315162628377</v>
+        <v>0.18089418549691</v>
       </c>
       <c r="C84">
-        <v>-5467.920159358566</v>
+        <v>-5128.205051678007</v>
       </c>
       <c r="D84">
-        <v>5134.691840641433</v>
+        <v>5474.406948321993</v>
       </c>
       <c r="E84">
         <v>9192.812</v>
@@ -8181,37 +8181,37 @@
         <v>1428.7</v>
       </c>
       <c r="M84">
-        <v>3365.548541668518</v>
+        <v>3135.826361668518</v>
       </c>
       <c r="N84">
-        <v>-1936.848541668518</v>
+        <v>-1707.126361668518</v>
       </c>
       <c r="O84">
-        <v>-387.3697083337037</v>
+        <v>-341.4252723337037</v>
       </c>
       <c r="P84">
-        <v>-1549.478833334815</v>
+        <v>-1365.701089334815</v>
       </c>
       <c r="Q84">
-        <v>-1123.378833334815</v>
+        <v>-939.6010893348147</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1578509485656525</v>
+        <v>0.1571788533908358</v>
       </c>
       <c r="T84">
-        <v>2.302689220389072</v>
+        <v>2.290066453989941</v>
       </c>
       <c r="U84">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V84">
-        <v>0.08490146449004725</v>
+        <v>0.09112111674702637</v>
       </c>
       <c r="W84">
-        <v>0.2010999901055605</v>
+        <v>0.1860999901055604</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4245073224502361</v>
+        <v>0.4556055837351318</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1950547400727939</v>
+        <v>0.1824837629413269</v>
       </c>
       <c r="C85">
-        <v>-5698.968014161344</v>
+        <v>-5360.97656670433</v>
       </c>
       <c r="D85">
-        <v>5090.409985838654</v>
+        <v>5428.401433295669</v>
       </c>
       <c r="E85">
         <v>9379.578</v>
@@ -8263,37 +8263,37 @@
         <v>1428.7</v>
       </c>
       <c r="M85">
-        <v>3406.591816566915</v>
+        <v>3174.068146566914</v>
       </c>
       <c r="N85">
-        <v>-1977.891816566915</v>
+        <v>-1745.368146566915</v>
       </c>
       <c r="O85">
-        <v>-395.5783633133831</v>
+        <v>-349.073629313383</v>
       </c>
       <c r="P85">
-        <v>-1582.313453253532</v>
+        <v>-1396.294517253532</v>
       </c>
       <c r="Q85">
-        <v>-1156.213453253532</v>
+        <v>-970.1945172535317</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1644421808342203</v>
+        <v>0.1637305506491202</v>
       </c>
       <c r="T85">
-        <v>2.438141527470782</v>
+        <v>2.424776245401114</v>
       </c>
       <c r="U85">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V85">
-        <v>0.08387855527932378</v>
+        <v>0.09002327196694172</v>
       </c>
       <c r="W85">
-        <v>0.2013247823264777</v>
+        <v>0.1863247823264776</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4193927763966189</v>
+        <v>0.4501163598347085</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1967943175172108</v>
+        <v>0.1840733403857437</v>
       </c>
       <c r="C86">
-        <v>-5929.258621377987</v>
+        <v>-5592.981288514784</v>
       </c>
       <c r="D86">
-        <v>5046.885378622011</v>
+        <v>5383.162711485214</v>
       </c>
       <c r="E86">
         <v>9566.343999999997</v>
@@ -8345,37 +8345,37 @@
         <v>1428.7</v>
       </c>
       <c r="M86">
-        <v>3447.635091465311</v>
+        <v>3212.30993146531</v>
       </c>
       <c r="N86">
-        <v>-2018.935091465311</v>
+        <v>-1783.609931465311</v>
       </c>
       <c r="O86">
-        <v>-403.7870182930622</v>
+        <v>-356.7219862930622</v>
       </c>
       <c r="P86">
-        <v>-1615.148073172249</v>
+        <v>-1426.887945172248</v>
       </c>
       <c r="Q86">
-        <v>-1189.048073172249</v>
+        <v>-1000.787945172248</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.171857317136359</v>
+        <v>0.1711012100646902</v>
       </c>
       <c r="T86">
-        <v>2.590525372937705</v>
+        <v>2.576324760738682</v>
       </c>
       <c r="U86">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V86">
-        <v>0.08288000104980803</v>
+        <v>0.08895156634828767</v>
       </c>
       <c r="W86">
-        <v>0.2015442223516587</v>
+        <v>0.1865442223516587</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4144000052490402</v>
+        <v>0.4447578317414383</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1985338949616277</v>
+        <v>0.1856629178301607</v>
       </c>
       <c r="C87">
-        <v>-6158.811240449659</v>
+        <v>-5824.238229363013</v>
       </c>
       <c r="D87">
-        <v>5004.098759550341</v>
+        <v>5338.671770636987</v>
       </c>
       <c r="E87">
         <v>9753.109999999999</v>
@@ -8427,37 +8427,37 @@
         <v>1428.7</v>
       </c>
       <c r="M87">
-        <v>3488.678366363708</v>
+        <v>3250.551716363707</v>
       </c>
       <c r="N87">
-        <v>-2059.978366363708</v>
+        <v>-1821.851716363708</v>
       </c>
       <c r="O87">
-        <v>-411.9956732727417</v>
+        <v>-364.3703432727415</v>
       </c>
       <c r="P87">
-        <v>-1647.982693090966</v>
+        <v>-1457.481373090966</v>
       </c>
       <c r="Q87">
-        <v>-1221.882693090966</v>
+        <v>-1031.381373090966</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1802611382787829</v>
+        <v>0.1794546240690029</v>
       </c>
       <c r="T87">
-        <v>2.763227064466886</v>
+        <v>2.748079744787928</v>
       </c>
       <c r="U87">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V87">
-        <v>0.08190494221392793</v>
+        <v>0.08790507733242546</v>
       </c>
       <c r="W87">
-        <v>0.2017584990821297</v>
+        <v>0.1867584990821297</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4095247110696396</v>
+        <v>0.4395253866621273</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2002734724060446</v>
+        <v>0.1872524952745775</v>
       </c>
       <c r="C88">
-        <v>-6387.64448319515</v>
+        <v>-6054.76577812237</v>
       </c>
       <c r="D88">
-        <v>4962.031516804849</v>
+        <v>5294.910221877628</v>
       </c>
       <c r="E88">
         <v>9939.875999999998</v>
@@ -8509,37 +8509,37 @@
         <v>1428.7</v>
       </c>
       <c r="M88">
-        <v>3529.721641262104</v>
+        <v>3288.793501262104</v>
       </c>
       <c r="N88">
-        <v>-2101.021641262104</v>
+        <v>-1860.093501262104</v>
       </c>
       <c r="O88">
-        <v>-420.2043282524209</v>
+        <v>-372.0187002524209</v>
       </c>
       <c r="P88">
-        <v>-1680.817313009683</v>
+        <v>-1488.074801009684</v>
       </c>
       <c r="Q88">
-        <v>-1254.717313009683</v>
+        <v>-1061.974801009684</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.189865505298696</v>
+        <v>0.1890013829310745</v>
       </c>
       <c r="T88">
-        <v>2.960600426214521</v>
+        <v>2.944371155129923</v>
       </c>
       <c r="U88">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V88">
-        <v>0.08095255916492877</v>
+        <v>0.08688292527042051</v>
       </c>
       <c r="W88">
-        <v>0.2019677926328223</v>
+        <v>0.1869677926328222</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4047627958246438</v>
+        <v>0.4344146263521025</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2020130498504615</v>
+        <v>0.1888420727189944</v>
       </c>
       <c r="C89">
-        <v>-6615.776340805312</v>
+        <v>-6284.581725627731</v>
       </c>
       <c r="D89">
-        <v>4920.665659194687</v>
+        <v>5251.860274372267</v>
       </c>
       <c r="E89">
         <v>10126.642</v>
@@ -8591,37 +8591,37 @@
         <v>1428.7</v>
       </c>
       <c r="M89">
-        <v>3570.764916160501</v>
+        <v>3327.035286160501</v>
       </c>
       <c r="N89">
-        <v>-2142.064916160501</v>
+        <v>-1898.335286160501</v>
       </c>
       <c r="O89">
-        <v>-428.4129832321003</v>
+        <v>-379.6670572321002</v>
       </c>
       <c r="P89">
-        <v>-1713.651932928401</v>
+        <v>-1518.668228928401</v>
       </c>
       <c r="Q89">
-        <v>-1287.551932928401</v>
+        <v>-1092.5682289284</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2009474672447495</v>
+        <v>0.2000168739257726</v>
       </c>
       <c r="T89">
-        <v>3.188338920538714</v>
+        <v>3.170861243986071</v>
       </c>
       <c r="U89">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V89">
-        <v>0.08002206997912499</v>
+        <v>0.08588427095696739</v>
       </c>
       <c r="W89">
-        <v>0.2021722748375219</v>
+        <v>0.1871722748375219</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4001103498956249</v>
+        <v>0.4294213547848369</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2037526272948784</v>
+        <v>0.1904316501634113</v>
       </c>
       <c r="C90">
-        <v>-6843.224209498434</v>
+        <v>-6513.703288790985</v>
       </c>
       <c r="D90">
-        <v>4879.983790501566</v>
+        <v>5209.504711209014</v>
       </c>
       <c r="E90">
         <v>10313.408</v>
@@ -8673,37 +8673,37 @@
         <v>1428.7</v>
       </c>
       <c r="M90">
-        <v>3611.808191058898</v>
+        <v>3365.277071058897</v>
       </c>
       <c r="N90">
-        <v>-2183.108191058898</v>
+        <v>-1936.577071058898</v>
       </c>
       <c r="O90">
-        <v>-436.6216382117796</v>
+        <v>-387.3154142117796</v>
       </c>
       <c r="P90">
-        <v>-1746.486552847118</v>
+        <v>-1549.261656847118</v>
       </c>
       <c r="Q90">
-        <v>-1320.386552847118</v>
+        <v>-1123.161656847118</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2138764228484787</v>
+        <v>0.2128682800862536</v>
       </c>
       <c r="T90">
-        <v>3.454033830583608</v>
+        <v>3.43509968098491</v>
       </c>
       <c r="U90">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V90">
-        <v>0.07911272827481675</v>
+        <v>0.08490831333245639</v>
       </c>
       <c r="W90">
-        <v>0.2023721097193874</v>
+        <v>0.1873721097193874</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3955636413740837</v>
+        <v>0.4245415666622819</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2054922047392953</v>
+        <v>0.1920212276078282</v>
       </c>
       <c r="C91">
-        <v>-7070.004914913407</v>
+        <v>-6742.147133558945</v>
       </c>
       <c r="D91">
-        <v>4839.969085086593</v>
+        <v>5167.826866441055</v>
       </c>
       <c r="E91">
         <v>10500.174</v>
@@ -8755,37 +8755,37 @@
         <v>1428.7</v>
       </c>
       <c r="M91">
-        <v>3652.851465957294</v>
+        <v>3403.518855957294</v>
       </c>
       <c r="N91">
-        <v>-2224.151465957294</v>
+        <v>-1974.818855957294</v>
       </c>
       <c r="O91">
-        <v>-444.8302931914588</v>
+        <v>-394.9637711914588</v>
       </c>
       <c r="P91">
-        <v>-1779.321172765835</v>
+        <v>-1579.855084765835</v>
       </c>
       <c r="Q91">
-        <v>-1353.221172765835</v>
+        <v>-1153.755084765835</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2291560976528859</v>
+        <v>0.2280563055486403</v>
       </c>
       <c r="T91">
-        <v>3.768036906091209</v>
+        <v>3.747381470165357</v>
       </c>
       <c r="U91">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V91">
-        <v>0.07822382121554916</v>
+        <v>0.08395428733995688</v>
       </c>
       <c r="W91">
-        <v>0.2025674539297504</v>
+        <v>0.1875674539297504</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3911191060777457</v>
+        <v>0.4197714366997845</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2072317821837122</v>
+        <v>0.1936108050522451</v>
       </c>
       <c r="C92">
-        <v>-7296.134735312551</v>
+        <v>-6969.929396777992</v>
       </c>
       <c r="D92">
-        <v>4800.605264687448</v>
+        <v>5126.810603222008</v>
       </c>
       <c r="E92">
         <v>10686.94</v>
@@ -8837,37 +8837,37 @@
         <v>1428.7</v>
       </c>
       <c r="M92">
-        <v>3693.894740855691</v>
+        <v>3441.76064085569</v>
       </c>
       <c r="N92">
-        <v>-2265.194740855691</v>
+        <v>-2013.060640855691</v>
       </c>
       <c r="O92">
-        <v>-453.0389481711381</v>
+        <v>-402.6121281711381</v>
       </c>
       <c r="P92">
-        <v>-1812.155792684553</v>
+        <v>-1610.448512684552</v>
       </c>
       <c r="Q92">
-        <v>-1386.055792684553</v>
+        <v>-1184.348512684553</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2474917074181744</v>
+        <v>0.2462819361035044</v>
       </c>
       <c r="T92">
-        <v>4.144840596700329</v>
+        <v>4.122119617181893</v>
       </c>
       <c r="U92">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V92">
-        <v>0.07735466764648749</v>
+        <v>0.08302146192506848</v>
       </c>
       <c r="W92">
-        <v>0.2027584571576608</v>
+        <v>0.1877584571576608</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3867733382324374</v>
+        <v>0.4151073096253424</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2089713596281291</v>
+        <v>0.1952003824966621</v>
       </c>
       <c r="C93">
-        <v>-7521.629423661301</v>
+        <v>-7197.065707025686</v>
       </c>
       <c r="D93">
-        <v>4761.876576338697</v>
+        <v>5086.440292974313</v>
       </c>
       <c r="E93">
         <v>10873.706</v>
@@ -8919,37 +8919,37 @@
         <v>1428.7</v>
       </c>
       <c r="M93">
-        <v>3734.938015754087</v>
+        <v>3480.002425754087</v>
       </c>
       <c r="N93">
-        <v>-2306.238015754087</v>
+        <v>-2051.302425754087</v>
       </c>
       <c r="O93">
-        <v>-461.2476031508175</v>
+        <v>-410.2604851508174</v>
       </c>
       <c r="P93">
-        <v>-1844.99041260327</v>
+        <v>-1641.041940603269</v>
       </c>
       <c r="Q93">
-        <v>-1418.89041260327</v>
+        <v>-1214.941940603269</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.269901897131305</v>
+        <v>0.2685577067816715</v>
       </c>
       <c r="T93">
-        <v>4.605378440778145</v>
+        <v>4.580132907979881</v>
       </c>
       <c r="U93">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V93">
-        <v>0.07650461635366895</v>
+        <v>0.08210913816765014</v>
       </c>
       <c r="W93">
-        <v>0.2029452625124304</v>
+        <v>0.1879452625124303</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3825230817683447</v>
+        <v>0.4105456908382508</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.210710937072546</v>
+        <v>0.196789959941079</v>
       </c>
       <c r="C94">
-        <v>-7746.50422864768</v>
+        <v>-7423.571204465861</v>
       </c>
       <c r="D94">
-        <v>4723.767771352318</v>
+        <v>5046.700795534138</v>
       </c>
       <c r="E94">
         <v>11060.472</v>
@@ -9001,37 +9001,37 @@
         <v>1428.7</v>
       </c>
       <c r="M94">
-        <v>3775.981290652483</v>
+        <v>3518.244210652483</v>
       </c>
       <c r="N94">
-        <v>-2347.281290652484</v>
+        <v>-2089.544210652483</v>
       </c>
       <c r="O94">
-        <v>-469.4562581304967</v>
+        <v>-417.9088421304967</v>
       </c>
       <c r="P94">
-        <v>-1877.825032521987</v>
+        <v>-1671.635368521987</v>
       </c>
       <c r="Q94">
-        <v>-1451.725032521987</v>
+        <v>-1245.535368521987</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.2979146342727182</v>
+        <v>0.2964024201293806</v>
       </c>
       <c r="T94">
-        <v>5.181050745875415</v>
+        <v>5.152649521477368</v>
       </c>
       <c r="U94">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V94">
-        <v>0.07567304443678124</v>
+        <v>0.08121664753539309</v>
       </c>
       <c r="W94">
-        <v>0.2031280068812266</v>
+        <v>0.1881280068812266</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3783652221839062</v>
+        <v>0.4060832376769654</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2124505145169628</v>
+        <v>0.1983795373854958</v>
       </c>
       <c r="C95">
-        <v>-7970.77391470052</v>
+        <v>-7649.46055978018</v>
       </c>
       <c r="D95">
-        <v>4686.264085299483</v>
+        <v>5007.577440219821</v>
       </c>
       <c r="E95">
         <v>11247.238</v>
@@ -9083,37 +9083,37 @@
         <v>1428.7</v>
       </c>
       <c r="M95">
-        <v>3817.024565550881</v>
+        <v>3556.48599555088</v>
       </c>
       <c r="N95">
-        <v>-2388.324565550881</v>
+        <v>-2127.785995550881</v>
       </c>
       <c r="O95">
-        <v>-477.6649131101762</v>
+        <v>-425.5571991101762</v>
       </c>
       <c r="P95">
-        <v>-1910.659652440705</v>
+        <v>-1702.228796440705</v>
       </c>
       <c r="Q95">
-        <v>-1484.559652440705</v>
+        <v>-1276.128796440705</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3339310105973922</v>
+        <v>0.3322027658621493</v>
       </c>
       <c r="T95">
-        <v>5.921200852429045</v>
+        <v>5.88874231025985</v>
       </c>
       <c r="U95">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V95">
-        <v>0.07485935578692336</v>
+        <v>0.08034335025006627</v>
       </c>
       <c r="W95">
-        <v>0.2033068212635972</v>
+        <v>0.1883068212635972</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3742967789346169</v>
+        <v>0.4017167512503312</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2141900919613798</v>
+        <v>0.1999691148299127</v>
       </c>
       <c r="C96">
-        <v>-8194.45278106154</v>
+        <v>-7874.74799222589</v>
       </c>
       <c r="D96">
-        <v>4649.351218938462</v>
+        <v>4969.05600777411</v>
       </c>
       <c r="E96">
         <v>11434.004</v>
@@ -9165,37 +9165,37 @@
         <v>1428.7</v>
       </c>
       <c r="M96">
-        <v>3858.067840449277</v>
+        <v>3594.727780449277</v>
       </c>
       <c r="N96">
-        <v>-2429.367840449278</v>
+        <v>-2166.027780449277</v>
       </c>
       <c r="O96">
-        <v>-485.8735680898556</v>
+        <v>-433.2055560898555</v>
       </c>
       <c r="P96">
-        <v>-1943.494272359422</v>
+        <v>-1732.822224359422</v>
       </c>
       <c r="Q96">
-        <v>-1517.394272359422</v>
+        <v>-1306.722224359421</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.3819528456969578</v>
+        <v>0.3799365601725075</v>
       </c>
       <c r="T96">
-        <v>6.908067661167222</v>
+        <v>6.870199361969827</v>
       </c>
       <c r="U96">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V96">
-        <v>0.07406297966153057</v>
+        <v>0.07948863375804428</v>
       </c>
       <c r="W96">
-        <v>0.2034818310846407</v>
+        <v>0.1884818310846407</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3703148983076529</v>
+        <v>0.3974431687902213</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2159296694057967</v>
+        <v>0.2015586922743296</v>
       </c>
       <c r="C97">
-        <v>-8417.554679963188</v>
+        <v>-8099.447286866493</v>
       </c>
       <c r="D97">
-        <v>4613.015320036811</v>
+        <v>4931.122713133508</v>
       </c>
       <c r="E97">
         <v>11620.77</v>
@@ -9247,37 +9247,37 @@
         <v>1428.7</v>
       </c>
       <c r="M97">
-        <v>3899.111115347674</v>
+        <v>3632.969565347673</v>
       </c>
       <c r="N97">
-        <v>-2470.411115347674</v>
+        <v>-2204.269565347674</v>
       </c>
       <c r="O97">
-        <v>-494.0822230695348</v>
+        <v>-440.8539130695347</v>
       </c>
       <c r="P97">
-        <v>-1976.328892278139</v>
+        <v>-1763.415652278139</v>
       </c>
       <c r="Q97">
-        <v>-1550.228892278139</v>
+        <v>-1337.315652278139</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4491834148363494</v>
+        <v>0.4467638722070092</v>
       </c>
       <c r="T97">
-        <v>8.28968119340067</v>
+        <v>8.244239234363796</v>
       </c>
       <c r="U97">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V97">
-        <v>0.07328336934930393</v>
+        <v>0.07865191129743329</v>
       </c>
       <c r="W97">
-        <v>0.2036531564883992</v>
+        <v>0.1886531564883991</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3664168467465196</v>
+        <v>0.3932595564871665</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2176692468502135</v>
+        <v>0.2031482697187465</v>
       </c>
       <c r="C98">
-        <v>-8640.093033960622</v>
+        <v>-8323.571811019123</v>
       </c>
       <c r="D98">
-        <v>4577.242966039375</v>
+        <v>4893.764188980873</v>
       </c>
       <c r="E98">
         <v>11807.536</v>
@@ -9329,37 +9329,37 @@
         <v>1428.7</v>
       </c>
       <c r="M98">
-        <v>3940.154390246069</v>
+        <v>3671.211350246069</v>
       </c>
       <c r="N98">
-        <v>-2511.45439024607</v>
+        <v>-2242.511350246069</v>
       </c>
       <c r="O98">
-        <v>-502.2908780492139</v>
+        <v>-448.5022700492139</v>
       </c>
       <c r="P98">
-        <v>-2009.163512196856</v>
+        <v>-1794.009080196856</v>
       </c>
       <c r="Q98">
-        <v>-1583.063512196856</v>
+        <v>-1367.909080196855</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.5500292685454355</v>
+        <v>0.5470048402587604</v>
       </c>
       <c r="T98">
-        <v>10.36210149175081</v>
+        <v>10.30529904295472</v>
       </c>
       <c r="U98">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V98">
-        <v>0.07252000091858203</v>
+        <v>0.07783262055475171</v>
       </c>
       <c r="W98">
-        <v>0.2038209126129126</v>
+        <v>0.1888209126129126</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3626000045929101</v>
+        <v>0.3891631027737585</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2194088242946304</v>
+        <v>0.2047378471631634</v>
       </c>
       <c r="C99">
-        <v>-8862.080852463543</v>
+        <v>-8547.134529959987</v>
       </c>
       <c r="D99">
-        <v>4542.021147536456</v>
+        <v>4856.967470040013</v>
       </c>
       <c r="E99">
         <v>11994.302</v>
@@ -9411,37 +9411,37 @@
         <v>1428.7</v>
       </c>
       <c r="M99">
-        <v>3981.197665144467</v>
+        <v>3709.453135144467</v>
       </c>
       <c r="N99">
-        <v>-2552.497665144467</v>
+        <v>-2280.753135144467</v>
       </c>
       <c r="O99">
-        <v>-510.4995330288934</v>
+        <v>-456.1506270288934</v>
       </c>
       <c r="P99">
-        <v>-2041.998132115573</v>
+        <v>-1824.602508115574</v>
       </c>
       <c r="Q99">
-        <v>-1615.898132115573</v>
+        <v>-1398.502508115574</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7181056913939142</v>
+        <v>0.7140731203450139</v>
       </c>
       <c r="T99">
-        <v>13.81613532233442</v>
+        <v>13.74039872393963</v>
       </c>
       <c r="U99">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V99">
-        <v>0.07177237204313272</v>
+        <v>0.0770302224047027</v>
       </c>
       <c r="W99">
-        <v>0.2039852098482608</v>
+        <v>0.1889852098482608</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3588618602156636</v>
+        <v>0.3851511120235135</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2211484017390473</v>
+        <v>0.2063274246075803</v>
       </c>
       <c r="C100">
-        <v>-9083.530747510526</v>
+        <v>-8770.14802192643</v>
       </c>
       <c r="D100">
-        <v>4507.337252489474</v>
+        <v>4820.719978073568</v>
       </c>
       <c r="E100">
         <v>12181.068</v>
@@ -9493,37 +9493,37 @@
         <v>1428.7</v>
       </c>
       <c r="M100">
-        <v>4022.240940042863</v>
+        <v>3747.694920042863</v>
       </c>
       <c r="N100">
-        <v>-2593.540940042863</v>
+        <v>-2318.994920042863</v>
       </c>
       <c r="O100">
-        <v>-518.7081880085727</v>
+        <v>-463.7989840085727</v>
       </c>
       <c r="P100">
-        <v>-2074.832752034291</v>
+        <v>-1855.195936034291</v>
       </c>
       <c r="Q100">
-        <v>-1648.732752034291</v>
+        <v>-1429.09593603429</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.054258537090871</v>
+        <v>1.048209680517521</v>
       </c>
       <c r="T100">
-        <v>20.72420298350163</v>
+        <v>20.61059808590944</v>
       </c>
       <c r="U100">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V100">
-        <v>0.07104000089983545</v>
+        <v>0.07624419972710371</v>
       </c>
       <c r="W100">
-        <v>0.204146154078806</v>
+        <v>0.189146154078806</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3552000044991772</v>
+        <v>0.3812209986355185</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2228879791834642</v>
+        <v>0.2079170020519972</v>
       </c>
       <c r="C101">
-        <v>-9304.454948826125</v>
+        <v>-8992.624492452347</v>
       </c>
       <c r="D101">
-        <v>4473.179051173875</v>
+        <v>4785.009507547652</v>
       </c>
       <c r="E101">
         <v>12367.834</v>
@@ -9575,37 +9575,37 @@
         <v>1428.7</v>
       </c>
       <c r="M101">
-        <v>4063.28421494126</v>
+        <v>3785.936704941259</v>
       </c>
       <c r="N101">
-        <v>-2634.58421494126</v>
+        <v>-2357.23670494126</v>
       </c>
       <c r="O101">
-        <v>-526.9168429882519</v>
+        <v>-471.4473409882519</v>
       </c>
       <c r="P101">
-        <v>-2107.667371953008</v>
+        <v>-1885.789363953008</v>
       </c>
       <c r="Q101">
-        <v>-1681.567371953008</v>
+        <v>-1459.689363953008</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.062717074181742</v>
+        <v>2.050619361035042</v>
       </c>
       <c r="T101">
-        <v>41.44840596700325</v>
+        <v>41.22119617181889</v>
       </c>
       <c r="U101">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V101">
-        <v>0.07032242513317044</v>
+        <v>0.07547405629551679</v>
       </c>
       <c r="W101">
-        <v>0.2043038469107543</v>
+        <v>0.1893038469107543</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3516121256658522</v>
+        <v>0.377370281477584</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_power.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_power.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06746714808947185</v>
+        <v>0.06739987574882643</v>
       </c>
       <c r="C2">
-        <v>18562.54365853564</v>
+        <v>18388.35738163073</v>
       </c>
       <c r="D2">
-        <v>13850.34365853564</v>
+        <v>13862.92338163073</v>
       </c>
       <c r="E2">
-        <v>-6122</v>
+        <v>-5935.234</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>186.766</v>
       </c>
       <c r="G2">
         <v>4712.2</v>
@@ -1457,28 +1457,28 @@
         <v>1428.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>10.13350189839656</v>
       </c>
       <c r="N2">
-        <v>1428.7</v>
+        <v>1418.566498101603</v>
       </c>
       <c r="O2">
-        <v>285.74</v>
+        <v>283.7132996203206</v>
       </c>
       <c r="P2">
-        <v>1142.96</v>
+        <v>1134.853198481283</v>
       </c>
       <c r="Q2">
-        <v>1569.06</v>
+        <v>1560.953198481282</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06746714808947185</v>
+        <v>0.06764223615484133</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4490993646954171</v>
       </c>
       <c r="U2">
         <v>0.0542577444416894</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>140.9877862879825</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06739987574882643</v>
+        <v>0.06733260340818099</v>
       </c>
       <c r="C3">
-        <v>18388.35738163073</v>
+        <v>18214.19397683635</v>
       </c>
       <c r="D3">
-        <v>13862.92338163073</v>
+        <v>13875.52597683635</v>
       </c>
       <c r="E3">
-        <v>-5935.234</v>
+        <v>-5748.468</v>
       </c>
       <c r="F3">
-        <v>186.766</v>
+        <v>373.532</v>
       </c>
       <c r="G3">
         <v>4712.2</v>
@@ -1539,28 +1539,28 @@
         <v>1428.7</v>
       </c>
       <c r="M3">
-        <v>10.13350189839656</v>
+        <v>20.26700379679313</v>
       </c>
       <c r="N3">
-        <v>1418.566498101603</v>
+        <v>1408.432996203207</v>
       </c>
       <c r="O3">
-        <v>283.7132996203206</v>
+        <v>281.6865992406413</v>
       </c>
       <c r="P3">
-        <v>1134.853198481283</v>
+        <v>1126.746396962565</v>
       </c>
       <c r="Q3">
-        <v>1560.953198481282</v>
+        <v>1552.846396962565</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06764223615484133</v>
+        <v>0.06782089744603466</v>
       </c>
       <c r="T3">
-        <v>0.4490993646954171</v>
+        <v>0.4527728288866192</v>
       </c>
       <c r="U3">
         <v>0.0542577444416894</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>140.9877862879825</v>
+        <v>70.49389314399126</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06733260340818099</v>
+        <v>0.06726533106753557</v>
       </c>
       <c r="C4">
-        <v>18214.19397683635</v>
+        <v>18040.05350658744</v>
       </c>
       <c r="D4">
-        <v>13875.52597683635</v>
+        <v>13888.15150658744</v>
       </c>
       <c r="E4">
-        <v>-5748.468</v>
+        <v>-5561.702</v>
       </c>
       <c r="F4">
-        <v>373.532</v>
+        <v>560.2979999999999</v>
       </c>
       <c r="G4">
         <v>4712.2</v>
@@ -1621,28 +1621,28 @@
         <v>1428.7</v>
       </c>
       <c r="M4">
-        <v>20.26700379679313</v>
+        <v>30.40050569518968</v>
       </c>
       <c r="N4">
-        <v>1408.432996203207</v>
+        <v>1398.29949430481</v>
       </c>
       <c r="O4">
-        <v>281.6865992406413</v>
+        <v>279.6598988609621</v>
       </c>
       <c r="P4">
-        <v>1126.746396962565</v>
+        <v>1118.639595443848</v>
       </c>
       <c r="Q4">
-        <v>1552.846396962565</v>
+        <v>1544.739595443848</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06782089744603466</v>
+        <v>0.06800324247519074</v>
       </c>
       <c r="T4">
-        <v>0.4527728288866192</v>
+        <v>0.4565220346075368</v>
       </c>
       <c r="U4">
         <v>0.0542577444416894</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.49389314399126</v>
+        <v>46.99592876266085</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06726533106753557</v>
+        <v>0.06719805872689015</v>
       </c>
       <c r="C5">
-        <v>18040.05350658744</v>
+        <v>17865.93603354638</v>
       </c>
       <c r="D5">
-        <v>13888.15150658744</v>
+        <v>13900.80003354638</v>
       </c>
       <c r="E5">
-        <v>-5561.702</v>
+        <v>-5374.936</v>
       </c>
       <c r="F5">
-        <v>560.2979999999999</v>
+        <v>747.064</v>
       </c>
       <c r="G5">
         <v>4712.2</v>
@@ -1703,28 +1703,28 @@
         <v>1428.7</v>
       </c>
       <c r="M5">
-        <v>30.40050569518968</v>
+        <v>40.53400759358625</v>
       </c>
       <c r="N5">
-        <v>1398.29949430481</v>
+        <v>1388.165992406414</v>
       </c>
       <c r="O5">
-        <v>279.6598988609621</v>
+        <v>277.6331984812827</v>
       </c>
       <c r="P5">
-        <v>1118.639595443848</v>
+        <v>1110.532793925131</v>
       </c>
       <c r="Q5">
-        <v>1544.739595443848</v>
+        <v>1536.632793925131</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06800324247519074</v>
+        <v>0.06818938635912092</v>
       </c>
       <c r="T5">
-        <v>0.4565220346075368</v>
+        <v>0.4603493487809736</v>
       </c>
       <c r="U5">
         <v>0.0542577444416894</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.99592876266085</v>
+        <v>35.24694657199563</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06719805872689015</v>
+        <v>0.0671307863862447</v>
       </c>
       <c r="C6">
-        <v>17865.93603354638</v>
+        <v>17691.84162060404</v>
       </c>
       <c r="D6">
-        <v>13900.80003354638</v>
+        <v>13913.47162060404</v>
       </c>
       <c r="E6">
-        <v>-5374.936</v>
+        <v>-5188.17</v>
       </c>
       <c r="F6">
-        <v>747.064</v>
+        <v>933.8299999999999</v>
       </c>
       <c r="G6">
         <v>4712.2</v>
@@ -1785,28 +1785,28 @@
         <v>1428.7</v>
       </c>
       <c r="M6">
-        <v>40.53400759358625</v>
+        <v>50.66750949198281</v>
       </c>
       <c r="N6">
-        <v>1388.165992406414</v>
+        <v>1378.032490508017</v>
       </c>
       <c r="O6">
-        <v>277.6331984812827</v>
+        <v>275.6064981016034</v>
       </c>
       <c r="P6">
-        <v>1110.532793925131</v>
+        <v>1102.425992406414</v>
       </c>
       <c r="Q6">
-        <v>1536.632793925131</v>
+        <v>1528.525992406413</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06818938635912092</v>
+        <v>0.06837944906166013</v>
       </c>
       <c r="T6">
-        <v>0.4603493487809736</v>
+        <v>0.4642572379896405</v>
       </c>
       <c r="U6">
         <v>0.0542577444416894</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.24694657199563</v>
+        <v>28.1975572575965</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0671307863862447</v>
+        <v>0.06706351404559928</v>
       </c>
       <c r="C7">
-        <v>17691.84162060404</v>
+        <v>17517.77033088081</v>
       </c>
       <c r="D7">
-        <v>13913.47162060404</v>
+        <v>13926.16633088081</v>
       </c>
       <c r="E7">
-        <v>-5188.17</v>
+        <v>-5001.404</v>
       </c>
       <c r="F7">
-        <v>933.8299999999999</v>
+        <v>1120.596</v>
       </c>
       <c r="G7">
         <v>4712.2</v>
@@ -1867,28 +1867,28 @@
         <v>1428.7</v>
       </c>
       <c r="M7">
-        <v>50.66750949198281</v>
+        <v>60.80101139037938</v>
       </c>
       <c r="N7">
-        <v>1378.032490508017</v>
+        <v>1367.89898860962</v>
       </c>
       <c r="O7">
-        <v>275.6064981016034</v>
+        <v>273.5797977219241</v>
       </c>
       <c r="P7">
-        <v>1102.425992406414</v>
+        <v>1094.319190887696</v>
       </c>
       <c r="Q7">
-        <v>1528.525992406413</v>
+        <v>1520.419190887696</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06837944906166013</v>
+        <v>0.06857355565148744</v>
       </c>
       <c r="T7">
-        <v>0.4642572379896405</v>
+        <v>0.4682482737772155</v>
       </c>
       <c r="U7">
         <v>0.0542577444416894</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.1975572575965</v>
+        <v>23.49796438133042</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06706351404559928</v>
+        <v>0.06699624170495386</v>
       </c>
       <c r="C8">
-        <v>17517.77033088081</v>
+        <v>17343.72222772766</v>
       </c>
       <c r="D8">
-        <v>13926.16633088081</v>
+        <v>13938.88422772767</v>
       </c>
       <c r="E8">
-        <v>-5001.404</v>
+        <v>-4814.638</v>
       </c>
       <c r="F8">
-        <v>1120.596</v>
+        <v>1307.362</v>
       </c>
       <c r="G8">
         <v>4712.2</v>
@@ -1949,28 +1949,28 @@
         <v>1428.7</v>
       </c>
       <c r="M8">
-        <v>60.80101139037937</v>
+        <v>70.93451328877593</v>
       </c>
       <c r="N8">
-        <v>1367.89898860962</v>
+        <v>1357.765486711224</v>
       </c>
       <c r="O8">
-        <v>273.5797977219241</v>
+        <v>271.5530973422448</v>
       </c>
       <c r="P8">
-        <v>1094.319190887696</v>
+        <v>1086.212389368979</v>
       </c>
       <c r="Q8">
-        <v>1520.419190887696</v>
+        <v>1512.312389368979</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06857355565148744</v>
+        <v>0.06877183657657984</v>
       </c>
       <c r="T8">
-        <v>0.4682482737772155</v>
+        <v>0.4723251382914048</v>
       </c>
       <c r="U8">
         <v>0.0542577444416894</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.49796438133042</v>
+        <v>20.14111232685465</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06699624170495386</v>
+        <v>0.06692896936430842</v>
       </c>
       <c r="C9">
-        <v>17343.72222772766</v>
+        <v>17169.6973747272</v>
       </c>
       <c r="D9">
-        <v>13938.88422772767</v>
+        <v>13951.6253747272</v>
       </c>
       <c r="E9">
-        <v>-4814.638</v>
+        <v>-4627.872</v>
       </c>
       <c r="F9">
-        <v>1307.362</v>
+        <v>1494.128</v>
       </c>
       <c r="G9">
         <v>4712.2</v>
@@ -2031,28 +2031,28 @@
         <v>1428.7</v>
       </c>
       <c r="M9">
-        <v>70.93451328877595</v>
+        <v>81.06801518717251</v>
       </c>
       <c r="N9">
-        <v>1357.765486711224</v>
+        <v>1347.631984812827</v>
       </c>
       <c r="O9">
-        <v>271.5530973422448</v>
+        <v>269.5263969625655</v>
       </c>
       <c r="P9">
-        <v>1086.212389368979</v>
+        <v>1078.105587850262</v>
       </c>
       <c r="Q9">
-        <v>1512.312389368979</v>
+        <v>1504.205587850262</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06877183657657984</v>
+        <v>0.06897442795656554</v>
       </c>
       <c r="T9">
-        <v>0.4723251382914048</v>
+        <v>0.476490630295033</v>
       </c>
       <c r="U9">
         <v>0.0542577444416894</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.14111232685465</v>
+        <v>17.62347328599781</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06692896936430842</v>
+        <v>0.06686169702366299</v>
       </c>
       <c r="C10">
-        <v>17169.6973747272</v>
+        <v>16995.6958356947</v>
       </c>
       <c r="D10">
-        <v>13951.6253747272</v>
+        <v>13964.3898356947</v>
       </c>
       <c r="E10">
-        <v>-4627.872</v>
+        <v>-4441.106</v>
       </c>
       <c r="F10">
-        <v>1494.128</v>
+        <v>1680.894</v>
       </c>
       <c r="G10">
         <v>4712.2</v>
@@ -2113,28 +2113,28 @@
         <v>1428.7</v>
       </c>
       <c r="M10">
-        <v>81.06801518717251</v>
+        <v>91.20151708556905</v>
       </c>
       <c r="N10">
-        <v>1347.631984812827</v>
+        <v>1337.498482914431</v>
       </c>
       <c r="O10">
-        <v>269.5263969625655</v>
+        <v>267.4996965828861</v>
       </c>
       <c r="P10">
-        <v>1078.105587850262</v>
+        <v>1069.998786331545</v>
       </c>
       <c r="Q10">
-        <v>1504.205587850262</v>
+        <v>1496.098786331544</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06897442795656554</v>
+        <v>0.06918147189435314</v>
       </c>
       <c r="T10">
-        <v>0.476490630295033</v>
+        <v>0.4807476715734662</v>
       </c>
       <c r="U10">
         <v>0.0542577444416894</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.62347328599781</v>
+        <v>15.66530958755362</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06686169702366299</v>
+        <v>0.06679442468301758</v>
       </c>
       <c r="C11">
-        <v>16995.6958356947</v>
+        <v>16821.71767467922</v>
       </c>
       <c r="D11">
-        <v>13964.3898356947</v>
+        <v>13977.17767467922</v>
       </c>
       <c r="E11">
-        <v>-4441.106</v>
+        <v>-4254.34</v>
       </c>
       <c r="F11">
-        <v>1680.894</v>
+        <v>1867.66</v>
       </c>
       <c r="G11">
         <v>4712.2</v>
@@ -2195,28 +2195,28 @@
         <v>1428.7</v>
       </c>
       <c r="M11">
-        <v>91.20151708556905</v>
+        <v>101.3350189839656</v>
       </c>
       <c r="N11">
-        <v>1337.498482914431</v>
+        <v>1327.364981016034</v>
       </c>
       <c r="O11">
-        <v>267.4996965828861</v>
+        <v>265.4729962032068</v>
       </c>
       <c r="P11">
-        <v>1069.998786331545</v>
+        <v>1061.891984812827</v>
       </c>
       <c r="Q11">
-        <v>1496.098786331544</v>
+        <v>1487.991984812827</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06918147189435314</v>
+        <v>0.06939311680853602</v>
       </c>
       <c r="T11">
-        <v>0.4807476715734662</v>
+        <v>0.4850993137691979</v>
       </c>
       <c r="U11">
         <v>0.0542577444416894</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.66530958755362</v>
+        <v>14.09877862879825</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06679442468301758</v>
+        <v>0.06672715234237214</v>
       </c>
       <c r="C12">
-        <v>16821.71767467922</v>
+        <v>16647.76295596462</v>
       </c>
       <c r="D12">
-        <v>13977.17767467922</v>
+        <v>13989.98895596462</v>
       </c>
       <c r="E12">
-        <v>-4254.34</v>
+        <v>-4067.574</v>
       </c>
       <c r="F12">
-        <v>1867.66</v>
+        <v>2054.426</v>
       </c>
       <c r="G12">
         <v>4712.2</v>
@@ -2277,28 +2277,28 @@
         <v>1428.7</v>
       </c>
       <c r="M12">
-        <v>101.3350189839656</v>
+        <v>111.4685208823622</v>
       </c>
       <c r="N12">
-        <v>1327.364981016034</v>
+        <v>1317.231479117638</v>
       </c>
       <c r="O12">
-        <v>265.4729962032068</v>
+        <v>263.4462958235276</v>
       </c>
       <c r="P12">
-        <v>1061.891984812827</v>
+        <v>1053.78518329411</v>
       </c>
       <c r="Q12">
-        <v>1487.991984812827</v>
+        <v>1479.88518329411</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06939311680853602</v>
+        <v>0.06960951778820615</v>
       </c>
       <c r="T12">
-        <v>0.485099313769198</v>
+        <v>0.4895487456771933</v>
       </c>
       <c r="U12">
         <v>0.0542577444416894</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.09877862879825</v>
+        <v>12.81707148072569</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06672715234237214</v>
+        <v>0.06665988000172671</v>
       </c>
       <c r="C13">
-        <v>16647.76295596462</v>
+        <v>16473.83174407067</v>
       </c>
       <c r="D13">
-        <v>13989.98895596462</v>
+        <v>14002.82374407067</v>
       </c>
       <c r="E13">
-        <v>-4067.574</v>
+        <v>-3880.808</v>
       </c>
       <c r="F13">
-        <v>2054.426</v>
+        <v>2241.192</v>
       </c>
       <c r="G13">
         <v>4712.2</v>
@@ -2359,28 +2359,28 @@
         <v>1428.7</v>
       </c>
       <c r="M13">
-        <v>111.4685208823622</v>
+        <v>121.6020227807587</v>
       </c>
       <c r="N13">
-        <v>1317.231479117638</v>
+        <v>1307.097977219241</v>
       </c>
       <c r="O13">
-        <v>263.4462958235276</v>
+        <v>261.4195954438482</v>
       </c>
       <c r="P13">
-        <v>1053.78518329411</v>
+        <v>1045.678381775393</v>
       </c>
       <c r="Q13">
-        <v>1479.88518329411</v>
+        <v>1471.778381775393</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06960951778820615</v>
+        <v>0.06983083697195969</v>
       </c>
       <c r="T13">
-        <v>0.4895487456771933</v>
+        <v>0.4940993010376432</v>
       </c>
       <c r="U13">
         <v>0.0542577444416894</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.81707148072569</v>
+        <v>11.74898219066521</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06665988000172671</v>
+        <v>0.06659260766108129</v>
       </c>
       <c r="C14">
-        <v>16473.83174407067</v>
+        <v>16299.92410375413</v>
       </c>
       <c r="D14">
-        <v>14002.82374407067</v>
+        <v>14015.68210375413</v>
       </c>
       <c r="E14">
-        <v>-3880.808</v>
+        <v>-3694.042</v>
       </c>
       <c r="F14">
-        <v>2241.192</v>
+        <v>2427.958</v>
       </c>
       <c r="G14">
         <v>4712.2</v>
@@ -2441,28 +2441,28 @@
         <v>1428.7</v>
       </c>
       <c r="M14">
-        <v>121.6020227807587</v>
+        <v>131.7355246791553</v>
       </c>
       <c r="N14">
-        <v>1307.097977219241</v>
+        <v>1296.964475320844</v>
       </c>
       <c r="O14">
-        <v>261.4195954438482</v>
+        <v>259.3928950641689</v>
       </c>
       <c r="P14">
-        <v>1045.678381775393</v>
+        <v>1037.571580256676</v>
       </c>
       <c r="Q14">
-        <v>1471.778381775393</v>
+        <v>1463.671580256675</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06983083697195969</v>
+        <v>0.0700572439530409</v>
       </c>
       <c r="T14">
-        <v>0.4940993010376432</v>
+        <v>0.4987544668661493</v>
       </c>
       <c r="U14">
         <v>0.0542577444416894</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.74898219066521</v>
+        <v>10.84521432984481</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06659260766108129</v>
+        <v>0.06652533532043585</v>
       </c>
       <c r="C15">
-        <v>16299.92410375413</v>
+        <v>16126.04010000984</v>
       </c>
       <c r="D15">
-        <v>14015.68210375413</v>
+        <v>14028.56410000984</v>
       </c>
       <c r="E15">
-        <v>-3694.042</v>
+        <v>-3507.276</v>
       </c>
       <c r="F15">
-        <v>2427.958</v>
+        <v>2614.724</v>
       </c>
       <c r="G15">
         <v>4712.2</v>
@@ -2523,28 +2523,28 @@
         <v>1428.7</v>
       </c>
       <c r="M15">
-        <v>131.7355246791553</v>
+        <v>141.8690265775519</v>
       </c>
       <c r="N15">
-        <v>1296.964475320844</v>
+        <v>1286.830973422448</v>
       </c>
       <c r="O15">
-        <v>259.3928950641689</v>
+        <v>257.3661946844896</v>
       </c>
       <c r="P15">
-        <v>1037.571580256676</v>
+        <v>1029.464778737958</v>
       </c>
       <c r="Q15">
-        <v>1463.671580256675</v>
+        <v>1455.564778737958</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0700572439530409</v>
+        <v>0.07028891621275191</v>
       </c>
       <c r="T15">
-        <v>0.4987544668661493</v>
+        <v>0.5035178923650859</v>
       </c>
       <c r="U15">
         <v>0.0542577444416894</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.84521432984481</v>
+        <v>10.07055616342732</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06652533532043585</v>
+        <v>0.06645806297979043</v>
       </c>
       <c r="C16">
-        <v>16126.04010000984</v>
+        <v>15952.17979807179</v>
       </c>
       <c r="D16">
-        <v>14028.56410000984</v>
+        <v>14041.46979807179</v>
       </c>
       <c r="E16">
-        <v>-3507.276</v>
+        <v>-3320.51</v>
       </c>
       <c r="F16">
-        <v>2614.724</v>
+        <v>2801.49</v>
       </c>
       <c r="G16">
         <v>4712.2</v>
@@ -2605,28 +2605,28 @@
         <v>1428.7</v>
       </c>
       <c r="M16">
-        <v>141.8690265775519</v>
+        <v>152.0025284759485</v>
       </c>
       <c r="N16">
-        <v>1286.830973422448</v>
+        <v>1276.697471524051</v>
       </c>
       <c r="O16">
-        <v>257.3661946844896</v>
+        <v>255.3394943048103</v>
       </c>
       <c r="P16">
-        <v>1029.464778737958</v>
+        <v>1021.357977219241</v>
       </c>
       <c r="Q16">
-        <v>1455.564778737958</v>
+        <v>1447.457977219241</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07028891621275191</v>
+        <v>0.07052603958445611</v>
       </c>
       <c r="T16">
-        <v>0.5035178923650859</v>
+        <v>0.5083933984639973</v>
       </c>
       <c r="U16">
         <v>0.0542577444416894</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.07055616342732</v>
+        <v>9.399185752532167</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06645806297979043</v>
+        <v>0.06639079063914499</v>
       </c>
       <c r="C17">
-        <v>15952.17979807179</v>
+        <v>15778.34326341427</v>
       </c>
       <c r="D17">
-        <v>14041.46979807179</v>
+        <v>14054.39926341427</v>
       </c>
       <c r="E17">
-        <v>-3320.51</v>
+        <v>-3133.744</v>
       </c>
       <c r="F17">
-        <v>2801.49</v>
+        <v>2988.256</v>
       </c>
       <c r="G17">
         <v>4712.2</v>
@@ -2687,28 +2687,28 @@
         <v>1428.7</v>
       </c>
       <c r="M17">
-        <v>152.0025284759484</v>
+        <v>162.136030374345</v>
       </c>
       <c r="N17">
-        <v>1276.697471524051</v>
+        <v>1266.563969625655</v>
       </c>
       <c r="O17">
-        <v>255.3394943048103</v>
+        <v>253.312793925131</v>
       </c>
       <c r="P17">
-        <v>1021.357977219241</v>
+        <v>1013.251175700524</v>
       </c>
       <c r="Q17">
-        <v>1447.457977219241</v>
+        <v>1439.351175700524</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07052603958445611</v>
+        <v>0.07076880875072471</v>
       </c>
       <c r="T17">
-        <v>0.5083933984639973</v>
+        <v>0.5133849880414544</v>
       </c>
       <c r="U17">
         <v>0.0542577444416894</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.399185752532171</v>
+        <v>8.811736642998909</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06639079063914499</v>
+        <v>0.06652751829849957</v>
       </c>
       <c r="C18">
-        <v>15778.34326341427</v>
+        <v>15565.32370930132</v>
       </c>
       <c r="D18">
-        <v>14054.39926341427</v>
+        <v>14028.14570930132</v>
       </c>
       <c r="E18">
-        <v>-3133.744</v>
+        <v>-2946.978</v>
       </c>
       <c r="F18">
-        <v>2988.256</v>
+        <v>3175.022</v>
       </c>
       <c r="G18">
         <v>4712.2</v>
@@ -2769,45 +2769,45 @@
         <v>1428.7</v>
       </c>
       <c r="M18">
-        <v>162.136030374345</v>
+        <v>177.0320652727416</v>
       </c>
       <c r="N18">
-        <v>1266.563969625655</v>
+        <v>1251.667934727258</v>
       </c>
       <c r="O18">
-        <v>253.312793925131</v>
+        <v>250.3335869454517</v>
       </c>
       <c r="P18">
-        <v>1013.251175700524</v>
+        <v>1001.334347781807</v>
       </c>
       <c r="Q18">
-        <v>1439.351175700524</v>
+        <v>1427.434347781807</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07076880875072471</v>
+        <v>0.07101742777642145</v>
       </c>
       <c r="T18">
-        <v>0.5133849880414544</v>
+        <v>0.5184968568858381</v>
       </c>
       <c r="U18">
-        <v>0.0542577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04340619555335153</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.811736642998909</v>
+        <v>8.070289400956241</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06652751829849957</v>
+        <v>0.06647224595785414</v>
       </c>
       <c r="C19">
-        <v>15565.32370930132</v>
+        <v>15389.15892424694</v>
       </c>
       <c r="D19">
-        <v>14028.14570930132</v>
+        <v>14038.74692424694</v>
       </c>
       <c r="E19">
-        <v>-2946.978</v>
+        <v>-2760.212</v>
       </c>
       <c r="F19">
-        <v>3175.022</v>
+        <v>3361.788</v>
       </c>
       <c r="G19">
         <v>4712.2</v>
@@ -2851,28 +2851,28 @@
         <v>1428.7</v>
       </c>
       <c r="M19">
-        <v>177.0320652727416</v>
+        <v>187.4457161711381</v>
       </c>
       <c r="N19">
-        <v>1251.667934727258</v>
+        <v>1241.254283828862</v>
       </c>
       <c r="O19">
-        <v>250.3335869454517</v>
+        <v>248.2508567657723</v>
       </c>
       <c r="P19">
-        <v>1001.334347781807</v>
+        <v>993.0034270630892</v>
       </c>
       <c r="Q19">
-        <v>1427.434347781807</v>
+        <v>1419.103427063089</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07101742777642145</v>
+        <v>0.07127211068079374</v>
       </c>
       <c r="T19">
-        <v>0.5184968568858381</v>
+        <v>0.5237334054581336</v>
       </c>
       <c r="U19">
         <v>0.0557577444416894</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.070289400956241</v>
+        <v>7.621939989792006</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06647224595785413</v>
+        <v>0.06641697361720872</v>
       </c>
       <c r="C20">
-        <v>15389.15892424694</v>
+        <v>15213.01017420616</v>
       </c>
       <c r="D20">
-        <v>14038.74692424694</v>
+        <v>14049.36417420616</v>
       </c>
       <c r="E20">
-        <v>-2760.212</v>
+        <v>-2573.446</v>
       </c>
       <c r="F20">
-        <v>3361.788</v>
+        <v>3548.554</v>
       </c>
       <c r="G20">
         <v>4712.2</v>
@@ -2933,28 +2933,28 @@
         <v>1428.7</v>
       </c>
       <c r="M20">
-        <v>187.4457161711381</v>
+        <v>197.8593670695347</v>
       </c>
       <c r="N20">
-        <v>1241.254283828862</v>
+        <v>1230.840632930465</v>
       </c>
       <c r="O20">
-        <v>248.2508567657724</v>
+        <v>246.168126586093</v>
       </c>
       <c r="P20">
-        <v>993.0034270630895</v>
+        <v>984.6725063443721</v>
       </c>
       <c r="Q20">
-        <v>1419.103427063089</v>
+        <v>1410.772506344372</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07127211068079373</v>
+        <v>0.07153308205194064</v>
       </c>
       <c r="T20">
-        <v>0.5237334054581335</v>
+        <v>0.5290992515260414</v>
       </c>
       <c r="U20">
         <v>0.0557577444416894</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.621939989792009</v>
+        <v>7.220785253487164</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06641697361720872</v>
+        <v>0.0663617012765633</v>
       </c>
       <c r="C21">
-        <v>15213.01017420616</v>
+        <v>15036.87749558748</v>
       </c>
       <c r="D21">
-        <v>14049.36417420616</v>
+        <v>14059.99749558748</v>
       </c>
       <c r="E21">
-        <v>-2573.446</v>
+        <v>-2386.68</v>
       </c>
       <c r="F21">
-        <v>3548.554</v>
+        <v>3735.32</v>
       </c>
       <c r="G21">
         <v>4712.2</v>
@@ -3015,28 +3015,28 @@
         <v>1428.7</v>
       </c>
       <c r="M21">
-        <v>197.8593670695347</v>
+        <v>208.2730179679312</v>
       </c>
       <c r="N21">
-        <v>1230.840632930465</v>
+        <v>1220.426982032069</v>
       </c>
       <c r="O21">
-        <v>246.168126586093</v>
+        <v>244.0853964064137</v>
       </c>
       <c r="P21">
-        <v>984.6725063443721</v>
+        <v>976.3415856256548</v>
       </c>
       <c r="Q21">
-        <v>1410.772506344372</v>
+        <v>1402.441585625655</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07153308205194064</v>
+        <v>0.07180057770736623</v>
       </c>
       <c r="T21">
-        <v>0.5290992515260414</v>
+        <v>0.5345992437456467</v>
       </c>
       <c r="U21">
         <v>0.0557577444416894</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.220785253487164</v>
+        <v>6.859745990812806</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0663617012765633</v>
+        <v>0.06659202893591787</v>
       </c>
       <c r="C22">
-        <v>15036.87749558748</v>
+        <v>14805.90682308299</v>
       </c>
       <c r="D22">
-        <v>14059.99749558748</v>
+        <v>14015.79282308299</v>
       </c>
       <c r="E22">
-        <v>-2386.68</v>
+        <v>-2199.914</v>
       </c>
       <c r="F22">
-        <v>3735.32</v>
+        <v>3922.086</v>
       </c>
       <c r="G22">
         <v>4712.2</v>
@@ -3097,45 +3097,45 @@
         <v>1428.7</v>
       </c>
       <c r="M22">
-        <v>208.2730179679312</v>
+        <v>225.3542150663278</v>
       </c>
       <c r="N22">
-        <v>1220.426982032069</v>
+        <v>1203.345784933672</v>
       </c>
       <c r="O22">
-        <v>244.0853964064137</v>
+        <v>240.6691569867344</v>
       </c>
       <c r="P22">
-        <v>976.3415856256548</v>
+        <v>962.6766279469375</v>
       </c>
       <c r="Q22">
-        <v>1402.441585625655</v>
+        <v>1388.776627946937</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07180057770736623</v>
+        <v>0.07207484540470131</v>
       </c>
       <c r="T22">
-        <v>0.5345992437456467</v>
+        <v>0.5402384762746093</v>
       </c>
       <c r="U22">
-        <v>0.0557577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04460619555335152</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.859745990812806</v>
+        <v>6.33979710377059</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06659202893591787</v>
+        <v>0.06655035659527243</v>
       </c>
       <c r="C23">
-        <v>14805.90682308299</v>
+        <v>14627.11800534611</v>
       </c>
       <c r="D23">
-        <v>14015.79282308299</v>
+        <v>14023.77000534611</v>
       </c>
       <c r="E23">
-        <v>-2199.914000000001</v>
+        <v>-2013.148</v>
       </c>
       <c r="F23">
-        <v>3922.085999999999</v>
+        <v>4108.852</v>
       </c>
       <c r="G23">
         <v>4712.2</v>
@@ -3179,28 +3179,28 @@
         <v>1428.7</v>
       </c>
       <c r="M23">
-        <v>225.3542150663278</v>
+        <v>236.0853681647244</v>
       </c>
       <c r="N23">
-        <v>1203.345784933672</v>
+        <v>1192.614631835276</v>
       </c>
       <c r="O23">
-        <v>240.6691569867344</v>
+        <v>238.5229263670551</v>
       </c>
       <c r="P23">
-        <v>962.6766279469377</v>
+        <v>954.0917054682204</v>
       </c>
       <c r="Q23">
-        <v>1388.776627946938</v>
+        <v>1380.19170546822</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07207484540470131</v>
+        <v>0.07235614560709627</v>
       </c>
       <c r="T23">
-        <v>0.5402384762746093</v>
+        <v>0.5460223045094427</v>
       </c>
       <c r="U23">
         <v>0.0574577444416894</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.339797103770592</v>
+        <v>6.051624508144655</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06655035659527243</v>
+        <v>0.066508684254627</v>
       </c>
       <c r="C24">
-        <v>14627.11800534611</v>
+        <v>14448.33827331373</v>
       </c>
       <c r="D24">
-        <v>14023.77000534611</v>
+        <v>14031.75627331373</v>
       </c>
       <c r="E24">
-        <v>-2013.148</v>
+        <v>-1826.382000000001</v>
       </c>
       <c r="F24">
-        <v>4108.852</v>
+        <v>4295.617999999999</v>
       </c>
       <c r="G24">
         <v>4712.2</v>
@@ -3261,28 +3261,28 @@
         <v>1428.7</v>
       </c>
       <c r="M24">
-        <v>236.0853681647244</v>
+        <v>246.8165212631209</v>
       </c>
       <c r="N24">
-        <v>1192.614631835276</v>
+        <v>1181.883478736879</v>
       </c>
       <c r="O24">
-        <v>238.5229263670551</v>
+        <v>236.3766957473758</v>
       </c>
       <c r="P24">
-        <v>954.0917054682204</v>
+        <v>945.5067829895031</v>
       </c>
       <c r="Q24">
-        <v>1380.19170546822</v>
+        <v>1371.606782989503</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07235614560709627</v>
+        <v>0.07264475230825473</v>
       </c>
       <c r="T24">
-        <v>0.5460223045094427</v>
+        <v>0.5519563620490768</v>
       </c>
       <c r="U24">
         <v>0.0574577444416894</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.051624508144655</v>
+        <v>5.788510399094887</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.066508684254627</v>
+        <v>0.06662061191398157</v>
       </c>
       <c r="C25">
-        <v>14448.33827331373</v>
+        <v>14240.1425342802</v>
       </c>
       <c r="D25">
-        <v>14031.75627331373</v>
+        <v>14010.3265342802</v>
       </c>
       <c r="E25">
-        <v>-1826.382000000001</v>
+        <v>-1639.616</v>
       </c>
       <c r="F25">
-        <v>4295.617999999999</v>
+        <v>4482.384</v>
       </c>
       <c r="G25">
         <v>4712.2</v>
@@ -3343,45 +3343,45 @@
         <v>1428.7</v>
       </c>
       <c r="M25">
-        <v>246.8165212631209</v>
+        <v>261.1335815615175</v>
       </c>
       <c r="N25">
-        <v>1181.883478736879</v>
+        <v>1167.566418438482</v>
       </c>
       <c r="O25">
-        <v>236.3766957473758</v>
+        <v>233.5132836876965</v>
       </c>
       <c r="P25">
-        <v>945.5067829895031</v>
+        <v>934.0531347507858</v>
       </c>
       <c r="Q25">
-        <v>1371.606782989503</v>
+        <v>1360.153134750786</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07264475230825473</v>
+        <v>0.07294095392260158</v>
       </c>
       <c r="T25">
-        <v>0.5519563620490768</v>
+        <v>0.5580465789976489</v>
       </c>
       <c r="U25">
-        <v>0.0574577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04596619555335152</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>5.788510399094887</v>
+        <v>5.47114619060754</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06662061191398157</v>
+        <v>0.06658533957333615</v>
       </c>
       <c r="C26">
-        <v>14240.1425342802</v>
+        <v>14060.12273152385</v>
       </c>
       <c r="D26">
-        <v>14010.3265342802</v>
+        <v>14017.07273152385</v>
       </c>
       <c r="E26">
-        <v>-1639.616000000001</v>
+        <v>-1452.85</v>
       </c>
       <c r="F26">
-        <v>4482.383999999999</v>
+        <v>4669.15</v>
       </c>
       <c r="G26">
         <v>4712.2</v>
@@ -3425,28 +3425,28 @@
         <v>1428.7</v>
       </c>
       <c r="M26">
-        <v>261.1335815615175</v>
+        <v>272.0141474599141</v>
       </c>
       <c r="N26">
-        <v>1167.566418438482</v>
+        <v>1156.685852540086</v>
       </c>
       <c r="O26">
-        <v>233.5132836876965</v>
+        <v>231.3371705080172</v>
       </c>
       <c r="P26">
-        <v>934.0531347507858</v>
+        <v>925.3486820320686</v>
       </c>
       <c r="Q26">
-        <v>1360.153134750786</v>
+        <v>1351.448682032069</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07294095392260158</v>
+        <v>0.07324505424666435</v>
       </c>
       <c r="T26">
-        <v>0.5580465789976488</v>
+        <v>0.5642992017315159</v>
       </c>
       <c r="U26">
         <v>0.0582577444416894</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.47114619060754</v>
+        <v>5.252300342983238</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06658533957333615</v>
+        <v>0.0665500672326907</v>
       </c>
       <c r="C27">
-        <v>14060.12273152385</v>
+        <v>13880.10942870198</v>
       </c>
       <c r="D27">
-        <v>14017.07273152385</v>
+        <v>14023.82542870198</v>
       </c>
       <c r="E27">
-        <v>-1452.85</v>
+        <v>-1266.084</v>
       </c>
       <c r="F27">
-        <v>4669.15</v>
+        <v>4855.916</v>
       </c>
       <c r="G27">
         <v>4712.2</v>
@@ -3507,28 +3507,28 @@
         <v>1428.7</v>
       </c>
       <c r="M27">
-        <v>272.0141474599141</v>
+        <v>282.8947133583106</v>
       </c>
       <c r="N27">
-        <v>1156.685852540086</v>
+        <v>1145.805286641689</v>
       </c>
       <c r="O27">
-        <v>231.3371705080172</v>
+        <v>229.1610573283378</v>
       </c>
       <c r="P27">
-        <v>925.3486820320686</v>
+        <v>916.6442293133514</v>
       </c>
       <c r="Q27">
-        <v>1351.448682032069</v>
+        <v>1342.744229313351</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07324505424666435</v>
+        <v>0.07355737349840448</v>
       </c>
       <c r="T27">
-        <v>0.5642992017315159</v>
+        <v>0.5707208142690012</v>
       </c>
       <c r="U27">
         <v>0.0582577444416894</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.252300342983238</v>
+        <v>5.050288791330037</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0665500672326907</v>
+        <v>0.06651479489204529</v>
       </c>
       <c r="C28">
-        <v>13880.10942870198</v>
+        <v>13700.10263521309</v>
       </c>
       <c r="D28">
-        <v>14023.82542870198</v>
+        <v>14030.58463521309</v>
       </c>
       <c r="E28">
-        <v>-1266.084</v>
+        <v>-1079.318</v>
       </c>
       <c r="F28">
-        <v>4855.916</v>
+        <v>5042.682</v>
       </c>
       <c r="G28">
         <v>4712.2</v>
@@ -3589,28 +3589,28 @@
         <v>1428.7</v>
       </c>
       <c r="M28">
-        <v>282.8947133583106</v>
+        <v>293.7752792567072</v>
       </c>
       <c r="N28">
-        <v>1145.805286641689</v>
+        <v>1134.924720743293</v>
       </c>
       <c r="O28">
-        <v>229.1610573283378</v>
+        <v>226.9849441486585</v>
       </c>
       <c r="P28">
-        <v>916.6442293133514</v>
+        <v>907.9397765946342</v>
       </c>
       <c r="Q28">
-        <v>1342.744229313351</v>
+        <v>1334.039776594634</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07355737349840448</v>
+        <v>0.07387824944197312</v>
       </c>
       <c r="T28">
-        <v>0.5707208142690012</v>
+        <v>0.5773183613965547</v>
       </c>
       <c r="U28">
         <v>0.0582577444416894</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.050288791330037</v>
+        <v>4.863241058317814</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06651479489204529</v>
+        <v>0.06647952255139986</v>
       </c>
       <c r="C29">
-        <v>13700.10263521309</v>
+        <v>13520.10236047384</v>
       </c>
       <c r="D29">
-        <v>14030.58463521309</v>
+        <v>14037.35036047384</v>
       </c>
       <c r="E29">
-        <v>-1079.318</v>
+        <v>-892.5519999999997</v>
       </c>
       <c r="F29">
-        <v>5042.682</v>
+        <v>5229.448</v>
       </c>
       <c r="G29">
         <v>4712.2</v>
@@ -3671,28 +3671,28 @@
         <v>1428.7</v>
       </c>
       <c r="M29">
-        <v>293.7752792567072</v>
+        <v>304.6558451551037</v>
       </c>
       <c r="N29">
-        <v>1134.924720743293</v>
+        <v>1124.044154844896</v>
       </c>
       <c r="O29">
-        <v>226.9849441486585</v>
+        <v>224.8088309689792</v>
       </c>
       <c r="P29">
-        <v>907.9397765946342</v>
+        <v>899.2353238759169</v>
       </c>
       <c r="Q29">
-        <v>1334.039776594634</v>
+        <v>1325.335323875917</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07387824944197312</v>
+        <v>0.07420803860619643</v>
       </c>
       <c r="T29">
-        <v>0.5773183613965547</v>
+        <v>0.5840991737220955</v>
       </c>
       <c r="U29">
         <v>0.0582577444416894</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.863241058317814</v>
+        <v>4.689553877663606</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06647952255139986</v>
+        <v>0.06644425021075442</v>
       </c>
       <c r="C30">
-        <v>13520.10236047384</v>
+        <v>13340.10861391904</v>
       </c>
       <c r="D30">
-        <v>14037.35036047384</v>
+        <v>14044.12261391904</v>
       </c>
       <c r="E30">
-        <v>-892.5519999999997</v>
+        <v>-705.7860000000001</v>
       </c>
       <c r="F30">
-        <v>5229.448</v>
+        <v>5416.214</v>
       </c>
       <c r="G30">
         <v>4712.2</v>
@@ -3753,28 +3753,28 @@
         <v>1428.7</v>
       </c>
       <c r="M30">
-        <v>304.6558451551037</v>
+        <v>315.5364110535003</v>
       </c>
       <c r="N30">
-        <v>1124.044154844896</v>
+        <v>1113.163588946499</v>
       </c>
       <c r="O30">
-        <v>224.8088309689792</v>
+        <v>222.6327177892999</v>
       </c>
       <c r="P30">
-        <v>899.2353238759169</v>
+        <v>890.5308711571995</v>
       </c>
       <c r="Q30">
-        <v>1325.335323875917</v>
+        <v>1316.6308711572</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07420803860619643</v>
+        <v>0.07454711760603167</v>
       </c>
       <c r="T30">
-        <v>0.5840991737220955</v>
+        <v>0.591070994845539</v>
       </c>
       <c r="U30">
         <v>0.0582577444416894</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.689553877663606</v>
+        <v>4.527845123261412</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06644425021075442</v>
+        <v>0.06640897787010899</v>
       </c>
       <c r="C31">
-        <v>13340.10861391904</v>
+        <v>13160.12140500173</v>
       </c>
       <c r="D31">
-        <v>14044.12261391904</v>
+        <v>14050.90140500173</v>
       </c>
       <c r="E31">
-        <v>-705.786000000001</v>
+        <v>-519.0200000000004</v>
       </c>
       <c r="F31">
-        <v>5416.213999999999</v>
+        <v>5602.98</v>
       </c>
       <c r="G31">
         <v>4712.2</v>
@@ -3835,28 +3835,28 @@
         <v>1428.7</v>
       </c>
       <c r="M31">
-        <v>315.5364110535003</v>
+        <v>326.4169769518969</v>
       </c>
       <c r="N31">
-        <v>1113.1635889465</v>
+        <v>1102.283023048103</v>
       </c>
       <c r="O31">
-        <v>222.6327177892999</v>
+        <v>220.4566046096206</v>
       </c>
       <c r="P31">
-        <v>890.5308711571997</v>
+        <v>881.8264184384823</v>
       </c>
       <c r="Q31">
-        <v>1316.6308711572</v>
+        <v>1307.926418438482</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07454711760603167</v>
+        <v>0.07489588457729077</v>
       </c>
       <c r="T31">
-        <v>0.591070994845539</v>
+        <v>0.5982420108582238</v>
       </c>
       <c r="U31">
         <v>0.0582577444416894</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.527845123261413</v>
+        <v>4.376916952486033</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06640897787010899</v>
+        <v>0.06662170552946356</v>
       </c>
       <c r="C32">
-        <v>13160.12140500173</v>
+        <v>12932.57147288012</v>
       </c>
       <c r="D32">
-        <v>14050.90140500173</v>
+        <v>14010.11747288012</v>
       </c>
       <c r="E32">
-        <v>-519.0200000000004</v>
+        <v>-332.2540000000008</v>
       </c>
       <c r="F32">
-        <v>5602.98</v>
+        <v>5789.745999999999</v>
       </c>
       <c r="G32">
         <v>4712.2</v>
@@ -3917,45 +3917,45 @@
         <v>1428.7</v>
       </c>
       <c r="M32">
-        <v>326.4169769518969</v>
+        <v>343.0872888502934</v>
       </c>
       <c r="N32">
-        <v>1102.283023048103</v>
+        <v>1085.612711149706</v>
       </c>
       <c r="O32">
-        <v>220.4566046096206</v>
+        <v>217.1225422299413</v>
       </c>
       <c r="P32">
-        <v>881.8264184384823</v>
+        <v>868.4901689197652</v>
       </c>
       <c r="Q32">
-        <v>1307.926418438482</v>
+        <v>1294.590168919765</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07489588457729077</v>
+        <v>0.0752547607361226</v>
       </c>
       <c r="T32">
-        <v>0.5982420108582238</v>
+        <v>0.605620882407508</v>
       </c>
       <c r="U32">
-        <v>0.0582577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04660619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.376916952486033</v>
+        <v>4.164246378196236</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06662170552946356</v>
+        <v>0.06659443318881814</v>
       </c>
       <c r="C33">
-        <v>12932.57147288012</v>
+        <v>12751.02086272307</v>
       </c>
       <c r="D33">
-        <v>14010.11747288012</v>
+        <v>14015.33286272307</v>
       </c>
       <c r="E33">
-        <v>-332.2540000000008</v>
+        <v>-145.4880000000003</v>
       </c>
       <c r="F33">
-        <v>5789.745999999999</v>
+        <v>5976.512</v>
       </c>
       <c r="G33">
         <v>4712.2</v>
@@ -3999,28 +3999,28 @@
         <v>1428.7</v>
       </c>
       <c r="M33">
-        <v>343.0872888502934</v>
+        <v>354.15462074869</v>
       </c>
       <c r="N33">
-        <v>1085.612711149706</v>
+        <v>1074.54537925131</v>
       </c>
       <c r="O33">
-        <v>217.1225422299413</v>
+        <v>214.909075850262</v>
       </c>
       <c r="P33">
-        <v>868.4901689197652</v>
+        <v>859.6363034010479</v>
       </c>
       <c r="Q33">
-        <v>1294.590168919765</v>
+        <v>1285.736303401048</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0752547607361226</v>
+        <v>0.07562419207609655</v>
       </c>
       <c r="T33">
-        <v>0.605620882407508</v>
+        <v>0.6132167795905947</v>
       </c>
       <c r="U33">
         <v>0.0592577444416894</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.164246378196236</v>
+        <v>4.034113678877603</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06659443318881814</v>
+        <v>0.06656716084817271</v>
       </c>
       <c r="C34">
-        <v>12751.02086272307</v>
+        <v>12569.4741369618</v>
       </c>
       <c r="D34">
-        <v>14015.33286272307</v>
+        <v>14020.5521369618</v>
       </c>
       <c r="E34">
-        <v>-145.4880000000003</v>
+        <v>41.27800000000025</v>
       </c>
       <c r="F34">
-        <v>5976.512</v>
+        <v>6163.278</v>
       </c>
       <c r="G34">
         <v>4712.2</v>
@@ -4081,28 +4081,28 @@
         <v>1428.7</v>
       </c>
       <c r="M34">
-        <v>354.15462074869</v>
+        <v>365.2219526470866</v>
       </c>
       <c r="N34">
-        <v>1074.54537925131</v>
+        <v>1063.478047352913</v>
       </c>
       <c r="O34">
-        <v>214.909075850262</v>
+        <v>212.6956094705826</v>
       </c>
       <c r="P34">
-        <v>859.6363034010479</v>
+        <v>850.7824378823304</v>
       </c>
       <c r="Q34">
-        <v>1285.736303401048</v>
+        <v>1276.882437882331</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07562419207609655</v>
+        <v>0.07600465121726374</v>
       </c>
       <c r="T34">
-        <v>0.6132167795905947</v>
+        <v>0.6210394199731767</v>
       </c>
       <c r="U34">
         <v>0.0592577444416894</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.034113678877603</v>
+        <v>3.911867809820705</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06656716084817271</v>
+        <v>0.06653988850752728</v>
       </c>
       <c r="C35">
-        <v>12569.4741369618</v>
+        <v>12387.93129993754</v>
       </c>
       <c r="D35">
-        <v>14020.5521369618</v>
+        <v>14025.77529993754</v>
       </c>
       <c r="E35">
-        <v>41.27800000000025</v>
+        <v>228.0439999999999</v>
       </c>
       <c r="F35">
-        <v>6163.278</v>
+        <v>6350.044</v>
       </c>
       <c r="G35">
         <v>4712.2</v>
@@ -4163,28 +4163,28 @@
         <v>1428.7</v>
       </c>
       <c r="M35">
-        <v>365.2219526470866</v>
+        <v>376.2892845454831</v>
       </c>
       <c r="N35">
-        <v>1063.478047352913</v>
+        <v>1052.410715454517</v>
       </c>
       <c r="O35">
-        <v>212.6956094705826</v>
+        <v>210.4821430909034</v>
       </c>
       <c r="P35">
-        <v>850.7824378823304</v>
+        <v>841.9285723636134</v>
       </c>
       <c r="Q35">
-        <v>1276.882437882331</v>
+        <v>1268.028572363613</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07600465121726374</v>
+        <v>0.07639663942331479</v>
       </c>
       <c r="T35">
-        <v>0.6210394199731767</v>
+        <v>0.6290991100643216</v>
       </c>
       <c r="U35">
         <v>0.0592577444416894</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.911867809820705</v>
+        <v>3.796812874237744</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06653988850752728</v>
+        <v>0.06651261616688185</v>
       </c>
       <c r="C36">
-        <v>12387.93129993754</v>
+        <v>12206.39235599798</v>
       </c>
       <c r="D36">
-        <v>14025.77529993754</v>
+        <v>14031.00235599799</v>
       </c>
       <c r="E36">
-        <v>228.0439999999999</v>
+        <v>414.8100000000004</v>
       </c>
       <c r="F36">
-        <v>6350.044</v>
+        <v>6536.81</v>
       </c>
       <c r="G36">
         <v>4712.2</v>
@@ -4245,28 +4245,28 @@
         <v>1428.7</v>
       </c>
       <c r="M36">
-        <v>376.2892845454831</v>
+        <v>387.3566164438797</v>
       </c>
       <c r="N36">
-        <v>1052.410715454517</v>
+        <v>1041.34338355612</v>
       </c>
       <c r="O36">
-        <v>210.4821430909034</v>
+        <v>208.268676711224</v>
       </c>
       <c r="P36">
-        <v>841.9285723636134</v>
+        <v>833.074706844896</v>
       </c>
       <c r="Q36">
-        <v>1268.028572363613</v>
+        <v>1259.174706844896</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07639663942331479</v>
+        <v>0.07680068880493665</v>
       </c>
       <c r="T36">
-        <v>0.6290991100643216</v>
+        <v>0.6374067906198095</v>
       </c>
       <c r="U36">
         <v>0.0592577444416894</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.796812874237744</v>
+        <v>3.688332506402379</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06651261616688185</v>
+        <v>0.06648534382623641</v>
       </c>
       <c r="C37">
-        <v>12206.39235599798</v>
+        <v>12024.85730949733</v>
       </c>
       <c r="D37">
-        <v>14031.00235599799</v>
+        <v>14036.23330949733</v>
       </c>
       <c r="E37">
-        <v>414.8100000000004</v>
+        <v>601.576</v>
       </c>
       <c r="F37">
-        <v>6536.81</v>
+        <v>6723.576</v>
       </c>
       <c r="G37">
         <v>4712.2</v>
@@ -4327,28 +4327,28 @@
         <v>1428.7</v>
       </c>
       <c r="M37">
-        <v>387.3566164438797</v>
+        <v>398.4239483422763</v>
       </c>
       <c r="N37">
-        <v>1041.34338355612</v>
+        <v>1030.276051657724</v>
       </c>
       <c r="O37">
-        <v>208.268676711224</v>
+        <v>206.0552103315447</v>
       </c>
       <c r="P37">
-        <v>833.074706844896</v>
+        <v>824.220841326179</v>
       </c>
       <c r="Q37">
-        <v>1259.174706844896</v>
+        <v>1250.320841326179</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07680068880493665</v>
+        <v>0.07721736472973419</v>
       </c>
       <c r="T37">
-        <v>0.6374067906198095</v>
+        <v>0.6459740861926565</v>
       </c>
       <c r="U37">
         <v>0.0592577444416894</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.688332506402379</v>
+        <v>3.58587882566898</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06648534382623643</v>
+        <v>0.06645807148559099</v>
       </c>
       <c r="C38">
-        <v>12024.85730949733</v>
+        <v>11843.32616479626</v>
       </c>
       <c r="D38">
-        <v>14036.23330949733</v>
+        <v>14041.46816479626</v>
       </c>
       <c r="E38">
-        <v>601.5759999999991</v>
+        <v>788.3419999999996</v>
       </c>
       <c r="F38">
-        <v>6723.575999999999</v>
+        <v>6910.342</v>
       </c>
       <c r="G38">
         <v>4712.2</v>
@@ -4409,28 +4409,28 @@
         <v>1428.7</v>
       </c>
       <c r="M38">
-        <v>398.4239483422762</v>
+        <v>409.4912802406728</v>
       </c>
       <c r="N38">
-        <v>1030.276051657724</v>
+        <v>1019.208719759327</v>
       </c>
       <c r="O38">
-        <v>206.0552103315447</v>
+        <v>203.8417439518654</v>
       </c>
       <c r="P38">
-        <v>824.220841326179</v>
+        <v>815.3669758074617</v>
       </c>
       <c r="Q38">
-        <v>1250.320841326179</v>
+        <v>1241.466975807462</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07721736472973419</v>
+        <v>0.07764726846166815</v>
       </c>
       <c r="T38">
-        <v>0.6459740861926565</v>
+        <v>0.6548133594027367</v>
       </c>
       <c r="U38">
         <v>0.0592577444416894</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.58587882566898</v>
+        <v>3.488963181731981</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06645807148559099</v>
+        <v>0.06643079914494557</v>
       </c>
       <c r="C39">
-        <v>11843.32616479626</v>
+        <v>11661.79892626197</v>
       </c>
       <c r="D39">
-        <v>14041.46816479626</v>
+        <v>14046.70692626197</v>
       </c>
       <c r="E39">
-        <v>788.3419999999996</v>
+        <v>975.1079999999993</v>
       </c>
       <c r="F39">
-        <v>6910.342</v>
+        <v>7097.107999999999</v>
       </c>
       <c r="G39">
         <v>4712.2</v>
@@ -4491,28 +4491,28 @@
         <v>1428.7</v>
       </c>
       <c r="M39">
-        <v>409.4912802406728</v>
+        <v>420.5586121390693</v>
       </c>
       <c r="N39">
-        <v>1019.208719759327</v>
+        <v>1008.141387860931</v>
       </c>
       <c r="O39">
-        <v>203.8417439518654</v>
+        <v>201.6282775721861</v>
       </c>
       <c r="P39">
-        <v>815.3669758074617</v>
+        <v>806.5131102887444</v>
       </c>
       <c r="Q39">
-        <v>1241.466975807462</v>
+        <v>1232.613110288744</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07764726846166815</v>
+        <v>0.07809104005592256</v>
       </c>
       <c r="T39">
-        <v>0.6548133594027367</v>
+        <v>0.6639377704583032</v>
       </c>
       <c r="U39">
         <v>0.0592577444416894</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.488963181731981</v>
+        <v>3.397148361160086</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06643079914494557</v>
+        <v>0.06640352680430014</v>
       </c>
       <c r="C40">
-        <v>11661.79892626197</v>
+        <v>11480.27559826816</v>
       </c>
       <c r="D40">
-        <v>14046.70692626197</v>
+        <v>14051.94959826816</v>
       </c>
       <c r="E40">
-        <v>975.1079999999993</v>
+        <v>1161.874</v>
       </c>
       <c r="F40">
-        <v>7097.107999999999</v>
+        <v>7283.874</v>
       </c>
       <c r="G40">
         <v>4712.2</v>
@@ -4573,28 +4573,28 @@
         <v>1428.7</v>
       </c>
       <c r="M40">
-        <v>420.5586121390693</v>
+        <v>431.625944037466</v>
       </c>
       <c r="N40">
-        <v>1008.141387860931</v>
+        <v>997.0740559625339</v>
       </c>
       <c r="O40">
-        <v>201.6282775721861</v>
+        <v>199.4148111925068</v>
       </c>
       <c r="P40">
-        <v>806.5131102887444</v>
+        <v>797.659244770027</v>
       </c>
       <c r="Q40">
-        <v>1232.613110288744</v>
+        <v>1223.759244770027</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07809104005592256</v>
+        <v>0.07854936153851319</v>
       </c>
       <c r="T40">
-        <v>0.6639377704583032</v>
+        <v>0.6733613425320851</v>
       </c>
       <c r="U40">
         <v>0.0592577444416894</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.397148361160086</v>
+        <v>3.310041992925212</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06640352680430014</v>
+        <v>0.06637625446365472</v>
       </c>
       <c r="C41">
-        <v>11480.27559826816</v>
+        <v>11298.75618519508</v>
       </c>
       <c r="D41">
-        <v>14051.94959826816</v>
+        <v>14057.19618519508</v>
       </c>
       <c r="E41">
-        <v>1161.874</v>
+        <v>1348.639999999999</v>
       </c>
       <c r="F41">
-        <v>7283.874</v>
+        <v>7470.639999999999</v>
       </c>
       <c r="G41">
         <v>4712.2</v>
@@ -4655,28 +4655,28 @@
         <v>1428.7</v>
       </c>
       <c r="M41">
-        <v>431.625944037466</v>
+        <v>442.6932759358625</v>
       </c>
       <c r="N41">
-        <v>997.0740559625339</v>
+        <v>986.0067240641374</v>
       </c>
       <c r="O41">
-        <v>199.4148111925068</v>
+        <v>197.2013448128275</v>
       </c>
       <c r="P41">
-        <v>797.659244770027</v>
+        <v>788.8053792513099</v>
       </c>
       <c r="Q41">
-        <v>1223.759244770027</v>
+        <v>1214.90537925131</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07854936153851319</v>
+        <v>0.07902296040385684</v>
       </c>
       <c r="T41">
-        <v>0.6733613425320851</v>
+        <v>0.6830990336749931</v>
       </c>
       <c r="U41">
         <v>0.0592577444416894</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.310041992925212</v>
+        <v>3.227290943102082</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06637625446365472</v>
+        <v>0.06634898212300928</v>
       </c>
       <c r="C42">
-        <v>11298.75618519508</v>
+        <v>11117.24069142954</v>
       </c>
       <c r="D42">
-        <v>14057.19618519508</v>
+        <v>14062.44669142954</v>
       </c>
       <c r="E42">
-        <v>1348.639999999999</v>
+        <v>1535.406</v>
       </c>
       <c r="F42">
-        <v>7470.639999999999</v>
+        <v>7657.406</v>
       </c>
       <c r="G42">
         <v>4712.2</v>
@@ -4737,28 +4737,28 @@
         <v>1428.7</v>
       </c>
       <c r="M42">
-        <v>442.6932759358625</v>
+        <v>453.7606078342591</v>
       </c>
       <c r="N42">
-        <v>986.0067240641374</v>
+        <v>974.9393921657407</v>
       </c>
       <c r="O42">
-        <v>197.2013448128275</v>
+        <v>194.9878784331482</v>
       </c>
       <c r="P42">
-        <v>788.8053792513099</v>
+        <v>779.9515137325926</v>
       </c>
       <c r="Q42">
-        <v>1214.90537925131</v>
+        <v>1206.051513732593</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07902296040385684</v>
+        <v>0.0795126134680257</v>
       </c>
       <c r="T42">
-        <v>0.6830990336749931</v>
+        <v>0.6931668160430844</v>
       </c>
       <c r="U42">
         <v>0.0592577444416894</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.227290943102082</v>
+        <v>3.148576529855689</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06634898212300928</v>
+        <v>0.06632170978236385</v>
       </c>
       <c r="C43">
-        <v>11117.24069142954</v>
+        <v>10935.72912136485</v>
       </c>
       <c r="D43">
-        <v>14062.44669142954</v>
+        <v>14067.70112136485</v>
       </c>
       <c r="E43">
-        <v>1535.406</v>
+        <v>1722.172</v>
       </c>
       <c r="F43">
-        <v>7657.406</v>
+        <v>7844.172</v>
       </c>
       <c r="G43">
         <v>4712.2</v>
@@ -4819,28 +4819,28 @@
         <v>1428.7</v>
       </c>
       <c r="M43">
-        <v>453.7606078342591</v>
+        <v>464.8279397326556</v>
       </c>
       <c r="N43">
-        <v>974.9393921657407</v>
+        <v>963.8720602673442</v>
       </c>
       <c r="O43">
-        <v>194.9878784331482</v>
+        <v>192.7744120534688</v>
       </c>
       <c r="P43">
-        <v>779.9515137325926</v>
+        <v>771.0976482138753</v>
       </c>
       <c r="Q43">
-        <v>1206.051513732593</v>
+        <v>1197.197648213875</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0795126134680257</v>
+        <v>0.08001915112061417</v>
       </c>
       <c r="T43">
-        <v>0.6931668160430844</v>
+        <v>0.7035817633204202</v>
       </c>
       <c r="U43">
         <v>0.0592577444416894</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.148576529855689</v>
+        <v>3.073610422001983</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06632170978236385</v>
+        <v>0.06629443744171842</v>
       </c>
       <c r="C44">
-        <v>10935.72912136485</v>
+        <v>10754.22147940095</v>
       </c>
       <c r="D44">
-        <v>14067.70112136485</v>
+        <v>14072.95947940095</v>
       </c>
       <c r="E44">
-        <v>1722.171999999999</v>
+        <v>1908.937999999999</v>
       </c>
       <c r="F44">
-        <v>7844.171999999999</v>
+        <v>8030.937999999999</v>
       </c>
       <c r="G44">
         <v>4712.2</v>
@@ -4901,28 +4901,28 @@
         <v>1428.7</v>
       </c>
       <c r="M44">
-        <v>464.8279397326556</v>
+        <v>475.8952716310521</v>
       </c>
       <c r="N44">
-        <v>963.8720602673443</v>
+        <v>952.8047283689477</v>
       </c>
       <c r="O44">
-        <v>192.7744120534689</v>
+        <v>190.5609456737895</v>
       </c>
       <c r="P44">
-        <v>771.0976482138755</v>
+        <v>762.2437826951582</v>
       </c>
       <c r="Q44">
-        <v>1197.197648213875</v>
+        <v>1188.343782695158</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08001915112061415</v>
+        <v>0.08054346202417065</v>
       </c>
       <c r="T44">
-        <v>0.70358176332042</v>
+        <v>0.7143621473443291</v>
       </c>
       <c r="U44">
         <v>0.0592577444416894</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.073610422001983</v>
+        <v>3.002131109862402</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06629443744171842</v>
+        <v>0.06714716510107301</v>
       </c>
       <c r="C45">
-        <v>10754.22147940095</v>
+        <v>10404.88035759959</v>
       </c>
       <c r="D45">
-        <v>14072.95947940095</v>
+        <v>13910.38435759959</v>
       </c>
       <c r="E45">
-        <v>1908.937999999999</v>
+        <v>2095.704</v>
       </c>
       <c r="F45">
-        <v>8030.937999999999</v>
+        <v>8217.704</v>
       </c>
       <c r="G45">
         <v>4712.2</v>
@@ -4983,45 +4983,45 @@
         <v>1428.7</v>
       </c>
       <c r="M45">
-        <v>475.8952716310521</v>
+        <v>507.5068635294487</v>
       </c>
       <c r="N45">
-        <v>952.8047283689477</v>
+        <v>921.1931364705511</v>
       </c>
       <c r="O45">
-        <v>190.5609456737895</v>
+        <v>184.2386272941102</v>
       </c>
       <c r="P45">
-        <v>762.2437826951582</v>
+        <v>736.9545091764409</v>
       </c>
       <c r="Q45">
-        <v>1188.343782695158</v>
+        <v>1163.054509176441</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08054346202417065</v>
+        <v>0.08108649831713988</v>
       </c>
       <c r="T45">
-        <v>0.7143621473443291</v>
+        <v>0.7255275450833777</v>
       </c>
       <c r="U45">
-        <v>0.0592577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.04740619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.002131109862402</v>
+        <v>2.815134341364622</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06714716510107301</v>
+        <v>0.06713989276042757</v>
       </c>
       <c r="C46">
-        <v>10404.88035759959</v>
+        <v>10219.48496929729</v>
       </c>
       <c r="D46">
-        <v>13910.38435759959</v>
+        <v>13911.75496929729</v>
       </c>
       <c r="E46">
-        <v>2095.704</v>
+        <v>2282.469999999999</v>
       </c>
       <c r="F46">
-        <v>8217.704</v>
+        <v>8404.469999999999</v>
       </c>
       <c r="G46">
         <v>4712.2</v>
@@ -5065,28 +5065,28 @@
         <v>1428.7</v>
       </c>
       <c r="M46">
-        <v>507.5068635294487</v>
+        <v>519.0411104278453</v>
       </c>
       <c r="N46">
-        <v>921.1931364705511</v>
+        <v>909.6588895721545</v>
       </c>
       <c r="O46">
-        <v>184.2386272941102</v>
+        <v>181.9317779144309</v>
       </c>
       <c r="P46">
-        <v>736.9545091764409</v>
+        <v>727.7271116577236</v>
       </c>
       <c r="Q46">
-        <v>1163.054509176441</v>
+        <v>1153.827111657724</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08108649831713988</v>
+        <v>0.08164928138439888</v>
       </c>
       <c r="T46">
-        <v>0.7255275450833777</v>
+        <v>0.7370989572856644</v>
       </c>
       <c r="U46">
         <v>0.0617577444416894</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.815134341364622</v>
+        <v>2.752575800445408</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06713989276042757</v>
+        <v>0.06713262041978214</v>
       </c>
       <c r="C47">
-        <v>10219.48496929729</v>
+        <v>10034.08985111859</v>
       </c>
       <c r="D47">
-        <v>13911.75496929729</v>
+        <v>13913.12585111859</v>
       </c>
       <c r="E47">
-        <v>2282.469999999999</v>
+        <v>2469.235999999999</v>
       </c>
       <c r="F47">
-        <v>8404.469999999999</v>
+        <v>8591.235999999999</v>
       </c>
       <c r="G47">
         <v>4712.2</v>
@@ -5147,28 +5147,28 @@
         <v>1428.7</v>
       </c>
       <c r="M47">
-        <v>519.0411104278453</v>
+        <v>530.5753573262418</v>
       </c>
       <c r="N47">
-        <v>909.6588895721545</v>
+        <v>898.124642673758</v>
       </c>
       <c r="O47">
-        <v>181.9317779144309</v>
+        <v>179.6249285347516</v>
       </c>
       <c r="P47">
-        <v>727.7271116577236</v>
+        <v>718.4997141390064</v>
       </c>
       <c r="Q47">
-        <v>1153.827111657724</v>
+        <v>1144.599714139006</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08164928138439888</v>
+        <v>0.08223290826896379</v>
       </c>
       <c r="T47">
-        <v>0.7370989572856644</v>
+        <v>0.7490989403102581</v>
       </c>
       <c r="U47">
         <v>0.0617577444416894</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.752575800445408</v>
+        <v>2.6927371960879</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06713262041978214</v>
+        <v>0.06712534807913671</v>
       </c>
       <c r="C48">
-        <v>10034.08985111859</v>
+        <v>9848.695003143344</v>
       </c>
       <c r="D48">
-        <v>13913.12585111859</v>
+        <v>13914.49700314335</v>
       </c>
       <c r="E48">
-        <v>2469.235999999999</v>
+        <v>2656.002</v>
       </c>
       <c r="F48">
-        <v>8591.235999999999</v>
+        <v>8778.002</v>
       </c>
       <c r="G48">
         <v>4712.2</v>
@@ -5229,28 +5229,28 @@
         <v>1428.7</v>
       </c>
       <c r="M48">
-        <v>530.5753573262418</v>
+        <v>542.1096042246385</v>
       </c>
       <c r="N48">
-        <v>898.124642673758</v>
+        <v>886.5903957753613</v>
       </c>
       <c r="O48">
-        <v>179.6249285347516</v>
+        <v>177.3180791550723</v>
       </c>
       <c r="P48">
-        <v>718.4997141390064</v>
+        <v>709.2723166202891</v>
       </c>
       <c r="Q48">
-        <v>1144.599714139006</v>
+        <v>1135.372316620289</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08223290826896379</v>
+        <v>0.08283855880954999</v>
       </c>
       <c r="T48">
-        <v>0.7490989403102581</v>
+        <v>0.7615517528829496</v>
       </c>
       <c r="U48">
         <v>0.0617577444416894</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.6927371960879</v>
+        <v>2.635444915320071</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06712534807913671</v>
+        <v>0.0671180757384913</v>
       </c>
       <c r="C49">
-        <v>9848.695003143344</v>
+        <v>9663.30042545146</v>
       </c>
       <c r="D49">
-        <v>13914.49700314335</v>
+        <v>13915.86842545146</v>
       </c>
       <c r="E49">
-        <v>2656.002</v>
+        <v>2842.768</v>
       </c>
       <c r="F49">
-        <v>8778.002</v>
+        <v>8964.768</v>
       </c>
       <c r="G49">
         <v>4712.2</v>
@@ -5311,28 +5311,28 @@
         <v>1428.7</v>
       </c>
       <c r="M49">
-        <v>542.1096042246385</v>
+        <v>553.643851123035</v>
       </c>
       <c r="N49">
-        <v>886.5903957753613</v>
+        <v>875.0561488769648</v>
       </c>
       <c r="O49">
-        <v>177.3180791550723</v>
+        <v>175.011229775393</v>
       </c>
       <c r="P49">
-        <v>709.2723166202891</v>
+        <v>700.0449191015718</v>
       </c>
       <c r="Q49">
-        <v>1135.372316620289</v>
+        <v>1126.144919101572</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08283855880954999</v>
+        <v>0.08346750360169722</v>
       </c>
       <c r="T49">
-        <v>0.7615517528829496</v>
+        <v>0.77448351978536</v>
       </c>
       <c r="U49">
         <v>0.0617577444416894</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.635444915320071</v>
+        <v>2.58053981291757</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06711807573849128</v>
+        <v>0.06711080339784585</v>
       </c>
       <c r="C50">
-        <v>9663.300425451465</v>
+        <v>9477.906118122861</v>
       </c>
       <c r="D50">
-        <v>13915.86842545146</v>
+        <v>13917.24011812286</v>
       </c>
       <c r="E50">
-        <v>2842.767999999998</v>
+        <v>3029.534</v>
       </c>
       <c r="F50">
-        <v>8964.767999999998</v>
+        <v>9151.534</v>
       </c>
       <c r="G50">
         <v>4712.2</v>
@@ -5393,28 +5393,28 @@
         <v>1428.7</v>
       </c>
       <c r="M50">
-        <v>553.6438511230349</v>
+        <v>565.1780980214315</v>
       </c>
       <c r="N50">
-        <v>875.0561488769649</v>
+        <v>863.5219019785683</v>
       </c>
       <c r="O50">
-        <v>175.011229775393</v>
+        <v>172.7043803957137</v>
       </c>
       <c r="P50">
-        <v>700.044919101572</v>
+        <v>690.8175215828546</v>
       </c>
       <c r="Q50">
-        <v>1126.144919101572</v>
+        <v>1116.917521582855</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08346750360169722</v>
+        <v>0.08412111289549727</v>
       </c>
       <c r="T50">
-        <v>0.77448351978536</v>
+        <v>0.7879224148015904</v>
       </c>
       <c r="U50">
         <v>0.0617577444416894</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.580539812917571</v>
+        <v>2.527875735102926</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06711080339784585</v>
+        <v>0.06850353105720043</v>
       </c>
       <c r="C51">
-        <v>9477.906118122861</v>
+        <v>9033.288565340754</v>
       </c>
       <c r="D51">
-        <v>13917.24011812286</v>
+        <v>13659.38856534075</v>
       </c>
       <c r="E51">
-        <v>3029.534</v>
+        <v>3216.299999999999</v>
       </c>
       <c r="F51">
-        <v>9151.534</v>
+        <v>9338.299999999999</v>
       </c>
       <c r="G51">
         <v>4712.2</v>
@@ -5475,45 +5475,45 @@
         <v>1428.7</v>
       </c>
       <c r="M51">
-        <v>565.1780980214315</v>
+        <v>609.396394919828</v>
       </c>
       <c r="N51">
-        <v>863.5219019785683</v>
+        <v>819.3036050801718</v>
       </c>
       <c r="O51">
-        <v>172.7043803957137</v>
+        <v>163.8607210160344</v>
       </c>
       <c r="P51">
-        <v>690.8175215828546</v>
+        <v>655.4428840641374</v>
       </c>
       <c r="Q51">
-        <v>1116.917521582855</v>
+        <v>1081.542884064138</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08412111289549727</v>
+        <v>0.08480086656104933</v>
       </c>
       <c r="T51">
-        <v>0.7879224148015904</v>
+        <v>0.8018988656184701</v>
       </c>
       <c r="U51">
-        <v>0.0617577444416894</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.04940619555335152</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.527875735102926</v>
+        <v>2.344451020567588</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06850353105720043</v>
+        <v>0.06852425871655499</v>
       </c>
       <c r="C52">
-        <v>9033.288565340754</v>
+        <v>8842.757155822204</v>
       </c>
       <c r="D52">
-        <v>13659.38856534075</v>
+        <v>13655.6231558222</v>
       </c>
       <c r="E52">
-        <v>3216.299999999999</v>
+        <v>3403.065999999999</v>
       </c>
       <c r="F52">
-        <v>9338.299999999999</v>
+        <v>9525.065999999999</v>
       </c>
       <c r="G52">
         <v>4712.2</v>
@@ -5557,28 +5557,28 @@
         <v>1428.7</v>
       </c>
       <c r="M52">
-        <v>609.396394919828</v>
+        <v>621.5843228182246</v>
       </c>
       <c r="N52">
-        <v>819.3036050801718</v>
+        <v>807.1156771817753</v>
       </c>
       <c r="O52">
-        <v>163.8607210160344</v>
+        <v>161.4231354363551</v>
       </c>
       <c r="P52">
-        <v>655.4428840641374</v>
+        <v>645.6925417454202</v>
       </c>
       <c r="Q52">
-        <v>1081.542884064138</v>
+        <v>1071.79254174542</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08480086656104933</v>
+        <v>0.08550836527417494</v>
       </c>
       <c r="T52">
-        <v>0.8018988656184701</v>
+        <v>0.8164457838156306</v>
       </c>
       <c r="U52">
         <v>0.0652577444416894</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.344451020567588</v>
+        <v>2.298481392713322</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06852425871655499</v>
+        <v>0.06854498637590957</v>
       </c>
       <c r="C53">
-        <v>8842.757155822204</v>
+        <v>8652.227821711547</v>
       </c>
       <c r="D53">
-        <v>13655.6231558222</v>
+        <v>13651.85982171155</v>
       </c>
       <c r="E53">
-        <v>3403.065999999999</v>
+        <v>3589.832</v>
       </c>
       <c r="F53">
-        <v>9525.065999999999</v>
+        <v>9711.832</v>
       </c>
       <c r="G53">
         <v>4712.2</v>
@@ -5639,28 +5639,28 @@
         <v>1428.7</v>
       </c>
       <c r="M53">
-        <v>621.5843228182246</v>
+        <v>633.7722507166212</v>
       </c>
       <c r="N53">
-        <v>807.1156771817753</v>
+        <v>794.9277492833786</v>
       </c>
       <c r="O53">
-        <v>161.4231354363551</v>
+        <v>158.9855498566757</v>
       </c>
       <c r="P53">
-        <v>645.6925417454202</v>
+        <v>635.9421994267029</v>
       </c>
       <c r="Q53">
-        <v>1071.79254174542</v>
+        <v>1062.042199426703</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08550836527417494</v>
+        <v>0.08624534310034745</v>
       </c>
       <c r="T53">
-        <v>0.8164457838156306</v>
+        <v>0.8315988236043393</v>
       </c>
       <c r="U53">
         <v>0.0652577444416894</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.298481392713322</v>
+        <v>2.254279827468834</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06854498637590957</v>
+        <v>0.06975291403526414</v>
       </c>
       <c r="C54">
-        <v>8652.227821711547</v>
+        <v>8249.675316329131</v>
       </c>
       <c r="D54">
-        <v>13651.85982171155</v>
+        <v>13436.07331632913</v>
       </c>
       <c r="E54">
-        <v>3589.832</v>
+        <v>3776.598</v>
       </c>
       <c r="F54">
-        <v>9711.832</v>
+        <v>9898.598</v>
       </c>
       <c r="G54">
         <v>4712.2</v>
@@ -5721,45 +5721,45 @@
         <v>1428.7</v>
       </c>
       <c r="M54">
-        <v>633.7722507166212</v>
+        <v>673.6762530150178</v>
       </c>
       <c r="N54">
-        <v>794.9277492833786</v>
+        <v>755.023746984982</v>
       </c>
       <c r="O54">
-        <v>158.9855498566757</v>
+        <v>151.0047493969964</v>
       </c>
       <c r="P54">
-        <v>635.9421994267029</v>
+        <v>604.0189975879856</v>
       </c>
       <c r="Q54">
-        <v>1062.042199426703</v>
+        <v>1030.118997587986</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08624534310034745</v>
+        <v>0.0870136816850805</v>
       </c>
       <c r="T54">
-        <v>0.8315988236043393</v>
+        <v>0.8473966735968231</v>
       </c>
       <c r="U54">
-        <v>0.0652577444416894</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.05220619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.254279827468834</v>
+        <v>2.120751612671363</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06975291403526414</v>
+        <v>0.06979604169461871</v>
       </c>
       <c r="C55">
-        <v>8249.675316329131</v>
+        <v>8055.330964482671</v>
       </c>
       <c r="D55">
-        <v>13436.07331632913</v>
+        <v>13428.49496448267</v>
       </c>
       <c r="E55">
-        <v>3776.598</v>
+        <v>3963.364</v>
       </c>
       <c r="F55">
-        <v>9898.598</v>
+        <v>10085.364</v>
       </c>
       <c r="G55">
         <v>4712.2</v>
@@ -5803,28 +5803,28 @@
         <v>1428.7</v>
       </c>
       <c r="M55">
-        <v>673.6762530150178</v>
+        <v>686.3871257134143</v>
       </c>
       <c r="N55">
-        <v>755.023746984982</v>
+        <v>742.3128742865855</v>
       </c>
       <c r="O55">
-        <v>151.0047493969964</v>
+        <v>148.4625748573171</v>
       </c>
       <c r="P55">
-        <v>604.0189975879856</v>
+        <v>593.8502994292684</v>
       </c>
       <c r="Q55">
-        <v>1030.118997587986</v>
+        <v>1019.950299429268</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0870136816850805</v>
+        <v>0.08781542629523673</v>
       </c>
       <c r="T55">
-        <v>0.8473966735968231</v>
+        <v>0.8638813866324582</v>
       </c>
       <c r="U55">
         <v>0.0680577444416894</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.120751612671363</v>
+        <v>2.08147843465893</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06979604169461871</v>
+        <v>0.06983916935397329</v>
       </c>
       <c r="C56">
-        <v>8055.330964482671</v>
+        <v>7860.99515665656</v>
       </c>
       <c r="D56">
-        <v>13428.49496448267</v>
+        <v>13420.92515665656</v>
       </c>
       <c r="E56">
-        <v>3963.364</v>
+        <v>4150.129999999999</v>
       </c>
       <c r="F56">
-        <v>10085.364</v>
+        <v>10272.13</v>
       </c>
       <c r="G56">
         <v>4712.2</v>
@@ -5885,28 +5885,28 @@
         <v>1428.7</v>
       </c>
       <c r="M56">
-        <v>686.3871257134143</v>
+        <v>699.0979984118109</v>
       </c>
       <c r="N56">
-        <v>742.3128742865855</v>
+        <v>729.602001588189</v>
       </c>
       <c r="O56">
-        <v>148.4625748573171</v>
+        <v>145.9204003176378</v>
       </c>
       <c r="P56">
-        <v>593.8502994292684</v>
+        <v>583.6816012705511</v>
       </c>
       <c r="Q56">
-        <v>1019.950299429268</v>
+        <v>1009.781601270551</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08781542629523673</v>
+        <v>0.08865280399917766</v>
       </c>
       <c r="T56">
-        <v>0.8638813866324582</v>
+        <v>0.8810987535807883</v>
       </c>
       <c r="U56">
         <v>0.0680577444416894</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.08147843465893</v>
+        <v>2.043633372210586</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06983916935397329</v>
+        <v>0.06988229701332786</v>
       </c>
       <c r="C57">
-        <v>7860.99515665656</v>
+        <v>7666.667878409826</v>
       </c>
       <c r="D57">
-        <v>13420.92515665656</v>
+        <v>13413.36387840983</v>
       </c>
       <c r="E57">
-        <v>4150.129999999999</v>
+        <v>4336.896000000001</v>
       </c>
       <c r="F57">
-        <v>10272.13</v>
+        <v>10458.896</v>
       </c>
       <c r="G57">
         <v>4712.2</v>
@@ -5967,28 +5967,28 @@
         <v>1428.7</v>
       </c>
       <c r="M57">
-        <v>699.0979984118109</v>
+        <v>711.8088711102075</v>
       </c>
       <c r="N57">
-        <v>729.602001588189</v>
+        <v>716.8911288897923</v>
       </c>
       <c r="O57">
-        <v>145.9204003176378</v>
+        <v>143.3782257779585</v>
       </c>
       <c r="P57">
-        <v>583.6816012705511</v>
+        <v>573.5129031118338</v>
       </c>
       <c r="Q57">
-        <v>1009.781601270551</v>
+        <v>999.6129031118338</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08865280399917766</v>
+        <v>0.08952824432602502</v>
       </c>
       <c r="T57">
-        <v>0.8810987535807883</v>
+        <v>0.8990987281176788</v>
       </c>
       <c r="U57">
         <v>0.0680577444416894</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.043633372210586</v>
+        <v>2.007139919135397</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06988229701332786</v>
+        <v>0.07348222467268242</v>
       </c>
       <c r="C58">
-        <v>7666.667878409826</v>
+        <v>6877.438955949576</v>
       </c>
       <c r="D58">
-        <v>13413.36387840983</v>
+        <v>12810.90095594958</v>
       </c>
       <c r="E58">
-        <v>4336.896000000001</v>
+        <v>4523.662</v>
       </c>
       <c r="F58">
-        <v>10458.896</v>
+        <v>10645.662</v>
       </c>
       <c r="G58">
         <v>4712.2</v>
@@ -6049,45 +6049,45 @@
         <v>1428.7</v>
       </c>
       <c r="M58">
-        <v>711.8088711102075</v>
+        <v>807.5559074086041</v>
       </c>
       <c r="N58">
-        <v>716.8911288897923</v>
+        <v>621.1440925913957</v>
       </c>
       <c r="O58">
-        <v>143.3782257779585</v>
+        <v>124.2288185182792</v>
       </c>
       <c r="P58">
-        <v>573.5129031118338</v>
+        <v>496.9152740731166</v>
       </c>
       <c r="Q58">
-        <v>999.6129031118338</v>
+        <v>923.0152740731166</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08952824432602502</v>
+        <v>0.09044440280760944</v>
       </c>
       <c r="T58">
-        <v>0.8990987281176788</v>
+        <v>0.9179359107725641</v>
       </c>
       <c r="U58">
-        <v>0.0680577444416894</v>
+        <v>0.0758577444416894</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.05444619555335152</v>
+        <v>0.06068619555335152</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.007139919135397</v>
+        <v>1.769165437207447</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07348222467268242</v>
+        <v>0.07539735233203701</v>
       </c>
       <c r="C59">
-        <v>6877.438955949576</v>
+        <v>6391.707460221249</v>
       </c>
       <c r="D59">
-        <v>12810.90095594958</v>
+        <v>12511.93546022125</v>
       </c>
       <c r="E59">
-        <v>4523.662</v>
+        <v>4710.428</v>
       </c>
       <c r="F59">
-        <v>10645.662</v>
+        <v>10832.428</v>
       </c>
       <c r="G59">
         <v>4712.2</v>
@@ -6131,45 +6131,45 @@
         <v>1428.7</v>
       </c>
       <c r="M59">
-        <v>807.5559074086041</v>
+        <v>863.9700241070007</v>
       </c>
       <c r="N59">
-        <v>621.1440925913957</v>
+        <v>564.7299758929992</v>
       </c>
       <c r="O59">
-        <v>124.2288185182792</v>
+        <v>112.9459951785998</v>
       </c>
       <c r="P59">
-        <v>496.9152740731166</v>
+        <v>451.7839807143993</v>
       </c>
       <c r="Q59">
-        <v>923.0152740731166</v>
+        <v>877.8839807143993</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09044440280760944</v>
+        <v>0.09140418788355505</v>
       </c>
       <c r="T59">
-        <v>0.9179359107725641</v>
+        <v>0.9376701021253012</v>
       </c>
       <c r="U59">
-        <v>0.0758577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.06068619555335152</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.769165437207447</v>
+        <v>1.653645335064378</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07539735233203701</v>
+        <v>0.07553407999139157</v>
       </c>
       <c r="C60">
-        <v>6391.707460221251</v>
+        <v>6184.13004728225</v>
       </c>
       <c r="D60">
-        <v>12511.93546022125</v>
+        <v>12491.12404728225</v>
       </c>
       <c r="E60">
-        <v>4710.427999999998</v>
+        <v>4897.193999999998</v>
       </c>
       <c r="F60">
-        <v>10832.428</v>
+        <v>11019.194</v>
       </c>
       <c r="G60">
         <v>4712.2</v>
@@ -6213,28 +6213,28 @@
         <v>1428.7</v>
       </c>
       <c r="M60">
-        <v>863.9700241070004</v>
+        <v>878.866059005397</v>
       </c>
       <c r="N60">
-        <v>564.7299758929994</v>
+        <v>549.8339409946028</v>
       </c>
       <c r="O60">
-        <v>112.9459951785999</v>
+        <v>109.9667881989206</v>
       </c>
       <c r="P60">
-        <v>451.7839807143995</v>
+        <v>439.8671527956823</v>
       </c>
       <c r="Q60">
-        <v>877.8839807143995</v>
+        <v>865.9671527956823</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09140418788355503</v>
+        <v>0.0924107917436931</v>
       </c>
       <c r="T60">
-        <v>0.9376701021253009</v>
+        <v>0.9583669369586595</v>
       </c>
       <c r="U60">
         <v>0.0797577444416894</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.653645335064378</v>
+        <v>1.625617448029389</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07553407999139157</v>
+        <v>0.07567080765074614</v>
       </c>
       <c r="C61">
-        <v>6184.13004728225</v>
+        <v>5976.621751658528</v>
       </c>
       <c r="D61">
-        <v>12491.12404728225</v>
+        <v>12470.38175165853</v>
       </c>
       <c r="E61">
-        <v>4897.193999999998</v>
+        <v>5083.959999999999</v>
       </c>
       <c r="F61">
-        <v>11019.194</v>
+        <v>11205.96</v>
       </c>
       <c r="G61">
         <v>4712.2</v>
@@ -6295,28 +6295,28 @@
         <v>1428.7</v>
       </c>
       <c r="M61">
-        <v>878.866059005397</v>
+        <v>893.7620939037937</v>
       </c>
       <c r="N61">
-        <v>549.8339409946028</v>
+        <v>534.9379060962061</v>
       </c>
       <c r="O61">
-        <v>109.9667881989206</v>
+        <v>106.9875812192412</v>
       </c>
       <c r="P61">
-        <v>439.8671527956823</v>
+        <v>427.9503248769649</v>
       </c>
       <c r="Q61">
-        <v>865.9671527956823</v>
+        <v>854.0503248769649</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.0924107917436931</v>
+        <v>0.09346772579683807</v>
       </c>
       <c r="T61">
-        <v>0.9583669369586595</v>
+        <v>0.9800986135336858</v>
       </c>
       <c r="U61">
         <v>0.0797577444416894</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.625617448029389</v>
+        <v>1.598523823895566</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07567080765074614</v>
+        <v>0.0758075353101007</v>
       </c>
       <c r="C62">
-        <v>5976.621751658528</v>
+        <v>5769.182229599992</v>
       </c>
       <c r="D62">
-        <v>12470.38175165853</v>
+        <v>12449.70822959999</v>
       </c>
       <c r="E62">
-        <v>5083.959999999999</v>
+        <v>5270.725999999999</v>
       </c>
       <c r="F62">
-        <v>11205.96</v>
+        <v>11392.726</v>
       </c>
       <c r="G62">
         <v>4712.2</v>
@@ -6377,28 +6377,28 @@
         <v>1428.7</v>
       </c>
       <c r="M62">
-        <v>893.7620939037937</v>
+        <v>908.6581288021902</v>
       </c>
       <c r="N62">
-        <v>534.9379060962061</v>
+        <v>520.0418711978097</v>
       </c>
       <c r="O62">
-        <v>106.9875812192412</v>
+        <v>104.0083742395619</v>
       </c>
       <c r="P62">
-        <v>427.9503248769649</v>
+        <v>416.0334969582477</v>
       </c>
       <c r="Q62">
-        <v>854.0503248769649</v>
+        <v>842.1334969582477</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09346772579683807</v>
+        <v>0.09457886159629816</v>
       </c>
       <c r="T62">
-        <v>0.9800986135336858</v>
+        <v>1.002944735061277</v>
       </c>
       <c r="U62">
         <v>0.0797577444416894</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.598523823895566</v>
+        <v>1.572318515307114</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0758075353101007</v>
+        <v>0.07594426296945528</v>
       </c>
       <c r="C63">
-        <v>5769.182229599992</v>
+        <v>5561.811139632253</v>
       </c>
       <c r="D63">
-        <v>12449.70822959999</v>
+        <v>12429.10313963225</v>
       </c>
       <c r="E63">
-        <v>5270.725999999999</v>
+        <v>5457.491999999998</v>
       </c>
       <c r="F63">
-        <v>11392.726</v>
+        <v>11579.492</v>
       </c>
       <c r="G63">
         <v>4712.2</v>
@@ -6459,28 +6459,28 @@
         <v>1428.7</v>
       </c>
       <c r="M63">
-        <v>908.6581288021902</v>
+        <v>923.5541637005867</v>
       </c>
       <c r="N63">
-        <v>520.0418711978097</v>
+        <v>505.1458362994131</v>
       </c>
       <c r="O63">
-        <v>104.0083742395619</v>
+        <v>101.0291672598826</v>
       </c>
       <c r="P63">
-        <v>416.0334969582477</v>
+        <v>404.1166690395304</v>
       </c>
       <c r="Q63">
-        <v>842.1334969582477</v>
+        <v>830.2166690395304</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09457886159629816</v>
+        <v>0.09574847822730879</v>
       </c>
       <c r="T63">
-        <v>1.002944735061277</v>
+        <v>1.02699328403769</v>
       </c>
       <c r="U63">
         <v>0.0797577444416894</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.572318515307114</v>
+        <v>1.546958539253773</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07594426296945528</v>
+        <v>0.07608099062880985</v>
       </c>
       <c r="C64">
-        <v>5561.811139632253</v>
+        <v>5354.508142537832</v>
       </c>
       <c r="D64">
-        <v>12429.10313963225</v>
+        <v>12408.56614253783</v>
       </c>
       <c r="E64">
-        <v>5457.491999999998</v>
+        <v>5644.258</v>
       </c>
       <c r="F64">
-        <v>11579.492</v>
+        <v>11766.258</v>
       </c>
       <c r="G64">
         <v>4712.2</v>
@@ -6541,28 +6541,28 @@
         <v>1428.7</v>
       </c>
       <c r="M64">
-        <v>923.5541637005867</v>
+        <v>938.4501985989834</v>
       </c>
       <c r="N64">
-        <v>505.1458362994131</v>
+        <v>490.2498014010164</v>
       </c>
       <c r="O64">
-        <v>101.0291672598826</v>
+        <v>98.04996028020328</v>
       </c>
       <c r="P64">
-        <v>404.1166690395304</v>
+        <v>392.1998411208131</v>
       </c>
       <c r="Q64">
-        <v>830.2166690395304</v>
+        <v>818.2998411208132</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09574847822730879</v>
+        <v>0.09698131737891459</v>
       </c>
       <c r="T64">
-        <v>1.02699328403769</v>
+        <v>1.052341754580395</v>
       </c>
       <c r="U64">
         <v>0.0797577444416894</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.546958539253773</v>
+        <v>1.5224036418053</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07608099062880985</v>
+        <v>0.08348811828816444</v>
       </c>
       <c r="C65">
-        <v>5354.508142537832</v>
+        <v>4148.260488372418</v>
       </c>
       <c r="D65">
-        <v>12408.56614253783</v>
+        <v>11389.08448837242</v>
       </c>
       <c r="E65">
-        <v>5644.258</v>
+        <v>5831.023999999999</v>
       </c>
       <c r="F65">
-        <v>11766.258</v>
+        <v>11953.024</v>
       </c>
       <c r="G65">
         <v>4712.2</v>
@@ -6623,45 +6623,45 @@
         <v>1428.7</v>
       </c>
       <c r="M65">
-        <v>938.4501985989834</v>
+        <v>1123.07917429738</v>
       </c>
       <c r="N65">
-        <v>490.2498014010164</v>
+        <v>305.6208257026199</v>
       </c>
       <c r="O65">
-        <v>98.04996028020328</v>
+        <v>61.12416514052398</v>
       </c>
       <c r="P65">
-        <v>392.1998411208131</v>
+        <v>244.4966605620959</v>
       </c>
       <c r="Q65">
-        <v>818.2998411208132</v>
+        <v>670.5966605620958</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09698131737891459</v>
+        <v>0.09828264759449849</v>
       </c>
       <c r="T65">
-        <v>1.052341754580395</v>
+        <v>1.079098473486583</v>
       </c>
       <c r="U65">
-        <v>0.0797577444416894</v>
+        <v>0.0939577444416894</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.06380619555335153</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.5224036418053</v>
+        <v>1.272127586992094</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08348811828816444</v>
+        <v>0.083738445947519</v>
       </c>
       <c r="C66">
-        <v>4148.260488372418</v>
+        <v>3929.95886371959</v>
       </c>
       <c r="D66">
-        <v>11389.08448837242</v>
+        <v>11357.54886371959</v>
       </c>
       <c r="E66">
-        <v>5831.023999999999</v>
+        <v>6017.789999999999</v>
       </c>
       <c r="F66">
-        <v>11953.024</v>
+        <v>12139.79</v>
       </c>
       <c r="G66">
         <v>4712.2</v>
@@ -6705,28 +6705,28 @@
         <v>1428.7</v>
       </c>
       <c r="M66">
-        <v>1123.07917429738</v>
+        <v>1140.627286395777</v>
       </c>
       <c r="N66">
-        <v>305.6208257026199</v>
+        <v>288.0727136042233</v>
       </c>
       <c r="O66">
-        <v>61.12416514052398</v>
+        <v>57.61454272084466</v>
       </c>
       <c r="P66">
-        <v>244.4966605620959</v>
+        <v>230.4581708833786</v>
       </c>
       <c r="Q66">
-        <v>670.5966605620958</v>
+        <v>656.5581708833786</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09828264759449849</v>
+        <v>0.09965833953668718</v>
       </c>
       <c r="T66">
-        <v>1.079098473486583</v>
+        <v>1.10738414775884</v>
       </c>
       <c r="U66">
         <v>0.0939577444416894</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.272127586992094</v>
+        <v>1.252556393346062</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.083738445947519</v>
+        <v>0.1001231067374275</v>
       </c>
       <c r="C67">
-        <v>3929.95886371959</v>
+        <v>2000.625105220297</v>
       </c>
       <c r="D67">
-        <v>11357.54886371959</v>
+        <v>9614.981105220299</v>
       </c>
       <c r="E67">
-        <v>6017.789999999999</v>
+        <v>6204.556</v>
       </c>
       <c r="F67">
-        <v>12139.79</v>
+        <v>12326.556</v>
       </c>
       <c r="G67">
         <v>4712.2</v>
@@ -6787,45 +6787,45 @@
         <v>1428.7</v>
       </c>
       <c r="M67">
-        <v>1140.627286395777</v>
+        <v>1510.714900094173</v>
       </c>
       <c r="N67">
-        <v>288.0727136042233</v>
+        <v>-82.0149000941733</v>
       </c>
       <c r="O67">
-        <v>57.61454272084466</v>
+        <v>-16.40298001883466</v>
       </c>
       <c r="P67">
-        <v>230.4581708833786</v>
+        <v>-65.61192007533865</v>
       </c>
       <c r="Q67">
-        <v>656.5581708833786</v>
+        <v>360.4880799246614</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.09965833953668718</v>
+        <v>0.1015716292986418</v>
       </c>
       <c r="T67">
-        <v>1.10738414775884</v>
+        <v>1.146723399036994</v>
       </c>
       <c r="U67">
-        <v>0.0939577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V67">
-        <v>0.2</v>
+        <v>0.1891422398641781</v>
       </c>
       <c r="W67">
-        <v>0.07516619555335152</v>
+        <v>0.09937689814528675</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.252556393346062</v>
+        <v>0.9457111993208905</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1001231067374275</v>
+        <v>0.1008906841818444</v>
       </c>
       <c r="C68">
-        <v>2000.625105220297</v>
+        <v>1745.242720407234</v>
       </c>
       <c r="D68">
-        <v>9614.981105220299</v>
+        <v>9546.364720407235</v>
       </c>
       <c r="E68">
-        <v>6204.556</v>
+        <v>6391.322</v>
       </c>
       <c r="F68">
-        <v>12326.556</v>
+        <v>12513.322</v>
       </c>
       <c r="G68">
         <v>4712.2</v>
@@ -6869,37 +6869,37 @@
         <v>1428.7</v>
       </c>
       <c r="M68">
-        <v>1510.714900094173</v>
+        <v>1533.60451979257</v>
       </c>
       <c r="N68">
-        <v>-82.0149000941733</v>
+        <v>-104.90451979257</v>
       </c>
       <c r="O68">
-        <v>-16.40298001883466</v>
+        <v>-20.980903958514</v>
       </c>
       <c r="P68">
-        <v>-65.61192007533865</v>
+        <v>-83.92361583405599</v>
       </c>
       <c r="Q68">
-        <v>360.4880799246614</v>
+        <v>342.176384165944</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1015716292986418</v>
+        <v>0.103261678671328</v>
       </c>
       <c r="T68">
-        <v>1.146723399036994</v>
+        <v>1.181472592947206</v>
       </c>
       <c r="U68">
         <v>0.1225577444416894</v>
       </c>
       <c r="V68">
-        <v>0.1891422398641781</v>
+        <v>0.1863192213587426</v>
       </c>
       <c r="W68">
-        <v>0.09937689814528675</v>
+        <v>0.09972288092583008</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9457111993208905</v>
+        <v>0.931596106793713</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1008906841818444</v>
+        <v>0.1016582616262613</v>
       </c>
       <c r="C69">
-        <v>1745.242720407234</v>
+        <v>1490.832744509284</v>
       </c>
       <c r="D69">
-        <v>9546.364720407235</v>
+        <v>9478.720744509283</v>
       </c>
       <c r="E69">
-        <v>6391.322</v>
+        <v>6578.088</v>
       </c>
       <c r="F69">
-        <v>12513.322</v>
+        <v>12700.088</v>
       </c>
       <c r="G69">
         <v>4712.2</v>
@@ -6951,37 +6951,37 @@
         <v>1428.7</v>
       </c>
       <c r="M69">
-        <v>1533.60451979257</v>
+        <v>1556.494139490966</v>
       </c>
       <c r="N69">
-        <v>-104.90451979257</v>
+        <v>-127.7941394909665</v>
       </c>
       <c r="O69">
-        <v>-20.980903958514</v>
+        <v>-25.5588278981933</v>
       </c>
       <c r="P69">
-        <v>-83.92361583405599</v>
+        <v>-102.2353115927732</v>
       </c>
       <c r="Q69">
-        <v>342.176384165944</v>
+        <v>323.8646884072268</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.103261678671328</v>
+        <v>0.105057356129807</v>
       </c>
       <c r="T69">
-        <v>1.181472592947206</v>
+        <v>1.218393611476806</v>
       </c>
       <c r="U69">
         <v>0.1225577444416894</v>
       </c>
       <c r="V69">
-        <v>0.1863192213587426</v>
+        <v>0.1835792328093493</v>
       </c>
       <c r="W69">
-        <v>0.09972288092583008</v>
+        <v>0.1000586877422398</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.931596106793713</v>
+        <v>0.9178961640467467</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1016582616262613</v>
+        <v>0.1024258390706781</v>
       </c>
       <c r="C70">
-        <v>1490.832744509284</v>
+        <v>1237.374651976497</v>
       </c>
       <c r="D70">
-        <v>9478.720744509283</v>
+        <v>9412.028651976496</v>
       </c>
       <c r="E70">
-        <v>6578.088</v>
+        <v>6764.853999999999</v>
       </c>
       <c r="F70">
-        <v>12700.088</v>
+        <v>12886.854</v>
       </c>
       <c r="G70">
         <v>4712.2</v>
@@ -7033,37 +7033,37 @@
         <v>1428.7</v>
       </c>
       <c r="M70">
-        <v>1556.494139490966</v>
+        <v>1579.383759189363</v>
       </c>
       <c r="N70">
-        <v>-127.7941394909665</v>
+        <v>-150.6837591893629</v>
       </c>
       <c r="O70">
-        <v>-25.5588278981933</v>
+        <v>-30.13675183787259</v>
       </c>
       <c r="P70">
-        <v>-102.2353115927732</v>
+        <v>-120.5470073514904</v>
       </c>
       <c r="Q70">
-        <v>323.8646884072268</v>
+        <v>305.5529926485096</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.105057356129807</v>
+        <v>0.1069688837468975</v>
       </c>
       <c r="T70">
-        <v>1.218393611476806</v>
+        <v>1.257696631201864</v>
       </c>
       <c r="U70">
         <v>0.1225577444416894</v>
       </c>
       <c r="V70">
-        <v>0.1835792328093493</v>
+        <v>0.1809186642179095</v>
       </c>
       <c r="W70">
-        <v>0.1000586877422398</v>
+        <v>0.100384761027739</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9178961640467467</v>
+        <v>0.9045933210895475</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1024258390706781</v>
+        <v>0.1031934165150951</v>
       </c>
       <c r="C71">
-        <v>1237.374651976497</v>
+        <v>984.8484908923147</v>
       </c>
       <c r="D71">
-        <v>9412.028651976496</v>
+        <v>9346.268490892315</v>
       </c>
       <c r="E71">
-        <v>6764.853999999999</v>
+        <v>6951.620000000001</v>
       </c>
       <c r="F71">
-        <v>12886.854</v>
+        <v>13073.62</v>
       </c>
       <c r="G71">
         <v>4712.2</v>
@@ -7115,37 +7115,37 @@
         <v>1428.7</v>
       </c>
       <c r="M71">
-        <v>1579.383759189363</v>
+        <v>1602.273378887759</v>
       </c>
       <c r="N71">
-        <v>-150.6837591893629</v>
+        <v>-173.5733788877596</v>
       </c>
       <c r="O71">
-        <v>-30.13675183787259</v>
+        <v>-34.71467577755193</v>
       </c>
       <c r="P71">
-        <v>-120.5470073514904</v>
+        <v>-138.8587031102077</v>
       </c>
       <c r="Q71">
-        <v>305.5529926485096</v>
+        <v>287.2412968897923</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1069688837468975</v>
+        <v>0.1090078465384608</v>
       </c>
       <c r="T71">
-        <v>1.257696631201864</v>
+        <v>1.299619852241927</v>
       </c>
       <c r="U71">
         <v>0.1225577444416894</v>
       </c>
       <c r="V71">
-        <v>0.1809186642179095</v>
+        <v>0.1783341118719394</v>
       </c>
       <c r="W71">
-        <v>0.100384761027739</v>
+        <v>0.1007015179336526</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9045933210895475</v>
+        <v>0.8916705593596967</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1031934165150951</v>
+        <v>0.1039609939595119</v>
       </c>
       <c r="C72">
-        <v>984.8484908923147</v>
+        <v>733.2348630732504</v>
       </c>
       <c r="D72">
-        <v>9346.268490892315</v>
+        <v>9281.42086307325</v>
       </c>
       <c r="E72">
-        <v>6951.620000000001</v>
+        <v>7138.386</v>
       </c>
       <c r="F72">
-        <v>13073.62</v>
+        <v>13260.386</v>
       </c>
       <c r="G72">
         <v>4712.2</v>
@@ -7197,37 +7197,37 @@
         <v>1428.7</v>
       </c>
       <c r="M72">
-        <v>1602.273378887759</v>
+        <v>1625.162998586156</v>
       </c>
       <c r="N72">
-        <v>-173.5733788877596</v>
+        <v>-196.4629985861561</v>
       </c>
       <c r="O72">
-        <v>-34.71467577755193</v>
+        <v>-39.29259971723123</v>
       </c>
       <c r="P72">
-        <v>-138.8587031102077</v>
+        <v>-157.1703988689249</v>
       </c>
       <c r="Q72">
-        <v>287.2412968897923</v>
+        <v>268.9296011310751</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1090078465384608</v>
+        <v>0.1111874274535801</v>
       </c>
       <c r="T72">
-        <v>1.299619852241927</v>
+        <v>1.344434329905442</v>
       </c>
       <c r="U72">
         <v>0.1225577444416894</v>
       </c>
       <c r="V72">
-        <v>0.1783341118719394</v>
+        <v>0.175822363817405</v>
       </c>
       <c r="W72">
-        <v>0.1007015179336526</v>
+        <v>0.1010093521098221</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8916705593596967</v>
+        <v>0.8791118190870251</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1039609939595119</v>
+        <v>0.1047285714039288</v>
       </c>
       <c r="C73">
-        <v>733.2348630732522</v>
+        <v>482.5149049912761</v>
       </c>
       <c r="D73">
-        <v>9281.42086307325</v>
+        <v>9217.466904991274</v>
       </c>
       <c r="E73">
-        <v>7138.385999999999</v>
+        <v>7325.151999999998</v>
       </c>
       <c r="F73">
-        <v>13260.386</v>
+        <v>13447.152</v>
       </c>
       <c r="G73">
         <v>4712.2</v>
@@ -7279,37 +7279,37 @@
         <v>1428.7</v>
       </c>
       <c r="M73">
-        <v>1625.162998586156</v>
+        <v>1648.052618284552</v>
       </c>
       <c r="N73">
-        <v>-196.4629985861559</v>
+        <v>-219.3526182845526</v>
       </c>
       <c r="O73">
-        <v>-39.29259971723118</v>
+        <v>-43.87052365691052</v>
       </c>
       <c r="P73">
-        <v>-157.1703988689247</v>
+        <v>-175.4820946276421</v>
       </c>
       <c r="Q73">
-        <v>268.9296011310753</v>
+        <v>250.6179053723579</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1111874274535801</v>
+        <v>0.1135226927197794</v>
       </c>
       <c r="T73">
-        <v>1.344434329905441</v>
+        <v>1.392449841687778</v>
       </c>
       <c r="U73">
         <v>0.1225577444416894</v>
       </c>
       <c r="V73">
-        <v>0.175822363817405</v>
+        <v>0.1733803865421633</v>
       </c>
       <c r="W73">
-        <v>0.1010093521098221</v>
+        <v>0.1013086353366536</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8791118190870252</v>
+        <v>0.8669019327108164</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1047285714039288</v>
+        <v>0.1054961488483457</v>
       </c>
       <c r="C74">
-        <v>482.5149049912761</v>
+        <v>232.6702694795822</v>
       </c>
       <c r="D74">
-        <v>9217.466904991274</v>
+        <v>9154.388269479581</v>
       </c>
       <c r="E74">
-        <v>7325.151999999998</v>
+        <v>7511.917999999998</v>
       </c>
       <c r="F74">
-        <v>13447.152</v>
+        <v>13633.918</v>
       </c>
       <c r="G74">
         <v>4712.2</v>
@@ -7361,37 +7361,37 @@
         <v>1428.7</v>
       </c>
       <c r="M74">
-        <v>1648.052618284552</v>
+        <v>1670.942237982949</v>
       </c>
       <c r="N74">
-        <v>-219.3526182845526</v>
+        <v>-242.2422379829491</v>
       </c>
       <c r="O74">
-        <v>-43.87052365691052</v>
+        <v>-48.44844759658982</v>
       </c>
       <c r="P74">
-        <v>-175.4820946276421</v>
+        <v>-193.7937903863593</v>
       </c>
       <c r="Q74">
-        <v>250.6179053723579</v>
+        <v>232.3062096136408</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1135226927197794</v>
+        <v>0.1160309405982897</v>
       </c>
       <c r="T74">
-        <v>1.392449841687778</v>
+        <v>1.444022058046585</v>
       </c>
       <c r="U74">
         <v>0.1225577444416894</v>
       </c>
       <c r="V74">
-        <v>0.1733803865421633</v>
+        <v>0.1710053127539145</v>
       </c>
       <c r="W74">
-        <v>0.1013086353366536</v>
+        <v>0.101599719023024</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8669019327108164</v>
+        <v>0.8550265637695724</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1054961488483457</v>
+        <v>0.1062637262927626</v>
       </c>
       <c r="C75">
-        <v>232.6702694795822</v>
+        <v>-16.31689181561342</v>
       </c>
       <c r="D75">
-        <v>9154.388269479581</v>
+        <v>9092.167108184385</v>
       </c>
       <c r="E75">
-        <v>7511.917999999998</v>
+        <v>7698.683999999999</v>
       </c>
       <c r="F75">
-        <v>13633.918</v>
+        <v>13820.684</v>
       </c>
       <c r="G75">
         <v>4712.2</v>
@@ -7443,37 +7443,37 @@
         <v>1428.7</v>
       </c>
       <c r="M75">
-        <v>1670.942237982949</v>
+        <v>1693.831857681346</v>
       </c>
       <c r="N75">
-        <v>-242.2422379829491</v>
+        <v>-265.1318576813458</v>
       </c>
       <c r="O75">
-        <v>-48.44844759658982</v>
+        <v>-53.02637153626915</v>
       </c>
       <c r="P75">
-        <v>-193.7937903863593</v>
+        <v>-212.1054861450766</v>
       </c>
       <c r="Q75">
-        <v>232.3062096136408</v>
+        <v>213.9945138549234</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1160309405982897</v>
+        <v>0.1187321306213009</v>
       </c>
       <c r="T75">
-        <v>1.444022058046585</v>
+        <v>1.499561367971453</v>
       </c>
       <c r="U75">
         <v>0.1225577444416894</v>
       </c>
       <c r="V75">
-        <v>0.1710053127539145</v>
+        <v>0.1686944301491319</v>
       </c>
       <c r="W75">
-        <v>0.101599719023024</v>
+        <v>0.1018829355827357</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8550265637695724</v>
+        <v>0.8434721507456592</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1062637262927626</v>
+        <v>0.1070313037371795</v>
       </c>
       <c r="C76">
-        <v>-16.31689181561342</v>
+        <v>-264.4639452724532</v>
       </c>
       <c r="D76">
-        <v>9092.167108184385</v>
+        <v>9030.786054727545</v>
       </c>
       <c r="E76">
-        <v>7698.683999999999</v>
+        <v>7885.449999999999</v>
       </c>
       <c r="F76">
-        <v>13820.684</v>
+        <v>14007.45</v>
       </c>
       <c r="G76">
         <v>4712.2</v>
@@ -7525,37 +7525,37 @@
         <v>1428.7</v>
       </c>
       <c r="M76">
-        <v>1693.831857681346</v>
+        <v>1716.721477379742</v>
       </c>
       <c r="N76">
-        <v>-265.1318576813458</v>
+        <v>-288.0214773797422</v>
       </c>
       <c r="O76">
-        <v>-53.02637153626915</v>
+        <v>-57.60429547594845</v>
       </c>
       <c r="P76">
-        <v>-212.1054861450766</v>
+        <v>-230.4171819037938</v>
       </c>
       <c r="Q76">
-        <v>213.9945138549234</v>
+        <v>195.6828180962062</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1187321306213009</v>
+        <v>0.1216494158461529</v>
       </c>
       <c r="T76">
-        <v>1.499561367971453</v>
+        <v>1.559543822690312</v>
       </c>
       <c r="U76">
         <v>0.1225577444416894</v>
       </c>
       <c r="V76">
-        <v>0.1686944301491319</v>
+        <v>0.1664451710804767</v>
       </c>
       <c r="W76">
-        <v>0.1018829355827357</v>
+        <v>0.1021585997008551</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8434721507456592</v>
+        <v>0.8322258554023838</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1070313037371795</v>
+        <v>0.1077988811815964</v>
       </c>
       <c r="C77">
-        <v>-264.4639452724532</v>
+        <v>-511.7877914533983</v>
       </c>
       <c r="D77">
-        <v>9030.786054727545</v>
+        <v>8970.228208546601</v>
       </c>
       <c r="E77">
-        <v>7885.449999999999</v>
+        <v>8072.215999999999</v>
       </c>
       <c r="F77">
-        <v>14007.45</v>
+        <v>14194.216</v>
       </c>
       <c r="G77">
         <v>4712.2</v>
@@ -7607,37 +7607,37 @@
         <v>1428.7</v>
       </c>
       <c r="M77">
-        <v>1716.721477379742</v>
+        <v>1739.611097078139</v>
       </c>
       <c r="N77">
-        <v>-288.0214773797422</v>
+        <v>-310.9110970781387</v>
       </c>
       <c r="O77">
-        <v>-57.60429547594845</v>
+        <v>-62.18221941562774</v>
       </c>
       <c r="P77">
-        <v>-230.4171819037938</v>
+        <v>-248.728877662511</v>
       </c>
       <c r="Q77">
-        <v>195.6828180962062</v>
+        <v>177.3711223374891</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1216494158461529</v>
+        <v>0.1248098081730759</v>
       </c>
       <c r="T77">
-        <v>1.559543822690312</v>
+        <v>1.624524815302408</v>
       </c>
       <c r="U77">
         <v>0.1225577444416894</v>
       </c>
       <c r="V77">
-        <v>0.1664451710804767</v>
+        <v>0.1642551030399442</v>
       </c>
       <c r="W77">
-        <v>0.1021585997008551</v>
+        <v>0.1024270095000766</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8322258554023838</v>
+        <v>0.8212755151997209</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1077988811815964</v>
+        <v>0.1085664586260133</v>
       </c>
       <c r="C78">
-        <v>-511.7877914533983</v>
+        <v>-758.3048806193074</v>
       </c>
       <c r="D78">
-        <v>8970.228208546601</v>
+        <v>8910.477119380694</v>
       </c>
       <c r="E78">
-        <v>8072.215999999999</v>
+        <v>8258.982</v>
       </c>
       <c r="F78">
-        <v>14194.216</v>
+        <v>14380.982</v>
       </c>
       <c r="G78">
         <v>4712.2</v>
@@ -7689,37 +7689,37 @@
         <v>1428.7</v>
       </c>
       <c r="M78">
-        <v>1739.611097078139</v>
+        <v>1762.500716776535</v>
       </c>
       <c r="N78">
-        <v>-310.9110970781387</v>
+        <v>-333.8007167765356</v>
       </c>
       <c r="O78">
-        <v>-62.18221941562774</v>
+        <v>-66.76014335530714</v>
       </c>
       <c r="P78">
-        <v>-248.728877662511</v>
+        <v>-267.0405734212285</v>
       </c>
       <c r="Q78">
-        <v>177.3711223374891</v>
+        <v>159.0594265787715</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1248098081730759</v>
+        <v>0.1282450172240792</v>
       </c>
       <c r="T78">
-        <v>1.624524815302408</v>
+        <v>1.695156329011208</v>
       </c>
       <c r="U78">
         <v>0.1225577444416894</v>
       </c>
       <c r="V78">
-        <v>0.1642551030399442</v>
+        <v>0.1621219198835812</v>
       </c>
       <c r="W78">
-        <v>0.1024270095000766</v>
+        <v>0.1026884476162014</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8212755151997209</v>
+        <v>0.8106095994179061</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1085664586260133</v>
+        <v>0.1093340360704302</v>
       </c>
       <c r="C79">
-        <v>-758.3048806193074</v>
+        <v>-1004.031227627609</v>
       </c>
       <c r="D79">
-        <v>8910.477119380694</v>
+        <v>8851.516772372392</v>
       </c>
       <c r="E79">
-        <v>8258.982</v>
+        <v>8445.748</v>
       </c>
       <c r="F79">
-        <v>14380.982</v>
+        <v>14567.748</v>
       </c>
       <c r="G79">
         <v>4712.2</v>
@@ -7771,37 +7771,37 @@
         <v>1428.7</v>
       </c>
       <c r="M79">
-        <v>1762.500716776535</v>
+        <v>1785.390336474932</v>
       </c>
       <c r="N79">
-        <v>-333.8007167765356</v>
+        <v>-356.6903364749321</v>
       </c>
       <c r="O79">
-        <v>-66.76014335530714</v>
+        <v>-71.33806729498643</v>
       </c>
       <c r="P79">
-        <v>-267.0405734212285</v>
+        <v>-285.3522691799457</v>
       </c>
       <c r="Q79">
-        <v>159.0594265787715</v>
+        <v>140.7477308200544</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1282450172240792</v>
+        <v>0.1319925180069919</v>
       </c>
       <c r="T79">
-        <v>1.695156329011208</v>
+        <v>1.772208889420809</v>
       </c>
       <c r="U79">
         <v>0.1225577444416894</v>
       </c>
       <c r="V79">
-        <v>0.1621219198835812</v>
+        <v>0.1600434337312276</v>
       </c>
       <c r="W79">
-        <v>0.1026884476162014</v>
+        <v>0.1029431821908871</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8106095994179061</v>
+        <v>0.8002171686561381</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1093340360704302</v>
+        <v>0.1761254531636593</v>
       </c>
       <c r="C80">
-        <v>-1004.031227627609</v>
+        <v>-4425.089704863309</v>
       </c>
       <c r="D80">
-        <v>8851.516772372392</v>
+        <v>5617.22429513669</v>
       </c>
       <c r="E80">
-        <v>8445.748</v>
+        <v>8632.513999999999</v>
       </c>
       <c r="F80">
-        <v>14567.748</v>
+        <v>14754.514</v>
       </c>
       <c r="G80">
         <v>4712.2</v>
@@ -7853,45 +7853,45 @@
         <v>1428.7</v>
       </c>
       <c r="M80">
-        <v>1785.390336474932</v>
+        <v>3021.101006973328</v>
       </c>
       <c r="N80">
-        <v>-356.6903364749321</v>
+        <v>-1592.401006973329</v>
       </c>
       <c r="O80">
-        <v>-71.33806729498643</v>
+        <v>-318.4802013946658</v>
       </c>
       <c r="P80">
-        <v>-285.3522691799457</v>
+        <v>-1273.920805578663</v>
       </c>
       <c r="Q80">
-        <v>140.7477308200544</v>
+        <v>-847.8208055786628</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1319925180069919</v>
+        <v>0.1412675886207164</v>
       </c>
       <c r="T80">
-        <v>1.772208889420809</v>
+        <v>1.962914103419949</v>
       </c>
       <c r="U80">
-        <v>0.1225577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V80">
-        <v>0.1600434337312276</v>
+        <v>0.09458141231969826</v>
       </c>
       <c r="W80">
-        <v>0.1029431821908871</v>
+        <v>0.1853914677889986</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8002171686561381</v>
+        <v>0.4729070615984913</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1761254531636593</v>
+        <v>0.1777150306080762</v>
       </c>
       <c r="C81">
-        <v>-4425.089704863309</v>
+        <v>-4660.282314835302</v>
       </c>
       <c r="D81">
-        <v>5617.22429513669</v>
+        <v>5568.797685164697</v>
       </c>
       <c r="E81">
-        <v>8632.513999999999</v>
+        <v>8819.279999999999</v>
       </c>
       <c r="F81">
-        <v>14754.514</v>
+        <v>14941.28</v>
       </c>
       <c r="G81">
         <v>4712.2</v>
@@ -7935,37 +7935,37 @@
         <v>1428.7</v>
       </c>
       <c r="M81">
-        <v>3021.101006973328</v>
+        <v>3059.342791871725</v>
       </c>
       <c r="N81">
-        <v>-1592.401006973329</v>
+        <v>-1630.642791871725</v>
       </c>
       <c r="O81">
-        <v>-318.4802013946658</v>
+        <v>-326.128558374345</v>
       </c>
       <c r="P81">
-        <v>-1273.920805578663</v>
+        <v>-1304.51423349738</v>
       </c>
       <c r="Q81">
-        <v>-847.8208055786628</v>
+        <v>-878.41423349738</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1412675886207164</v>
+        <v>0.1460409680517522</v>
       </c>
       <c r="T81">
-        <v>1.962914103419949</v>
+        <v>2.061059808590946</v>
       </c>
       <c r="U81">
         <v>0.2047577444416894</v>
       </c>
       <c r="V81">
-        <v>0.09458141231969826</v>
+        <v>0.09339914466570204</v>
       </c>
       <c r="W81">
-        <v>0.1853914677889986</v>
+        <v>0.1856335462471572</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4729070615984913</v>
+        <v>0.4669957233285101</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1777150306080762</v>
+        <v>0.1793046080524931</v>
       </c>
       <c r="C82">
-        <v>-4660.282314835302</v>
+        <v>-4894.647081160498</v>
       </c>
       <c r="D82">
-        <v>5568.797685164697</v>
+        <v>5521.198918839502</v>
       </c>
       <c r="E82">
-        <v>8819.279999999999</v>
+        <v>9006.046</v>
       </c>
       <c r="F82">
-        <v>14941.28</v>
+        <v>15128.046</v>
       </c>
       <c r="G82">
         <v>4712.2</v>
@@ -8017,37 +8017,37 @@
         <v>1428.7</v>
       </c>
       <c r="M82">
-        <v>3059.342791871725</v>
+        <v>3097.584576770122</v>
       </c>
       <c r="N82">
-        <v>-1630.642791871725</v>
+        <v>-1668.884576770122</v>
       </c>
       <c r="O82">
-        <v>-326.128558374345</v>
+        <v>-333.7769153540244</v>
       </c>
       <c r="P82">
-        <v>-1304.51423349738</v>
+        <v>-1335.107661416097</v>
       </c>
       <c r="Q82">
-        <v>-878.41423349738</v>
+        <v>-909.0076614160974</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1460409680517522</v>
+        <v>0.1513168084755286</v>
       </c>
       <c r="T82">
-        <v>2.061059808590946</v>
+        <v>2.169536640622049</v>
       </c>
       <c r="U82">
         <v>0.2047577444416894</v>
       </c>
       <c r="V82">
-        <v>0.09339914466570204</v>
+        <v>0.09224606880563163</v>
       </c>
       <c r="W82">
-        <v>0.1856335462471572</v>
+        <v>0.1858696474594354</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4669957233285101</v>
+        <v>0.4612303440281581</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1793046080524931</v>
+        <v>0.18089418549691</v>
       </c>
       <c r="C83">
-        <v>-4894.647081160498</v>
+        <v>-5128.205051678007</v>
       </c>
       <c r="D83">
-        <v>5521.198918839502</v>
+        <v>5474.406948321993</v>
       </c>
       <c r="E83">
-        <v>9006.046</v>
+        <v>9192.812</v>
       </c>
       <c r="F83">
-        <v>15128.046</v>
+        <v>15314.812</v>
       </c>
       <c r="G83">
         <v>4712.2</v>
@@ -8099,37 +8099,37 @@
         <v>1428.7</v>
       </c>
       <c r="M83">
-        <v>3097.584576770122</v>
+        <v>3135.826361668518</v>
       </c>
       <c r="N83">
-        <v>-1668.884576770122</v>
+        <v>-1707.126361668518</v>
       </c>
       <c r="O83">
-        <v>-333.7769153540244</v>
+        <v>-341.4252723337037</v>
       </c>
       <c r="P83">
-        <v>-1335.107661416097</v>
+        <v>-1365.701089334815</v>
       </c>
       <c r="Q83">
-        <v>-909.0076614160974</v>
+        <v>-939.6010893348147</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1513168084755286</v>
+        <v>0.1571788533908358</v>
       </c>
       <c r="T83">
-        <v>2.169536640622049</v>
+        <v>2.290066453989941</v>
       </c>
       <c r="U83">
         <v>0.2047577444416894</v>
       </c>
       <c r="V83">
-        <v>0.09224606880563163</v>
+        <v>0.09112111674702637</v>
       </c>
       <c r="W83">
-        <v>0.1858696474594354</v>
+        <v>0.1860999901055604</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4612303440281581</v>
+        <v>0.4556055837351318</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.18089418549691</v>
+        <v>0.1824837629413269</v>
       </c>
       <c r="C84">
-        <v>-5128.205051678007</v>
+        <v>-5360.97656670433</v>
       </c>
       <c r="D84">
-        <v>5474.406948321993</v>
+        <v>5428.401433295669</v>
       </c>
       <c r="E84">
-        <v>9192.812</v>
+        <v>9379.578</v>
       </c>
       <c r="F84">
-        <v>15314.812</v>
+        <v>15501.578</v>
       </c>
       <c r="G84">
         <v>4712.2</v>
@@ -8181,37 +8181,37 @@
         <v>1428.7</v>
       </c>
       <c r="M84">
-        <v>3135.826361668518</v>
+        <v>3174.068146566914</v>
       </c>
       <c r="N84">
-        <v>-1707.126361668518</v>
+        <v>-1745.368146566915</v>
       </c>
       <c r="O84">
-        <v>-341.4252723337037</v>
+        <v>-349.073629313383</v>
       </c>
       <c r="P84">
-        <v>-1365.701089334815</v>
+        <v>-1396.294517253532</v>
       </c>
       <c r="Q84">
-        <v>-939.6010893348147</v>
+        <v>-970.1945172535317</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1571788533908358</v>
+        <v>0.1637305506491202</v>
       </c>
       <c r="T84">
-        <v>2.290066453989941</v>
+        <v>2.424776245401114</v>
       </c>
       <c r="U84">
         <v>0.2047577444416894</v>
       </c>
       <c r="V84">
-        <v>0.09112111674702637</v>
+        <v>0.09002327196694172</v>
       </c>
       <c r="W84">
-        <v>0.1860999901055604</v>
+        <v>0.1863247823264776</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4556055837351318</v>
+        <v>0.4501163598347085</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1824837629413269</v>
+        <v>0.1840733403857438</v>
       </c>
       <c r="C85">
-        <v>-5360.97656670433</v>
+        <v>-5592.981288514788</v>
       </c>
       <c r="D85">
-        <v>5428.401433295669</v>
+        <v>5383.162711485213</v>
       </c>
       <c r="E85">
-        <v>9379.578</v>
+        <v>9566.344000000001</v>
       </c>
       <c r="F85">
-        <v>15501.578</v>
+        <v>15688.344</v>
       </c>
       <c r="G85">
         <v>4712.2</v>
@@ -8263,37 +8263,37 @@
         <v>1428.7</v>
       </c>
       <c r="M85">
-        <v>3174.068146566914</v>
+        <v>3212.309931465311</v>
       </c>
       <c r="N85">
-        <v>-1745.368146566915</v>
+        <v>-1783.609931465312</v>
       </c>
       <c r="O85">
-        <v>-349.073629313383</v>
+        <v>-356.7219862930623</v>
       </c>
       <c r="P85">
-        <v>-1396.294517253532</v>
+        <v>-1426.887945172249</v>
       </c>
       <c r="Q85">
-        <v>-970.1945172535317</v>
+        <v>-1000.787945172249</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1637305506491202</v>
+        <v>0.1711012100646903</v>
       </c>
       <c r="T85">
-        <v>2.424776245401114</v>
+        <v>2.576324760738685</v>
       </c>
       <c r="U85">
         <v>0.2047577444416894</v>
       </c>
       <c r="V85">
-        <v>0.09002327196694172</v>
+        <v>0.08895156634828764</v>
       </c>
       <c r="W85">
-        <v>0.1863247823264776</v>
+        <v>0.1865442223516587</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4501163598347085</v>
+        <v>0.4447578317414382</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1840733403857437</v>
+        <v>0.1856629178301607</v>
       </c>
       <c r="C86">
-        <v>-5592.981288514784</v>
+        <v>-5824.238229363013</v>
       </c>
       <c r="D86">
-        <v>5383.162711485214</v>
+        <v>5338.671770636987</v>
       </c>
       <c r="E86">
-        <v>9566.343999999997</v>
+        <v>9753.109999999999</v>
       </c>
       <c r="F86">
-        <v>15688.344</v>
+        <v>15875.11</v>
       </c>
       <c r="G86">
         <v>4712.2</v>
@@ -8345,37 +8345,37 @@
         <v>1428.7</v>
       </c>
       <c r="M86">
-        <v>3212.30993146531</v>
+        <v>3250.551716363707</v>
       </c>
       <c r="N86">
-        <v>-1783.609931465311</v>
+        <v>-1821.851716363708</v>
       </c>
       <c r="O86">
-        <v>-356.7219862930622</v>
+        <v>-364.3703432727415</v>
       </c>
       <c r="P86">
-        <v>-1426.887945172248</v>
+        <v>-1457.481373090966</v>
       </c>
       <c r="Q86">
-        <v>-1000.787945172248</v>
+        <v>-1031.381373090966</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1711012100646902</v>
+        <v>0.1794546240690029</v>
       </c>
       <c r="T86">
-        <v>2.576324760738682</v>
+        <v>2.748079744787928</v>
       </c>
       <c r="U86">
         <v>0.2047577444416894</v>
       </c>
       <c r="V86">
-        <v>0.08895156634828767</v>
+        <v>0.08790507733242546</v>
       </c>
       <c r="W86">
-        <v>0.1865442223516587</v>
+        <v>0.1867584990821297</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4447578317414383</v>
+        <v>0.4395253866621273</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1856629178301607</v>
+        <v>0.1872524952745775</v>
       </c>
       <c r="C87">
-        <v>-5824.238229363013</v>
+        <v>-6054.76577812237</v>
       </c>
       <c r="D87">
-        <v>5338.671770636987</v>
+        <v>5294.910221877628</v>
       </c>
       <c r="E87">
-        <v>9753.109999999999</v>
+        <v>9939.875999999998</v>
       </c>
       <c r="F87">
-        <v>15875.11</v>
+        <v>16061.876</v>
       </c>
       <c r="G87">
         <v>4712.2</v>
@@ -8427,37 +8427,37 @@
         <v>1428.7</v>
       </c>
       <c r="M87">
-        <v>3250.551716363707</v>
+        <v>3288.793501262104</v>
       </c>
       <c r="N87">
-        <v>-1821.851716363708</v>
+        <v>-1860.093501262104</v>
       </c>
       <c r="O87">
-        <v>-364.3703432727415</v>
+        <v>-372.0187002524209</v>
       </c>
       <c r="P87">
-        <v>-1457.481373090966</v>
+        <v>-1488.074801009684</v>
       </c>
       <c r="Q87">
-        <v>-1031.381373090966</v>
+        <v>-1061.974801009684</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1794546240690029</v>
+        <v>0.1890013829310745</v>
       </c>
       <c r="T87">
-        <v>2.748079744787928</v>
+        <v>2.944371155129923</v>
       </c>
       <c r="U87">
         <v>0.2047577444416894</v>
       </c>
       <c r="V87">
-        <v>0.08790507733242546</v>
+        <v>0.08688292527042051</v>
       </c>
       <c r="W87">
-        <v>0.1867584990821297</v>
+        <v>0.1869677926328222</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4395253866621273</v>
+        <v>0.4344146263521025</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1872524952745775</v>
+        <v>0.1888420727189944</v>
       </c>
       <c r="C88">
-        <v>-6054.76577812237</v>
+        <v>-6284.581725627731</v>
       </c>
       <c r="D88">
-        <v>5294.910221877628</v>
+        <v>5251.860274372267</v>
       </c>
       <c r="E88">
-        <v>9939.875999999998</v>
+        <v>10126.642</v>
       </c>
       <c r="F88">
-        <v>16061.876</v>
+        <v>16248.642</v>
       </c>
       <c r="G88">
         <v>4712.2</v>
@@ -8509,37 +8509,37 @@
         <v>1428.7</v>
       </c>
       <c r="M88">
-        <v>3288.793501262104</v>
+        <v>3327.035286160501</v>
       </c>
       <c r="N88">
-        <v>-1860.093501262104</v>
+        <v>-1898.335286160501</v>
       </c>
       <c r="O88">
-        <v>-372.0187002524209</v>
+        <v>-379.6670572321002</v>
       </c>
       <c r="P88">
-        <v>-1488.074801009684</v>
+        <v>-1518.668228928401</v>
       </c>
       <c r="Q88">
-        <v>-1061.974801009684</v>
+        <v>-1092.5682289284</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1890013829310745</v>
+        <v>0.2000168739257726</v>
       </c>
       <c r="T88">
-        <v>2.944371155129923</v>
+        <v>3.170861243986071</v>
       </c>
       <c r="U88">
         <v>0.2047577444416894</v>
       </c>
       <c r="V88">
-        <v>0.08688292527042051</v>
+        <v>0.08588427095696739</v>
       </c>
       <c r="W88">
-        <v>0.1869677926328222</v>
+        <v>0.1871722748375219</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4344146263521025</v>
+        <v>0.4294213547848369</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1888420727189944</v>
+        <v>0.1904316501634113</v>
       </c>
       <c r="C89">
-        <v>-6284.581725627731</v>
+        <v>-6513.703288790985</v>
       </c>
       <c r="D89">
-        <v>5251.860274372267</v>
+        <v>5209.504711209014</v>
       </c>
       <c r="E89">
-        <v>10126.642</v>
+        <v>10313.408</v>
       </c>
       <c r="F89">
-        <v>16248.642</v>
+        <v>16435.408</v>
       </c>
       <c r="G89">
         <v>4712.2</v>
@@ -8591,37 +8591,37 @@
         <v>1428.7</v>
       </c>
       <c r="M89">
-        <v>3327.035286160501</v>
+        <v>3365.277071058897</v>
       </c>
       <c r="N89">
-        <v>-1898.335286160501</v>
+        <v>-1936.577071058898</v>
       </c>
       <c r="O89">
-        <v>-379.6670572321002</v>
+        <v>-387.3154142117796</v>
       </c>
       <c r="P89">
-        <v>-1518.668228928401</v>
+        <v>-1549.261656847118</v>
       </c>
       <c r="Q89">
-        <v>-1092.5682289284</v>
+        <v>-1123.161656847118</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2000168739257726</v>
+        <v>0.2128682800862536</v>
       </c>
       <c r="T89">
-        <v>3.170861243986071</v>
+        <v>3.43509968098491</v>
       </c>
       <c r="U89">
         <v>0.2047577444416894</v>
       </c>
       <c r="V89">
-        <v>0.08588427095696739</v>
+        <v>0.08490831333245639</v>
       </c>
       <c r="W89">
-        <v>0.1871722748375219</v>
+        <v>0.1873721097193874</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4294213547848369</v>
+        <v>0.4245415666622819</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1904316501634113</v>
+        <v>0.1920212276078282</v>
       </c>
       <c r="C90">
-        <v>-6513.703288790985</v>
+        <v>-6742.147133558945</v>
       </c>
       <c r="D90">
-        <v>5209.504711209014</v>
+        <v>5167.826866441055</v>
       </c>
       <c r="E90">
-        <v>10313.408</v>
+        <v>10500.174</v>
       </c>
       <c r="F90">
-        <v>16435.408</v>
+        <v>16622.174</v>
       </c>
       <c r="G90">
         <v>4712.2</v>
@@ -8673,37 +8673,37 @@
         <v>1428.7</v>
       </c>
       <c r="M90">
-        <v>3365.277071058897</v>
+        <v>3403.518855957294</v>
       </c>
       <c r="N90">
-        <v>-1936.577071058898</v>
+        <v>-1974.818855957294</v>
       </c>
       <c r="O90">
-        <v>-387.3154142117796</v>
+        <v>-394.9637711914588</v>
       </c>
       <c r="P90">
-        <v>-1549.261656847118</v>
+        <v>-1579.855084765835</v>
       </c>
       <c r="Q90">
-        <v>-1123.161656847118</v>
+        <v>-1153.755084765835</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2128682800862536</v>
+        <v>0.2280563055486403</v>
       </c>
       <c r="T90">
-        <v>3.43509968098491</v>
+        <v>3.747381470165357</v>
       </c>
       <c r="U90">
         <v>0.2047577444416894</v>
       </c>
       <c r="V90">
-        <v>0.08490831333245639</v>
+        <v>0.08395428733995688</v>
       </c>
       <c r="W90">
-        <v>0.1873721097193874</v>
+        <v>0.1875674539297504</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4245415666622819</v>
+        <v>0.4197714366997845</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1920212276078282</v>
+        <v>0.1936108050522451</v>
       </c>
       <c r="C91">
-        <v>-6742.147133558945</v>
+        <v>-6969.929396777992</v>
       </c>
       <c r="D91">
-        <v>5167.826866441055</v>
+        <v>5126.810603222008</v>
       </c>
       <c r="E91">
-        <v>10500.174</v>
+        <v>10686.94</v>
       </c>
       <c r="F91">
-        <v>16622.174</v>
+        <v>16808.94</v>
       </c>
       <c r="G91">
         <v>4712.2</v>
@@ -8755,37 +8755,37 @@
         <v>1428.7</v>
       </c>
       <c r="M91">
-        <v>3403.518855957294</v>
+        <v>3441.76064085569</v>
       </c>
       <c r="N91">
-        <v>-1974.818855957294</v>
+        <v>-2013.060640855691</v>
       </c>
       <c r="O91">
-        <v>-394.9637711914588</v>
+        <v>-402.6121281711381</v>
       </c>
       <c r="P91">
-        <v>-1579.855084765835</v>
+        <v>-1610.448512684552</v>
       </c>
       <c r="Q91">
-        <v>-1153.755084765835</v>
+        <v>-1184.348512684553</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2280563055486403</v>
+        <v>0.2462819361035044</v>
       </c>
       <c r="T91">
-        <v>3.747381470165357</v>
+        <v>4.122119617181893</v>
       </c>
       <c r="U91">
         <v>0.2047577444416894</v>
       </c>
       <c r="V91">
-        <v>0.08395428733995688</v>
+        <v>0.08302146192506848</v>
       </c>
       <c r="W91">
-        <v>0.1875674539297504</v>
+        <v>0.1877584571576608</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4197714366997845</v>
+        <v>0.4151073096253424</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1936108050522451</v>
+        <v>0.1952003824966621</v>
       </c>
       <c r="C92">
-        <v>-6969.929396777992</v>
+        <v>-7197.065707025686</v>
       </c>
       <c r="D92">
-        <v>5126.810603222008</v>
+        <v>5086.440292974313</v>
       </c>
       <c r="E92">
-        <v>10686.94</v>
+        <v>10873.706</v>
       </c>
       <c r="F92">
-        <v>16808.94</v>
+        <v>16995.706</v>
       </c>
       <c r="G92">
         <v>4712.2</v>
@@ -8837,37 +8837,37 @@
         <v>1428.7</v>
       </c>
       <c r="M92">
-        <v>3441.76064085569</v>
+        <v>3480.002425754087</v>
       </c>
       <c r="N92">
-        <v>-2013.060640855691</v>
+        <v>-2051.302425754087</v>
       </c>
       <c r="O92">
-        <v>-402.6121281711381</v>
+        <v>-410.2604851508174</v>
       </c>
       <c r="P92">
-        <v>-1610.448512684552</v>
+        <v>-1641.041940603269</v>
       </c>
       <c r="Q92">
-        <v>-1184.348512684553</v>
+        <v>-1214.941940603269</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2462819361035044</v>
+        <v>0.2685577067816715</v>
       </c>
       <c r="T92">
-        <v>4.122119617181893</v>
+        <v>4.580132907979881</v>
       </c>
       <c r="U92">
         <v>0.2047577444416894</v>
       </c>
       <c r="V92">
-        <v>0.08302146192506848</v>
+        <v>0.08210913816765014</v>
       </c>
       <c r="W92">
-        <v>0.1877584571576608</v>
+        <v>0.1879452625124303</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4151073096253424</v>
+        <v>0.4105456908382508</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1952003824966621</v>
+        <v>0.196789959941079</v>
       </c>
       <c r="C93">
-        <v>-7197.065707025686</v>
+        <v>-7423.571204465861</v>
       </c>
       <c r="D93">
-        <v>5086.440292974313</v>
+        <v>5046.700795534138</v>
       </c>
       <c r="E93">
-        <v>10873.706</v>
+        <v>11060.472</v>
       </c>
       <c r="F93">
-        <v>16995.706</v>
+        <v>17182.472</v>
       </c>
       <c r="G93">
         <v>4712.2</v>
@@ -8919,37 +8919,37 @@
         <v>1428.7</v>
       </c>
       <c r="M93">
-        <v>3480.002425754087</v>
+        <v>3518.244210652483</v>
       </c>
       <c r="N93">
-        <v>-2051.302425754087</v>
+        <v>-2089.544210652483</v>
       </c>
       <c r="O93">
-        <v>-410.2604851508174</v>
+        <v>-417.9088421304967</v>
       </c>
       <c r="P93">
-        <v>-1641.041940603269</v>
+        <v>-1671.635368521987</v>
       </c>
       <c r="Q93">
-        <v>-1214.941940603269</v>
+        <v>-1245.535368521987</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2685577067816715</v>
+        <v>0.2964024201293806</v>
       </c>
       <c r="T93">
-        <v>4.580132907979881</v>
+        <v>5.152649521477368</v>
       </c>
       <c r="U93">
         <v>0.2047577444416894</v>
       </c>
       <c r="V93">
-        <v>0.08210913816765014</v>
+        <v>0.08121664753539309</v>
       </c>
       <c r="W93">
-        <v>0.1879452625124303</v>
+        <v>0.1881280068812266</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4105456908382508</v>
+        <v>0.4060832376769654</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.196789959941079</v>
+        <v>0.1983795373854958</v>
       </c>
       <c r="C94">
-        <v>-7423.571204465861</v>
+        <v>-7649.46055978018</v>
       </c>
       <c r="D94">
-        <v>5046.700795534138</v>
+        <v>5007.577440219821</v>
       </c>
       <c r="E94">
-        <v>11060.472</v>
+        <v>11247.238</v>
       </c>
       <c r="F94">
-        <v>17182.472</v>
+        <v>17369.238</v>
       </c>
       <c r="G94">
         <v>4712.2</v>
@@ -9001,37 +9001,37 @@
         <v>1428.7</v>
       </c>
       <c r="M94">
-        <v>3518.244210652483</v>
+        <v>3556.48599555088</v>
       </c>
       <c r="N94">
-        <v>-2089.544210652483</v>
+        <v>-2127.785995550881</v>
       </c>
       <c r="O94">
-        <v>-417.9088421304967</v>
+        <v>-425.5571991101762</v>
       </c>
       <c r="P94">
-        <v>-1671.635368521987</v>
+        <v>-1702.228796440705</v>
       </c>
       <c r="Q94">
-        <v>-1245.535368521987</v>
+        <v>-1276.128796440705</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2964024201293806</v>
+        <v>0.3322027658621493</v>
       </c>
       <c r="T94">
-        <v>5.152649521477368</v>
+        <v>5.88874231025985</v>
       </c>
       <c r="U94">
         <v>0.2047577444416894</v>
       </c>
       <c r="V94">
-        <v>0.08121664753539309</v>
+        <v>0.08034335025006627</v>
       </c>
       <c r="W94">
-        <v>0.1881280068812266</v>
+        <v>0.1883068212635972</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4060832376769654</v>
+        <v>0.4017167512503312</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1983795373854958</v>
+        <v>0.1999691148299127</v>
       </c>
       <c r="C95">
-        <v>-7649.46055978018</v>
+        <v>-7874.74799222589</v>
       </c>
       <c r="D95">
-        <v>5007.577440219821</v>
+        <v>4969.05600777411</v>
       </c>
       <c r="E95">
-        <v>11247.238</v>
+        <v>11434.004</v>
       </c>
       <c r="F95">
-        <v>17369.238</v>
+        <v>17556.004</v>
       </c>
       <c r="G95">
         <v>4712.2</v>
@@ -9083,37 +9083,37 @@
         <v>1428.7</v>
       </c>
       <c r="M95">
-        <v>3556.48599555088</v>
+        <v>3594.727780449277</v>
       </c>
       <c r="N95">
-        <v>-2127.785995550881</v>
+        <v>-2166.027780449277</v>
       </c>
       <c r="O95">
-        <v>-425.5571991101762</v>
+        <v>-433.2055560898555</v>
       </c>
       <c r="P95">
-        <v>-1702.228796440705</v>
+        <v>-1732.822224359422</v>
       </c>
       <c r="Q95">
-        <v>-1276.128796440705</v>
+        <v>-1306.722224359421</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3322027658621493</v>
+        <v>0.3799365601725075</v>
       </c>
       <c r="T95">
-        <v>5.88874231025985</v>
+        <v>6.870199361969827</v>
       </c>
       <c r="U95">
         <v>0.2047577444416894</v>
       </c>
       <c r="V95">
-        <v>0.08034335025006627</v>
+        <v>0.07948863375804428</v>
       </c>
       <c r="W95">
-        <v>0.1883068212635972</v>
+        <v>0.1884818310846407</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4017167512503312</v>
+        <v>0.3974431687902213</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1999691148299127</v>
+        <v>0.2015586922743296</v>
       </c>
       <c r="C96">
-        <v>-7874.74799222589</v>
+        <v>-8099.447286866493</v>
       </c>
       <c r="D96">
-        <v>4969.05600777411</v>
+        <v>4931.122713133508</v>
       </c>
       <c r="E96">
-        <v>11434.004</v>
+        <v>11620.77</v>
       </c>
       <c r="F96">
-        <v>17556.004</v>
+        <v>17742.77</v>
       </c>
       <c r="G96">
         <v>4712.2</v>
@@ -9165,37 +9165,37 @@
         <v>1428.7</v>
       </c>
       <c r="M96">
-        <v>3594.727780449277</v>
+        <v>3632.969565347673</v>
       </c>
       <c r="N96">
-        <v>-2166.027780449277</v>
+        <v>-2204.269565347674</v>
       </c>
       <c r="O96">
-        <v>-433.2055560898555</v>
+        <v>-440.8539130695347</v>
       </c>
       <c r="P96">
-        <v>-1732.822224359422</v>
+        <v>-1763.415652278139</v>
       </c>
       <c r="Q96">
-        <v>-1306.722224359421</v>
+        <v>-1337.315652278139</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3799365601725075</v>
+        <v>0.4467638722070092</v>
       </c>
       <c r="T96">
-        <v>6.870199361969827</v>
+        <v>8.244239234363796</v>
       </c>
       <c r="U96">
         <v>0.2047577444416894</v>
       </c>
       <c r="V96">
-        <v>0.07948863375804428</v>
+        <v>0.07865191129743329</v>
       </c>
       <c r="W96">
-        <v>0.1884818310846407</v>
+        <v>0.1886531564883991</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3974431687902213</v>
+        <v>0.3932595564871665</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2015586922743296</v>
+        <v>0.2031482697187465</v>
       </c>
       <c r="C97">
-        <v>-8099.447286866493</v>
+        <v>-8323.571811019128</v>
       </c>
       <c r="D97">
-        <v>4931.122713133508</v>
+        <v>4893.764188980872</v>
       </c>
       <c r="E97">
-        <v>11620.77</v>
+        <v>11807.536</v>
       </c>
       <c r="F97">
-        <v>17742.77</v>
+        <v>17929.536</v>
       </c>
       <c r="G97">
         <v>4712.2</v>
@@ -9247,37 +9247,37 @@
         <v>1428.7</v>
       </c>
       <c r="M97">
-        <v>3632.969565347673</v>
+        <v>3671.21135024607</v>
       </c>
       <c r="N97">
-        <v>-2204.269565347674</v>
+        <v>-2242.51135024607</v>
       </c>
       <c r="O97">
-        <v>-440.8539130695347</v>
+        <v>-448.5022700492141</v>
       </c>
       <c r="P97">
-        <v>-1763.415652278139</v>
+        <v>-1794.009080196856</v>
       </c>
       <c r="Q97">
-        <v>-1337.315652278139</v>
+        <v>-1367.909080196856</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4467638722070092</v>
+        <v>0.5470048402587616</v>
       </c>
       <c r="T97">
-        <v>8.244239234363796</v>
+        <v>10.30529904295475</v>
       </c>
       <c r="U97">
         <v>0.2047577444416894</v>
       </c>
       <c r="V97">
-        <v>0.07865191129743329</v>
+        <v>0.07783262055475169</v>
       </c>
       <c r="W97">
-        <v>0.1886531564883991</v>
+        <v>0.1888209126129126</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3932595564871665</v>
+        <v>0.3891631027737584</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2031482697187465</v>
+        <v>0.2047378471631634</v>
       </c>
       <c r="C98">
-        <v>-8323.571811019123</v>
+        <v>-8547.134529959987</v>
       </c>
       <c r="D98">
-        <v>4893.764188980873</v>
+        <v>4856.967470040013</v>
       </c>
       <c r="E98">
-        <v>11807.536</v>
+        <v>11994.302</v>
       </c>
       <c r="F98">
-        <v>17929.536</v>
+        <v>18116.302</v>
       </c>
       <c r="G98">
         <v>4712.2</v>
@@ -9329,37 +9329,37 @@
         <v>1428.7</v>
       </c>
       <c r="M98">
-        <v>3671.211350246069</v>
+        <v>3709.453135144467</v>
       </c>
       <c r="N98">
-        <v>-2242.511350246069</v>
+        <v>-2280.753135144467</v>
       </c>
       <c r="O98">
-        <v>-448.5022700492139</v>
+        <v>-456.1506270288934</v>
       </c>
       <c r="P98">
-        <v>-1794.009080196856</v>
+        <v>-1824.602508115574</v>
       </c>
       <c r="Q98">
-        <v>-1367.909080196855</v>
+        <v>-1398.502508115574</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5470048402587604</v>
+        <v>0.7140731203450139</v>
       </c>
       <c r="T98">
-        <v>10.30529904295472</v>
+        <v>13.74039872393963</v>
       </c>
       <c r="U98">
         <v>0.2047577444416894</v>
       </c>
       <c r="V98">
-        <v>0.07783262055475171</v>
+        <v>0.0770302224047027</v>
       </c>
       <c r="W98">
-        <v>0.1888209126129126</v>
+        <v>0.1889852098482608</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3891631027737585</v>
+        <v>0.3851511120235135</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2047378471631634</v>
+        <v>0.2063274246075803</v>
       </c>
       <c r="C99">
-        <v>-8547.134529959987</v>
+        <v>-8770.14802192643</v>
       </c>
       <c r="D99">
-        <v>4856.967470040013</v>
+        <v>4820.719978073568</v>
       </c>
       <c r="E99">
-        <v>11994.302</v>
+        <v>12181.068</v>
       </c>
       <c r="F99">
-        <v>18116.302</v>
+        <v>18303.068</v>
       </c>
       <c r="G99">
         <v>4712.2</v>
@@ -9411,37 +9411,37 @@
         <v>1428.7</v>
       </c>
       <c r="M99">
-        <v>3709.453135144467</v>
+        <v>3747.694920042863</v>
       </c>
       <c r="N99">
-        <v>-2280.753135144467</v>
+        <v>-2318.994920042863</v>
       </c>
       <c r="O99">
-        <v>-456.1506270288934</v>
+        <v>-463.7989840085727</v>
       </c>
       <c r="P99">
-        <v>-1824.602508115574</v>
+        <v>-1855.195936034291</v>
       </c>
       <c r="Q99">
-        <v>-1398.502508115574</v>
+        <v>-1429.09593603429</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7140731203450139</v>
+        <v>1.048209680517521</v>
       </c>
       <c r="T99">
-        <v>13.74039872393963</v>
+        <v>20.61059808590944</v>
       </c>
       <c r="U99">
         <v>0.2047577444416894</v>
       </c>
       <c r="V99">
-        <v>0.0770302224047027</v>
+        <v>0.07624419972710371</v>
       </c>
       <c r="W99">
-        <v>0.1889852098482608</v>
+        <v>0.189146154078806</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3851511120235135</v>
+        <v>0.3812209986355185</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2063274246075803</v>
+        <v>0.2079170020519972</v>
       </c>
       <c r="C100">
-        <v>-8770.14802192643</v>
+        <v>-8992.624492452347</v>
       </c>
       <c r="D100">
-        <v>4820.719978073568</v>
+        <v>4785.009507547652</v>
       </c>
       <c r="E100">
-        <v>12181.068</v>
+        <v>12367.834</v>
       </c>
       <c r="F100">
-        <v>18303.068</v>
+        <v>18489.834</v>
       </c>
       <c r="G100">
         <v>4712.2</v>
@@ -9493,37 +9493,37 @@
         <v>1428.7</v>
       </c>
       <c r="M100">
-        <v>3747.694920042863</v>
+        <v>3785.936704941259</v>
       </c>
       <c r="N100">
-        <v>-2318.994920042863</v>
+        <v>-2357.23670494126</v>
       </c>
       <c r="O100">
-        <v>-463.7989840085727</v>
+        <v>-471.4473409882519</v>
       </c>
       <c r="P100">
-        <v>-1855.195936034291</v>
+        <v>-1885.789363953008</v>
       </c>
       <c r="Q100">
-        <v>-1429.09593603429</v>
+        <v>-1459.689363953008</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.048209680517521</v>
+        <v>2.050619361035042</v>
       </c>
       <c r="T100">
-        <v>20.61059808590944</v>
+        <v>41.22119617181889</v>
       </c>
       <c r="U100">
         <v>0.2047577444416894</v>
       </c>
       <c r="V100">
-        <v>0.07624419972710371</v>
+        <v>0.07547405629551679</v>
       </c>
       <c r="W100">
-        <v>0.189146154078806</v>
+        <v>0.1893038469107543</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3812209986355185</v>
+        <v>0.377370281477584</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2079170020519972</v>
-      </c>
-      <c r="C101">
-        <v>-8992.624492452347</v>
-      </c>
-      <c r="D101">
-        <v>4785.009507547652</v>
-      </c>
-      <c r="E101">
-        <v>12367.834</v>
-      </c>
-      <c r="F101">
-        <v>18489.834</v>
-      </c>
-      <c r="G101">
-        <v>4712.2</v>
-      </c>
-      <c r="H101">
-        <v>12554.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1854.8</v>
-      </c>
-      <c r="K101">
-        <v>426.1</v>
-      </c>
-      <c r="L101">
-        <v>1428.7</v>
-      </c>
-      <c r="M101">
-        <v>3785.936704941259</v>
-      </c>
-      <c r="N101">
-        <v>-2357.23670494126</v>
-      </c>
-      <c r="O101">
-        <v>-471.4473409882519</v>
-      </c>
-      <c r="P101">
-        <v>-1885.789363953008</v>
-      </c>
-      <c r="Q101">
-        <v>-1459.689363953008</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.050619361035042</v>
-      </c>
-      <c r="T101">
-        <v>41.22119617181889</v>
-      </c>
-      <c r="U101">
-        <v>0.2047577444416894</v>
-      </c>
-      <c r="V101">
-        <v>0.07547405629551679</v>
-      </c>
-      <c r="W101">
-        <v>0.1893038469107543</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.377370281477584</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
